--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -2525,7 +2525,7 @@
         <v>122821104</v>
       </c>
       <c r="B16" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>122817980</v>
       </c>
       <c r="B17" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2794,10 +2794,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821729</v>
+        <v>122821824</v>
       </c>
       <c r="B18" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2829,12 +2829,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524077</v>
+        <v>524055</v>
       </c>
       <c r="R18" t="n">
-        <v>6714076</v>
+        <v>6714048</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2898,12 +2898,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2930,10 +2925,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122821198</v>
+        <v>122821729</v>
       </c>
       <c r="B19" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2965,12 +2960,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2978,7 +2973,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2990,10 +2984,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524049</v>
+        <v>524077</v>
       </c>
       <c r="R19" t="n">
-        <v>6714097</v>
+        <v>6714076</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3005,7 +2999,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -3025,7 +3019,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3035,12 +3029,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3049,7 +3043,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3071,7 +3064,7 @@
         <v>122821745</v>
       </c>
       <c r="B20" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3199,10 +3192,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122821824</v>
+        <v>122821198</v>
       </c>
       <c r="B21" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3247,6 +3240,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3258,10 +3252,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524055</v>
+        <v>524049</v>
       </c>
       <c r="R21" t="n">
-        <v>6714048</v>
+        <v>6714097</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3273,7 +3267,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -3293,7 +3287,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3303,7 +3297,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3312,6 +3311,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -2522,7 +2522,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122821104</v>
+        <v>122821824</v>
       </c>
       <c r="B16" t="n">
         <v>98355</v>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524057</v>
+        <v>524055</v>
       </c>
       <c r="R16" t="n">
-        <v>6714094</v>
+        <v>6714048</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2626,12 +2626,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2794,7 +2789,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821824</v>
+        <v>122821729</v>
       </c>
       <c r="B18" t="n">
         <v>98355</v>
@@ -2829,12 +2824,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2853,10 +2848,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524055</v>
+        <v>524077</v>
       </c>
       <c r="R18" t="n">
-        <v>6714048</v>
+        <v>6714076</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2888,7 +2883,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2898,7 +2893,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2925,7 +2925,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122821729</v>
+        <v>122821198</v>
       </c>
       <c r="B19" t="n">
         <v>98355</v>
@@ -2960,12 +2960,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2973,6 +2973,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2984,10 +2985,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524077</v>
+        <v>524049</v>
       </c>
       <c r="R19" t="n">
-        <v>6714076</v>
+        <v>6714097</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2999,7 +3000,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -3019,7 +3020,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3029,12 +3030,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3043,6 +3044,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3192,7 +3194,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122821198</v>
+        <v>122821104</v>
       </c>
       <c r="B21" t="n">
         <v>98355</v>
@@ -3227,12 +3229,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3240,7 +3242,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3252,10 +3253,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524049</v>
+        <v>524057</v>
       </c>
       <c r="R21" t="n">
-        <v>6714097</v>
+        <v>6714094</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3267,7 +3268,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -3302,7 +3303,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3311,7 +3312,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2522,10 +2522,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122821824</v>
+        <v>122821104</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524055</v>
+        <v>524057</v>
       </c>
       <c r="R16" t="n">
-        <v>6714048</v>
+        <v>6714094</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2626,7 +2626,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2656,7 +2661,7 @@
         <v>122817980</v>
       </c>
       <c r="B17" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2789,10 +2794,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821729</v>
+        <v>122821198</v>
       </c>
       <c r="B18" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2824,12 +2829,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2837,6 +2842,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2848,10 +2854,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524077</v>
+        <v>524049</v>
       </c>
       <c r="R18" t="n">
-        <v>6714076</v>
+        <v>6714097</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2863,7 +2869,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2883,7 +2889,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2893,12 +2899,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2907,6 +2913,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2925,10 +2932,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122821198</v>
+        <v>122821824</v>
       </c>
       <c r="B19" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2973,7 +2980,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2985,10 +2991,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524049</v>
+        <v>524055</v>
       </c>
       <c r="R19" t="n">
-        <v>6714097</v>
+        <v>6714048</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3000,7 +3006,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -3020,7 +3026,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3030,12 +3036,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3044,7 +3045,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3063,10 +3063,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122821745</v>
+        <v>122821729</v>
       </c>
       <c r="B20" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524080</v>
+        <v>524077</v>
       </c>
       <c r="R20" t="n">
-        <v>6714074</v>
+        <v>6714076</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3167,7 +3167,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3194,10 +3199,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122821104</v>
+        <v>122821745</v>
       </c>
       <c r="B21" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3229,12 +3234,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3253,10 +3258,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524057</v>
+        <v>524080</v>
       </c>
       <c r="R21" t="n">
-        <v>6714094</v>
+        <v>6714074</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3288,7 +3293,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3298,12 +3303,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3327,6 +3327,395 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122916997</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>524142</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6713729</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122915863</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>524025</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6713544</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122917069</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>524154</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6713729</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3717,6 +3717,1409 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122958064</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>524144</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6713722</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122959354</v>
+      </c>
+      <c r="B26" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>524122</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6713710</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122957710</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>524145</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6713733</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122958842</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57848</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Banvallen, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>524149</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6713704</v>
+      </c>
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122958244</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>524143</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6713721</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122959503</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>524145</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6713672</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>122961337</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90944</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>524040</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6713957</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>122958631</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>524136</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6713723</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122958484</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>524142</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6713723</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122959453</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8441</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>524128</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6713669</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122958550</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98357</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>524147</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6713728</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-03-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -2522,7 +2522,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122821104</v>
+        <v>122817980</v>
       </c>
       <c r="B16" t="n">
         <v>98357</v>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2577,14 +2577,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524057</v>
+        <v>524038</v>
       </c>
       <c r="R16" t="n">
-        <v>6714094</v>
+        <v>6713288</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>10-15 bladrosetter under klen senvuxen gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2658,7 +2658,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122817980</v>
+        <v>122821824</v>
       </c>
       <c r="B17" t="n">
         <v>98357</v>
@@ -2713,14 +2713,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524038</v>
+        <v>524055</v>
       </c>
       <c r="R17" t="n">
-        <v>6713288</v>
+        <v>6714048</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2762,12 +2762,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>10-15 bladrosetter under klen senvuxen gran.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2932,7 +2927,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122821824</v>
+        <v>122821729</v>
       </c>
       <c r="B19" t="n">
         <v>98357</v>
@@ -2967,12 +2962,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2991,10 +2986,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524055</v>
+        <v>524077</v>
       </c>
       <c r="R19" t="n">
-        <v>6714048</v>
+        <v>6714076</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3026,7 +3021,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3036,7 +3031,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3063,7 +3063,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122821729</v>
+        <v>122821104</v>
       </c>
       <c r="B20" t="n">
         <v>98357</v>
@@ -3098,12 +3098,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524077</v>
+        <v>524057</v>
       </c>
       <c r="R20" t="n">
-        <v>6714076</v>
+        <v>6714094</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3330,7 +3330,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122916997</v>
+        <v>122917069</v>
       </c>
       <c r="B22" t="n">
         <v>98357</v>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524142</v>
+        <v>524154</v>
       </c>
       <c r="R22" t="n">
         <v>6713729</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3583,7 +3583,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122917069</v>
+        <v>122916997</v>
       </c>
       <c r="B24" t="n">
         <v>98357</v>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524154</v>
+        <v>524142</v>
       </c>
       <c r="R24" t="n">
         <v>6713729</v>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3687,12 +3687,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3719,10 +3719,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122958064</v>
+        <v>122959354</v>
       </c>
       <c r="B25" t="n">
-        <v>98357</v>
+        <v>8441</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3731,45 +3731,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3778,10 +3764,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524144</v>
+        <v>524122</v>
       </c>
       <c r="R25" t="n">
-        <v>6713722</v>
+        <v>6713710</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3813,7 +3799,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3823,12 +3809,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3855,10 +3836,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122959354</v>
+        <v>122958064</v>
       </c>
       <c r="B26" t="n">
-        <v>8441</v>
+        <v>98357</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3867,31 +3848,45 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3900,10 +3895,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524122</v>
+        <v>524144</v>
       </c>
       <c r="R26" t="n">
-        <v>6713710</v>
+        <v>6713722</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3935,7 +3930,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3945,7 +3940,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4103,10 +4103,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122958842</v>
+        <v>122959503</v>
       </c>
       <c r="B28" t="n">
-        <v>57848</v>
+        <v>98357</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4115,25 +4115,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4141,24 +4141,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524149</v>
+        <v>524145</v>
       </c>
       <c r="R28" t="n">
-        <v>6713704</v>
+        <v>6713672</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4187,7 +4192,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4197,7 +4202,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4224,10 +4229,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122958244</v>
+        <v>122961337</v>
       </c>
       <c r="B29" t="n">
-        <v>98357</v>
+        <v>90944</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4236,57 +4241,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524143</v>
+        <v>524040</v>
       </c>
       <c r="R29" t="n">
-        <v>6713721</v>
+        <v>6713957</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4318,7 +4307,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4328,12 +4317,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4342,6 +4326,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4360,10 +4345,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122959503</v>
+        <v>122958842</v>
       </c>
       <c r="B30" t="n">
-        <v>98357</v>
+        <v>57848</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4372,25 +4357,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4398,29 +4383,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524145</v>
+        <v>524149</v>
       </c>
       <c r="R30" t="n">
-        <v>6713672</v>
+        <v>6713704</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4449,7 +4429,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4459,7 +4439,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4486,10 +4466,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122961337</v>
+        <v>122958484</v>
       </c>
       <c r="B31" t="n">
-        <v>90944</v>
+        <v>98357</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4498,41 +4478,57 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524040</v>
+        <v>524142</v>
       </c>
       <c r="R31" t="n">
-        <v>6713957</v>
+        <v>6713723</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4564,7 +4560,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4574,7 +4570,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4583,7 +4579,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4602,10 +4597,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122958631</v>
+        <v>122959453</v>
       </c>
       <c r="B32" t="n">
-        <v>98357</v>
+        <v>8441</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4614,45 +4609,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4661,10 +4642,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524136</v>
+        <v>524128</v>
       </c>
       <c r="R32" t="n">
-        <v>6713723</v>
+        <v>6713669</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4696,7 +4677,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4706,12 +4687,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4738,7 +4714,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122958484</v>
+        <v>122958631</v>
       </c>
       <c r="B33" t="n">
         <v>98357</v>
@@ -4773,7 +4749,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4797,7 +4773,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524142</v>
+        <v>524136</v>
       </c>
       <c r="R33" t="n">
         <v>6713723</v>
@@ -4832,7 +4808,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4842,7 +4818,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4869,10 +4850,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122959453</v>
+        <v>122958244</v>
       </c>
       <c r="B34" t="n">
-        <v>8441</v>
+        <v>98357</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4881,31 +4862,45 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4914,10 +4909,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524128</v>
+        <v>524143</v>
       </c>
       <c r="R34" t="n">
-        <v>6713669</v>
+        <v>6713721</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4949,7 +4944,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4959,7 +4954,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD34" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -2522,10 +2522,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122817980</v>
+        <v>122821198</v>
       </c>
       <c r="B16" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2570,6 +2570,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2577,14 +2578,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524038</v>
+        <v>524049</v>
       </c>
       <c r="R16" t="n">
-        <v>6713288</v>
+        <v>6714097</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2596,7 +2597,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2616,7 +2617,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2626,12 +2627,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>10-15 bladrosetter under klen senvuxen gran.</t>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2640,6 +2641,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2658,10 +2660,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122821824</v>
+        <v>122821745</v>
       </c>
       <c r="B17" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2698,7 +2700,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2717,10 +2719,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524055</v>
+        <v>524080</v>
       </c>
       <c r="R17" t="n">
-        <v>6714048</v>
+        <v>6714074</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2752,7 +2754,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2762,7 +2764,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2789,10 +2791,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821198</v>
+        <v>122821104</v>
       </c>
       <c r="B18" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2824,12 +2826,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2837,7 +2839,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2849,10 +2850,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524049</v>
+        <v>524057</v>
       </c>
       <c r="R18" t="n">
-        <v>6714097</v>
+        <v>6714094</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2864,7 +2865,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2899,7 +2900,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2908,7 +2909,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2927,10 +2927,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122821729</v>
+        <v>122817980</v>
       </c>
       <c r="B19" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2982,14 +2982,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524077</v>
+        <v>524038</v>
       </c>
       <c r="R19" t="n">
-        <v>6714076</v>
+        <v>6713288</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3031,12 +3031,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>10-15 bladrosetter under klen senvuxen gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3063,10 +3063,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122821104</v>
+        <v>122821824</v>
       </c>
       <c r="B20" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3098,12 +3098,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3122,10 +3122,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524057</v>
+        <v>524055</v>
       </c>
       <c r="R20" t="n">
-        <v>6714094</v>
+        <v>6714048</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3157,7 +3157,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3167,12 +3167,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3199,10 +3194,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122821745</v>
+        <v>122821729</v>
       </c>
       <c r="B21" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3234,7 +3229,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3258,10 +3253,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524080</v>
+        <v>524077</v>
       </c>
       <c r="R21" t="n">
-        <v>6714074</v>
+        <v>6714076</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3293,7 +3288,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3303,7 +3298,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122917069</v>
+        <v>122916997</v>
       </c>
       <c r="B22" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524154</v>
+        <v>524142</v>
       </c>
       <c r="R22" t="n">
         <v>6713729</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3466,10 +3466,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122915863</v>
+        <v>122917069</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
+        <v>98365</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3478,43 +3478,57 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524025</v>
+        <v>524154</v>
       </c>
       <c r="R23" t="n">
-        <v>6713544</v>
+        <v>6713729</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3546,7 +3560,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3556,7 +3570,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3583,10 +3602,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122916997</v>
+        <v>122915863</v>
       </c>
       <c r="B24" t="n">
-        <v>98357</v>
+        <v>8441</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3595,57 +3614,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524142</v>
+        <v>524025</v>
       </c>
       <c r="R24" t="n">
-        <v>6713729</v>
+        <v>6713544</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3677,7 +3682,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3687,12 +3692,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3719,10 +3719,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122959354</v>
+        <v>122959503</v>
       </c>
       <c r="B25" t="n">
-        <v>8441</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3731,31 +3731,40 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3764,10 +3773,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524122</v>
+        <v>524145</v>
       </c>
       <c r="R25" t="n">
-        <v>6713710</v>
+        <v>6713672</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3799,7 +3808,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3809,7 +3818,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3836,10 +3845,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122958064</v>
+        <v>122958484</v>
       </c>
       <c r="B26" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3871,12 +3880,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3895,10 +3904,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524144</v>
+        <v>524142</v>
       </c>
       <c r="R26" t="n">
-        <v>6713722</v>
+        <v>6713723</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3930,7 +3939,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3940,12 +3949,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3972,10 +3976,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122957710</v>
+        <v>122958244</v>
       </c>
       <c r="B27" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4020,16 +4024,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524145</v>
+        <v>524143</v>
       </c>
       <c r="R27" t="n">
-        <v>6713733</v>
+        <v>6713721</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4061,7 +4070,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4071,12 +4080,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Under klena granar.</t>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4103,10 +4112,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122959503</v>
+        <v>122957710</v>
       </c>
       <c r="B28" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4138,12 +4147,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4160,7 +4169,7 @@
         <v>524145</v>
       </c>
       <c r="R28" t="n">
-        <v>6713672</v>
+        <v>6713733</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4192,7 +4201,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4202,7 +4211,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4229,10 +4243,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122961337</v>
+        <v>122958631</v>
       </c>
       <c r="B29" t="n">
-        <v>90944</v>
+        <v>98365</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4241,41 +4255,57 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524040</v>
+        <v>524136</v>
       </c>
       <c r="R29" t="n">
-        <v>6713957</v>
+        <v>6713723</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4307,7 +4337,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4317,7 +4347,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4326,7 +4361,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4345,10 +4379,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122958842</v>
+        <v>122961337</v>
       </c>
       <c r="B30" t="n">
-        <v>57848</v>
+        <v>90952</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4357,50 +4391,44 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524149</v>
+        <v>524040</v>
       </c>
       <c r="R30" t="n">
-        <v>6713704</v>
+        <v>6713957</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4429,7 +4457,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4439,7 +4467,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4448,6 +4476,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4466,10 +4495,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122958484</v>
+        <v>122959354</v>
       </c>
       <c r="B31" t="n">
-        <v>98357</v>
+        <v>8441</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4478,45 +4507,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4525,10 +4540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524142</v>
+        <v>524122</v>
       </c>
       <c r="R31" t="n">
-        <v>6713723</v>
+        <v>6713710</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4560,7 +4575,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4570,7 +4585,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4597,10 +4612,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122959453</v>
+        <v>122958842</v>
       </c>
       <c r="B32" t="n">
-        <v>8441</v>
+        <v>57848</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4613,42 +4628,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524128</v>
+        <v>524149</v>
       </c>
       <c r="R32" t="n">
-        <v>6713669</v>
+        <v>6713704</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4677,7 +4696,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4687,7 +4706,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4714,10 +4733,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122958631</v>
+        <v>122958064</v>
       </c>
       <c r="B33" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4749,12 +4768,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4773,10 +4792,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524136</v>
+        <v>524144</v>
       </c>
       <c r="R33" t="n">
-        <v>6713723</v>
+        <v>6713722</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4808,7 +4827,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4818,12 +4837,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4850,10 +4869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122958244</v>
+        <v>122959453</v>
       </c>
       <c r="B34" t="n">
-        <v>98357</v>
+        <v>8441</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4862,45 +4881,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4909,10 +4914,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524143</v>
+        <v>524128</v>
       </c>
       <c r="R34" t="n">
-        <v>6713721</v>
+        <v>6713669</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4944,7 +4949,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4954,12 +4959,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4989,7 +4989,7 @@
         <v>122958550</v>
       </c>
       <c r="B35" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -2522,7 +2522,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122821198</v>
+        <v>122821745</v>
       </c>
       <c r="B16" t="n">
         <v>98365</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2570,7 +2570,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2582,10 +2581,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524049</v>
+        <v>524080</v>
       </c>
       <c r="R16" t="n">
-        <v>6714097</v>
+        <v>6714074</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2597,7 +2596,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2617,7 +2616,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2627,12 +2626,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2641,7 +2635,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2660,7 +2653,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122821745</v>
+        <v>122821824</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2700,7 +2693,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2719,10 +2712,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524080</v>
+        <v>524055</v>
       </c>
       <c r="R17" t="n">
-        <v>6714074</v>
+        <v>6714048</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2754,7 +2747,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2764,7 +2757,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2791,7 +2784,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821104</v>
+        <v>122821729</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2826,12 +2819,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2850,10 +2843,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524057</v>
+        <v>524077</v>
       </c>
       <c r="R18" t="n">
-        <v>6714094</v>
+        <v>6714076</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2885,7 +2878,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2895,12 +2888,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2927,7 +2920,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122817980</v>
+        <v>122821104</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2962,12 +2955,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2982,14 +2975,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524038</v>
+        <v>524057</v>
       </c>
       <c r="R19" t="n">
-        <v>6713288</v>
+        <v>6714094</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3021,7 +3014,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3031,12 +3024,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>10-15 bladrosetter under klen senvuxen gran.</t>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3063,7 +3056,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122821824</v>
+        <v>122821198</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -3111,6 +3104,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3122,10 +3116,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524055</v>
+        <v>524049</v>
       </c>
       <c r="R20" t="n">
-        <v>6714048</v>
+        <v>6714097</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3137,7 +3131,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -3157,7 +3151,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3167,7 +3161,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3176,6 +3175,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122821729</v>
+        <v>122817980</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3249,14 +3249,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524077</v>
+        <v>524038</v>
       </c>
       <c r="R21" t="n">
-        <v>6714076</v>
+        <v>6713288</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>10-15 bladrosetter under klen senvuxen gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122916997</v>
+        <v>122915863</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>8441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3342,57 +3342,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524142</v>
+        <v>524025</v>
       </c>
       <c r="R22" t="n">
-        <v>6713729</v>
+        <v>6713544</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3424,7 +3410,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3434,12 +3420,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3602,10 +3583,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122915863</v>
+        <v>122916997</v>
       </c>
       <c r="B24" t="n">
-        <v>8441</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3614,43 +3595,57 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524025</v>
+        <v>524142</v>
       </c>
       <c r="R24" t="n">
-        <v>6713544</v>
+        <v>6713729</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3682,7 +3677,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3692,7 +3687,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3719,7 +3719,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122959503</v>
+        <v>122958631</v>
       </c>
       <c r="B25" t="n">
         <v>98365</v>
@@ -3754,12 +3754,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3767,16 +3767,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524145</v>
+        <v>524136</v>
       </c>
       <c r="R25" t="n">
-        <v>6713672</v>
+        <v>6713723</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3808,7 +3813,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3818,7 +3823,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3976,10 +3986,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122958244</v>
+        <v>122961337</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3988,57 +3998,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524143</v>
+        <v>524040</v>
       </c>
       <c r="R27" t="n">
-        <v>6713721</v>
+        <v>6713957</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4070,7 +4064,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4080,12 +4074,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4094,6 +4083,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4243,10 +4233,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122958631</v>
+        <v>122959453</v>
       </c>
       <c r="B29" t="n">
-        <v>98365</v>
+        <v>8441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4255,45 +4245,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4302,10 +4278,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524136</v>
+        <v>524128</v>
       </c>
       <c r="R29" t="n">
-        <v>6713723</v>
+        <v>6713669</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4337,7 +4313,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4347,12 +4323,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4379,10 +4350,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122961337</v>
+        <v>122958064</v>
       </c>
       <c r="B30" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4391,41 +4362,57 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524040</v>
+        <v>524144</v>
       </c>
       <c r="R30" t="n">
-        <v>6713957</v>
+        <v>6713722</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4457,7 +4444,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4467,7 +4454,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4476,7 +4468,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4612,10 +4603,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122958842</v>
+        <v>122958550</v>
       </c>
       <c r="B32" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4624,25 +4615,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4650,24 +4641,34 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524149</v>
+        <v>524147</v>
       </c>
       <c r="R32" t="n">
-        <v>6713704</v>
+        <v>6713728</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4696,7 +4697,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4706,7 +4707,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4733,7 +4739,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122958064</v>
+        <v>122959503</v>
       </c>
       <c r="B33" t="n">
         <v>98365</v>
@@ -4773,7 +4779,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4781,21 +4787,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524144</v>
+        <v>524145</v>
       </c>
       <c r="R33" t="n">
-        <v>6713722</v>
+        <v>6713672</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4827,7 +4828,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4837,12 +4838,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4869,10 +4865,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122959453</v>
+        <v>122958842</v>
       </c>
       <c r="B34" t="n">
-        <v>8441</v>
+        <v>57848</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4885,42 +4881,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524128</v>
+        <v>524149</v>
       </c>
       <c r="R34" t="n">
-        <v>6713669</v>
+        <v>6713704</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4986,7 +4986,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122958550</v>
+        <v>122958244</v>
       </c>
       <c r="B35" t="n">
         <v>98365</v>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524147</v>
+        <v>524143</v>
       </c>
       <c r="R35" t="n">
-        <v>6713728</v>
+        <v>6713721</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -3719,10 +3719,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122958631</v>
+        <v>122961337</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3731,57 +3731,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524136</v>
+        <v>524040</v>
       </c>
       <c r="R25" t="n">
-        <v>6713723</v>
+        <v>6713957</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3813,7 +3797,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3823,12 +3807,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3837,6 +3816,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3855,7 +3835,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122958484</v>
+        <v>122958631</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3890,7 +3870,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3914,7 +3894,7 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524142</v>
+        <v>524136</v>
       </c>
       <c r="R26" t="n">
         <v>6713723</v>
@@ -3949,7 +3929,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3959,7 +3939,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3986,10 +3971,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122961337</v>
+        <v>122958484</v>
       </c>
       <c r="B27" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3998,41 +3983,57 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524040</v>
+        <v>524142</v>
       </c>
       <c r="R27" t="n">
-        <v>6713957</v>
+        <v>6713723</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4064,7 +4065,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4074,7 +4075,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4083,7 +4084,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -2653,7 +2653,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122821824</v>
+        <v>122821104</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524055</v>
+        <v>524057</v>
       </c>
       <c r="R17" t="n">
-        <v>6714048</v>
+        <v>6714094</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2757,7 +2757,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2784,7 +2789,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821729</v>
+        <v>122821824</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2819,12 +2824,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2843,10 +2848,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524077</v>
+        <v>524055</v>
       </c>
       <c r="R18" t="n">
-        <v>6714076</v>
+        <v>6714048</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2878,7 +2883,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2888,12 +2893,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2920,7 +2920,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122821104</v>
+        <v>122821729</v>
       </c>
       <c r="B19" t="n">
         <v>98365</v>
@@ -2955,12 +2955,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524057</v>
+        <v>524077</v>
       </c>
       <c r="R19" t="n">
-        <v>6714094</v>
+        <v>6714076</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3056,7 +3056,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122821198</v>
+        <v>122817980</v>
       </c>
       <c r="B20" t="n">
         <v>98365</v>
@@ -3104,7 +3104,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3112,14 +3111,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524049</v>
+        <v>524038</v>
       </c>
       <c r="R20" t="n">
-        <v>6714097</v>
+        <v>6713288</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3131,7 +3130,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -3151,7 +3150,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3161,12 +3160,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>10-15 bladrosetter under klen senvuxen gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3175,7 +3174,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3194,7 +3192,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122817980</v>
+        <v>122821198</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -3242,6 +3240,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3249,14 +3248,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524038</v>
+        <v>524049</v>
       </c>
       <c r="R21" t="n">
-        <v>6713288</v>
+        <v>6714097</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3268,7 +3267,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -3288,7 +3287,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3298,12 +3297,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>10-15 bladrosetter under klen senvuxen gran.</t>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3312,6 +3311,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122915863</v>
+        <v>122916997</v>
       </c>
       <c r="B22" t="n">
-        <v>8441</v>
+        <v>98365</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3342,43 +3342,57 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524025</v>
+        <v>524142</v>
       </c>
       <c r="R22" t="n">
-        <v>6713544</v>
+        <v>6713729</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3410,7 +3424,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3420,7 +3434,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3583,10 +3602,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122916997</v>
+        <v>122915863</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>8441</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3595,57 +3614,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524142</v>
+        <v>524025</v>
       </c>
       <c r="R24" t="n">
-        <v>6713729</v>
+        <v>6713544</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3677,7 +3682,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3687,12 +3692,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3719,10 +3719,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122961337</v>
+        <v>122958484</v>
       </c>
       <c r="B25" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3731,41 +3731,57 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524040</v>
+        <v>524142</v>
       </c>
       <c r="R25" t="n">
-        <v>6713957</v>
+        <v>6713723</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3797,7 +3813,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3807,7 +3823,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3816,7 +3832,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3835,7 +3850,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122958631</v>
+        <v>122958550</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3870,7 +3885,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3894,10 +3909,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524136</v>
+        <v>524147</v>
       </c>
       <c r="R26" t="n">
-        <v>6713723</v>
+        <v>6713728</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3929,7 +3944,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3939,12 +3954,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3971,10 +3986,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122958484</v>
+        <v>122959354</v>
       </c>
       <c r="B27" t="n">
-        <v>98365</v>
+        <v>8441</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3983,45 +3998,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4030,10 +4031,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524142</v>
+        <v>524122</v>
       </c>
       <c r="R27" t="n">
-        <v>6713723</v>
+        <v>6713710</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4065,7 +4066,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4075,7 +4076,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4102,7 +4103,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122957710</v>
+        <v>122958064</v>
       </c>
       <c r="B28" t="n">
         <v>98365</v>
@@ -4137,12 +4138,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4150,16 +4151,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524145</v>
+        <v>524144</v>
       </c>
       <c r="R28" t="n">
-        <v>6713733</v>
+        <v>6713722</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4191,7 +4197,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4201,12 +4207,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Under klena granar.</t>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4233,10 +4239,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122959453</v>
+        <v>122958842</v>
       </c>
       <c r="B29" t="n">
-        <v>8441</v>
+        <v>57848</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4249,42 +4255,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524128</v>
+        <v>524149</v>
       </c>
       <c r="R29" t="n">
-        <v>6713669</v>
+        <v>6713704</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4313,7 +4323,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4323,7 +4333,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4350,10 +4360,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122958064</v>
+        <v>122959453</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>8441</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4362,45 +4372,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4409,10 +4405,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524144</v>
+        <v>524128</v>
       </c>
       <c r="R30" t="n">
-        <v>6713722</v>
+        <v>6713669</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4444,7 +4440,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4454,12 +4450,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4486,10 +4477,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122959354</v>
+        <v>122959503</v>
       </c>
       <c r="B31" t="n">
-        <v>8441</v>
+        <v>98365</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4498,31 +4489,40 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4531,10 +4531,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524122</v>
+        <v>524145</v>
       </c>
       <c r="R31" t="n">
-        <v>6713710</v>
+        <v>6713672</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4603,7 +4603,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122958550</v>
+        <v>122958244</v>
       </c>
       <c r="B32" t="n">
         <v>98365</v>
@@ -4638,7 +4638,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524147</v>
+        <v>524143</v>
       </c>
       <c r="R32" t="n">
-        <v>6713728</v>
+        <v>6713721</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4707,12 +4707,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4739,10 +4739,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122959503</v>
+        <v>122961337</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4751,52 +4751,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524145</v>
+        <v>524040</v>
       </c>
       <c r="R33" t="n">
-        <v>6713672</v>
+        <v>6713957</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4828,7 +4817,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4838,7 +4827,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4847,6 +4836,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4865,10 +4855,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122958842</v>
+        <v>122957710</v>
       </c>
       <c r="B34" t="n">
-        <v>57848</v>
+        <v>98365</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4877,50 +4867,55 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524149</v>
+        <v>524145</v>
       </c>
       <c r="R34" t="n">
-        <v>6713704</v>
+        <v>6713733</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4949,7 +4944,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4959,7 +4954,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4986,7 +4986,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122958244</v>
+        <v>122958631</v>
       </c>
       <c r="B35" t="n">
         <v>98365</v>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524143</v>
+        <v>524136</v>
       </c>
       <c r="R35" t="n">
-        <v>6713721</v>
+        <v>6713723</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -2653,7 +2653,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122821104</v>
+        <v>122821198</v>
       </c>
       <c r="B17" t="n">
         <v>98365</v>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2701,6 +2701,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2712,10 +2713,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524057</v>
+        <v>524049</v>
       </c>
       <c r="R17" t="n">
-        <v>6714094</v>
+        <v>6714097</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2727,7 +2728,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2762,7 +2763,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2771,6 +2772,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2789,7 +2791,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821824</v>
+        <v>122821104</v>
       </c>
       <c r="B18" t="n">
         <v>98365</v>
@@ -2824,12 +2826,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2848,10 +2850,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524055</v>
+        <v>524057</v>
       </c>
       <c r="R18" t="n">
-        <v>6714048</v>
+        <v>6714094</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2883,7 +2885,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2893,7 +2895,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3192,7 +3199,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122821198</v>
+        <v>122821824</v>
       </c>
       <c r="B21" t="n">
         <v>98365</v>
@@ -3240,7 +3247,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3252,10 +3258,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524049</v>
+        <v>524055</v>
       </c>
       <c r="R21" t="n">
-        <v>6714097</v>
+        <v>6714048</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3267,7 +3273,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -3287,7 +3293,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3297,12 +3303,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3311,7 +3312,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3466,10 +3466,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122917069</v>
+        <v>122915863</v>
       </c>
       <c r="B23" t="n">
-        <v>98365</v>
+        <v>8441</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3478,57 +3478,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524154</v>
+        <v>524025</v>
       </c>
       <c r="R23" t="n">
-        <v>6713729</v>
+        <v>6713544</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3560,7 +3546,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3570,12 +3556,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:36</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3602,10 +3583,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122915863</v>
+        <v>122917069</v>
       </c>
       <c r="B24" t="n">
-        <v>8441</v>
+        <v>98365</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3614,43 +3595,57 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524025</v>
+        <v>524154</v>
       </c>
       <c r="R24" t="n">
-        <v>6713544</v>
+        <v>6713729</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3682,7 +3677,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3692,7 +3687,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3719,10 +3719,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122958484</v>
+        <v>122961337</v>
       </c>
       <c r="B25" t="n">
-        <v>98365</v>
+        <v>90952</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3731,57 +3731,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524142</v>
+        <v>524040</v>
       </c>
       <c r="R25" t="n">
-        <v>6713723</v>
+        <v>6713957</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3813,7 +3797,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3823,7 +3807,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3832,6 +3816,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3850,7 +3835,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122958550</v>
+        <v>122959503</v>
       </c>
       <c r="B26" t="n">
         <v>98365</v>
@@ -3890,7 +3875,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3898,21 +3883,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524147</v>
+        <v>524145</v>
       </c>
       <c r="R26" t="n">
-        <v>6713728</v>
+        <v>6713672</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3944,7 +3924,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3954,12 +3934,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3986,7 +3961,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122959354</v>
+        <v>122959453</v>
       </c>
       <c r="B27" t="n">
         <v>8441</v>
@@ -4031,10 +4006,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524122</v>
+        <v>524128</v>
       </c>
       <c r="R27" t="n">
-        <v>6713710</v>
+        <v>6713669</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4066,7 +4041,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4076,7 +4051,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4103,7 +4078,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122958064</v>
+        <v>122958550</v>
       </c>
       <c r="B28" t="n">
         <v>98365</v>
@@ -4143,7 +4118,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4162,10 +4137,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524144</v>
+        <v>524147</v>
       </c>
       <c r="R28" t="n">
-        <v>6713722</v>
+        <v>6713728</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4197,7 +4172,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4207,12 +4182,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4239,10 +4214,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122958842</v>
+        <v>122959354</v>
       </c>
       <c r="B29" t="n">
-        <v>57848</v>
+        <v>8441</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4255,46 +4230,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524149</v>
+        <v>524122</v>
       </c>
       <c r="R29" t="n">
-        <v>6713704</v>
+        <v>6713710</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4323,7 +4294,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4333,7 +4304,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4360,10 +4331,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122959453</v>
+        <v>122957710</v>
       </c>
       <c r="B30" t="n">
-        <v>8441</v>
+        <v>98365</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4372,31 +4343,40 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4405,10 +4385,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524128</v>
+        <v>524145</v>
       </c>
       <c r="R30" t="n">
-        <v>6713669</v>
+        <v>6713733</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4440,7 +4420,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4450,7 +4430,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4477,7 +4462,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122959503</v>
+        <v>122958244</v>
       </c>
       <c r="B31" t="n">
         <v>98365</v>
@@ -4512,12 +4497,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4525,16 +4510,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524145</v>
+        <v>524143</v>
       </c>
       <c r="R31" t="n">
-        <v>6713672</v>
+        <v>6713721</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4566,7 +4556,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4576,7 +4566,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4603,10 +4598,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122958244</v>
+        <v>122958842</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>57848</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4615,60 +4610,50 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524143</v>
+        <v>524149</v>
       </c>
       <c r="R32" t="n">
-        <v>6713721</v>
+        <v>6713704</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4697,7 +4682,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4707,12 +4692,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4739,10 +4719,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122961337</v>
+        <v>122958484</v>
       </c>
       <c r="B33" t="n">
-        <v>90952</v>
+        <v>98365</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4751,41 +4731,57 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524040</v>
+        <v>524142</v>
       </c>
       <c r="R33" t="n">
-        <v>6713957</v>
+        <v>6713723</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4817,7 +4813,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4827,7 +4823,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4836,7 +4832,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4855,7 +4850,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122957710</v>
+        <v>122958631</v>
       </c>
       <c r="B34" t="n">
         <v>98365</v>
@@ -4890,7 +4885,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4903,16 +4898,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524145</v>
+        <v>524136</v>
       </c>
       <c r="R34" t="n">
-        <v>6713733</v>
+        <v>6713723</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Under klena granar.</t>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4986,7 +4986,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122958631</v>
+        <v>122958064</v>
       </c>
       <c r="B35" t="n">
         <v>98365</v>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524136</v>
+        <v>524144</v>
       </c>
       <c r="R35" t="n">
-        <v>6713723</v>
+        <v>6713722</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD35" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5120,6 +5120,1541 @@
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>123412973</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>524116</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6713634</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>123413078</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>524102</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6713632</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>123412439</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>524137</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6713646</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123413856</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>524041</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6713443</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>18:24</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>123414352</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>524098</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6713405</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>18:43</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123414270</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>524085</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6713390</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>123412257</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>524123</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6713637</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>123412367</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>524136</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6713648</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123413119</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>524101</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6713638</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>123413726</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>524030</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6713469</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>18:19</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123413633</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>524031</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6713503</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123412326</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98368</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>524122</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6713640</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -2525,7 +2525,7 @@
         <v>122821745</v>
       </c>
       <c r="B16" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2653,10 +2653,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122821198</v>
+        <v>122817980</v>
       </c>
       <c r="B17" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2701,7 +2701,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2709,14 +2708,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524049</v>
+        <v>524038</v>
       </c>
       <c r="R17" t="n">
-        <v>6714097</v>
+        <v>6713288</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2728,7 +2727,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2748,7 +2747,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2758,12 +2757,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>10-15 bladrosetter under klen senvuxen gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2772,7 +2771,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2791,10 +2789,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821104</v>
+        <v>122821729</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2826,12 +2824,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2850,10 +2848,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524057</v>
+        <v>524077</v>
       </c>
       <c r="R18" t="n">
-        <v>6714094</v>
+        <v>6714076</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2885,7 +2883,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2895,12 +2893,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2927,10 +2925,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122821729</v>
+        <v>122821104</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2962,12 +2960,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2986,10 +2984,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524077</v>
+        <v>524057</v>
       </c>
       <c r="R19" t="n">
-        <v>6714076</v>
+        <v>6714094</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3021,7 +3019,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3031,12 +3029,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3063,10 +3061,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122817980</v>
+        <v>122821824</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3118,14 +3116,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524038</v>
+        <v>524055</v>
       </c>
       <c r="R20" t="n">
-        <v>6713288</v>
+        <v>6714048</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3157,7 +3155,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3167,12 +3165,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>10-15 bladrosetter under klen senvuxen gran.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3199,10 +3192,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122821824</v>
+        <v>122821198</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3247,6 +3240,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3258,10 +3252,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524055</v>
+        <v>524049</v>
       </c>
       <c r="R21" t="n">
-        <v>6714048</v>
+        <v>6714097</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3273,7 +3267,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -3293,7 +3287,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3303,7 +3297,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3312,6 +3311,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122916997</v>
+        <v>122917069</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524142</v>
+        <v>524154</v>
       </c>
       <c r="R22" t="n">
         <v>6713729</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3583,10 +3583,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122917069</v>
+        <v>122916997</v>
       </c>
       <c r="B24" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524154</v>
+        <v>524142</v>
       </c>
       <c r="R24" t="n">
         <v>6713729</v>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3687,12 +3687,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3719,10 +3719,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122961337</v>
+        <v>122958244</v>
       </c>
       <c r="B25" t="n">
-        <v>90952</v>
+        <v>98368</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3731,41 +3731,57 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524040</v>
+        <v>524143</v>
       </c>
       <c r="R25" t="n">
-        <v>6713957</v>
+        <v>6713721</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3797,7 +3813,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3807,7 +3823,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3816,7 +3837,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3835,10 +3855,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122959503</v>
+        <v>122958631</v>
       </c>
       <c r="B26" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3870,12 +3890,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3883,16 +3903,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524145</v>
+        <v>524136</v>
       </c>
       <c r="R26" t="n">
-        <v>6713672</v>
+        <v>6713723</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3924,7 +3949,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3934,7 +3959,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3961,10 +3991,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122959453</v>
+        <v>122961337</v>
       </c>
       <c r="B27" t="n">
-        <v>8441</v>
+        <v>90955</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3973,43 +4003,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524128</v>
+        <v>524040</v>
       </c>
       <c r="R27" t="n">
-        <v>6713669</v>
+        <v>6713957</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4041,7 +4069,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4051,7 +4079,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4060,6 +4088,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4078,10 +4107,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122958550</v>
+        <v>122957710</v>
       </c>
       <c r="B28" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4113,7 +4142,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -4126,21 +4155,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524147</v>
+        <v>524145</v>
       </c>
       <c r="R28" t="n">
-        <v>6713728</v>
+        <v>6713733</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4172,7 +4196,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4182,12 +4206,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4214,7 +4238,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122959354</v>
+        <v>122959453</v>
       </c>
       <c r="B29" t="n">
         <v>8441</v>
@@ -4259,10 +4283,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524122</v>
+        <v>524128</v>
       </c>
       <c r="R29" t="n">
-        <v>6713710</v>
+        <v>6713669</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4294,7 +4318,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4304,7 +4328,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4331,10 +4355,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122957710</v>
+        <v>122958842</v>
       </c>
       <c r="B30" t="n">
-        <v>98365</v>
+        <v>57851</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4343,55 +4367,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524145</v>
+        <v>524149</v>
       </c>
       <c r="R30" t="n">
-        <v>6713733</v>
+        <v>6713704</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4420,7 +4439,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4430,12 +4449,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Under klena granar.</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4462,10 +4476,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122958244</v>
+        <v>122958484</v>
       </c>
       <c r="B31" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4497,7 +4511,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4521,10 +4535,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524143</v>
+        <v>524142</v>
       </c>
       <c r="R31" t="n">
-        <v>6713721</v>
+        <v>6713723</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4556,7 +4570,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4566,12 +4580,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4598,10 +4607,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122958842</v>
+        <v>122959354</v>
       </c>
       <c r="B32" t="n">
-        <v>57848</v>
+        <v>8441</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4614,46 +4623,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524149</v>
+        <v>524122</v>
       </c>
       <c r="R32" t="n">
-        <v>6713704</v>
+        <v>6713710</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4682,7 +4687,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4692,7 +4697,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4719,10 +4724,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122958484</v>
+        <v>122959503</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4754,12 +4759,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4767,21 +4772,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524142</v>
+        <v>524145</v>
       </c>
       <c r="R33" t="n">
-        <v>6713723</v>
+        <v>6713672</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4850,10 +4850,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122958631</v>
+        <v>122958064</v>
       </c>
       <c r="B34" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4909,10 +4909,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524136</v>
+        <v>524144</v>
       </c>
       <c r="R34" t="n">
-        <v>6713723</v>
+        <v>6713722</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4986,10 +4986,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122958064</v>
+        <v>122958550</v>
       </c>
       <c r="B35" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524144</v>
+        <v>524147</v>
       </c>
       <c r="R35" t="n">
-        <v>6713722</v>
+        <v>6713728</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5122,7 +5122,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123412973</v>
+        <v>123412367</v>
       </c>
       <c r="B36" t="n">
         <v>98368</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5170,21 +5170,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524116</v>
+        <v>524136</v>
       </c>
       <c r="R36" t="n">
-        <v>6713634</v>
+        <v>6713648</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5216,7 +5211,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5226,7 +5221,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5253,10 +5248,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123413078</v>
+        <v>123413633</v>
       </c>
       <c r="B37" t="n">
-        <v>98368</v>
+        <v>57497</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5265,57 +5260,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524102</v>
+        <v>524031</v>
       </c>
       <c r="R37" t="n">
-        <v>6713632</v>
+        <v>6713503</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5347,7 +5328,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5357,7 +5338,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5384,7 +5365,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123412439</v>
+        <v>123413119</v>
       </c>
       <c r="B38" t="n">
         <v>98368</v>
@@ -5419,12 +5400,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5432,6 +5413,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5439,14 +5421,14 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524137</v>
+        <v>524101</v>
       </c>
       <c r="R38" t="n">
-        <v>6713646</v>
+        <v>6713638</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5478,7 +5460,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5488,12 +5470,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5502,6 +5484,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5520,7 +5503,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123413856</v>
+        <v>123412326</v>
       </c>
       <c r="B39" t="n">
         <v>98368</v>
@@ -5555,7 +5538,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5574,10 +5557,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524041</v>
+        <v>524122</v>
       </c>
       <c r="R39" t="n">
-        <v>6713443</v>
+        <v>6713640</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5609,7 +5592,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5619,7 +5602,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5646,7 +5629,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123414352</v>
+        <v>123413726</v>
       </c>
       <c r="B40" t="n">
         <v>98368</v>
@@ -5681,7 +5664,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5700,10 +5683,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524098</v>
+        <v>524030</v>
       </c>
       <c r="R40" t="n">
-        <v>6713405</v>
+        <v>6713469</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5735,7 +5718,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5745,7 +5728,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5772,7 +5755,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123414270</v>
+        <v>123412439</v>
       </c>
       <c r="B41" t="n">
         <v>98368</v>
@@ -5807,7 +5790,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5820,16 +5803,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524085</v>
+        <v>524137</v>
       </c>
       <c r="R41" t="n">
-        <v>6713390</v>
+        <v>6713646</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5861,7 +5849,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5871,7 +5859,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5898,7 +5891,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123412257</v>
+        <v>123414270</v>
       </c>
       <c r="B42" t="n">
         <v>98368</v>
@@ -5933,7 +5926,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5952,10 +5945,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524123</v>
+        <v>524085</v>
       </c>
       <c r="R42" t="n">
-        <v>6713637</v>
+        <v>6713390</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5987,7 +5980,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5997,7 +5990,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6024,7 +6017,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123412367</v>
+        <v>123412973</v>
       </c>
       <c r="B43" t="n">
         <v>98368</v>
@@ -6059,7 +6052,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6072,16 +6065,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524136</v>
+        <v>524116</v>
       </c>
       <c r="R43" t="n">
-        <v>6713648</v>
+        <v>6713634</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6113,7 +6111,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6123,7 +6121,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6150,7 +6148,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123413119</v>
+        <v>123413856</v>
       </c>
       <c r="B44" t="n">
         <v>98368</v>
@@ -6185,12 +6183,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -6198,22 +6196,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524101</v>
+        <v>524041</v>
       </c>
       <c r="R44" t="n">
-        <v>6713638</v>
+        <v>6713443</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6245,7 +6237,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6255,12 +6247,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6269,7 +6256,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6288,7 +6274,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123413726</v>
+        <v>123412257</v>
       </c>
       <c r="B45" t="n">
         <v>98368</v>
@@ -6323,7 +6309,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6342,10 +6328,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524030</v>
+        <v>524123</v>
       </c>
       <c r="R45" t="n">
-        <v>6713469</v>
+        <v>6713637</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6377,7 +6363,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6387,7 +6373,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6414,10 +6400,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123413633</v>
+        <v>123413078</v>
       </c>
       <c r="B46" t="n">
-        <v>57497</v>
+        <v>98368</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6426,43 +6412,57 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524031</v>
+        <v>524102</v>
       </c>
       <c r="R46" t="n">
-        <v>6713503</v>
+        <v>6713632</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6531,7 +6531,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123412326</v>
+        <v>123414352</v>
       </c>
       <c r="B47" t="n">
         <v>98368</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524122</v>
+        <v>524098</v>
       </c>
       <c r="R47" t="n">
-        <v>6713640</v>
+        <v>6713405</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -2522,10 +2522,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122821745</v>
+        <v>122821104</v>
       </c>
       <c r="B16" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>524080</v>
+        <v>524057</v>
       </c>
       <c r="R16" t="n">
-        <v>6714074</v>
+        <v>6714094</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2626,7 +2626,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2653,10 +2658,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122817980</v>
+        <v>122821198</v>
       </c>
       <c r="B17" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2701,6 +2706,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -2708,14 +2714,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>524038</v>
+        <v>524049</v>
       </c>
       <c r="R17" t="n">
-        <v>6713288</v>
+        <v>6714097</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2727,7 +2733,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Borlänge</t>
+          <t>Falun</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2747,7 +2753,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2757,12 +2763,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>10-15 bladrosetter under klen senvuxen gran.</t>
+          <t>Under klen gran. En överblommad.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2771,6 +2777,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2789,10 +2796,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821729</v>
+        <v>122821745</v>
       </c>
       <c r="B18" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2824,7 +2831,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2848,10 +2855,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524077</v>
+        <v>524080</v>
       </c>
       <c r="R18" t="n">
-        <v>6714076</v>
+        <v>6714074</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2883,7 +2890,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2893,12 +2900,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2925,10 +2927,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122821104</v>
+        <v>122821824</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2960,12 +2962,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2984,10 +2986,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524057</v>
+        <v>524055</v>
       </c>
       <c r="R19" t="n">
-        <v>6714094</v>
+        <v>6714048</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3019,7 +3021,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3029,12 +3031,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:13</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>En samling bladrosetter och några sporadiska runt om. Inom ca 1-2 kvm.</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3061,10 +3058,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122821824</v>
+        <v>122821729</v>
       </c>
       <c r="B20" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3096,12 +3093,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3120,10 +3117,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524055</v>
+        <v>524077</v>
       </c>
       <c r="R20" t="n">
-        <v>6714048</v>
+        <v>6714076</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3155,7 +3152,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3165,7 +3162,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3192,10 +3194,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122821198</v>
+        <v>122817980</v>
       </c>
       <c r="B21" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3240,7 +3242,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -3248,14 +3249,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524049</v>
+        <v>524038</v>
       </c>
       <c r="R21" t="n">
-        <v>6714097</v>
+        <v>6713288</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3267,7 +3268,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>Falun</t>
+          <t>Borlänge</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -3287,7 +3288,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3297,12 +3298,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Under klen gran. En överblommad.</t>
+          <t>10-15 bladrosetter under klen senvuxen gran.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3311,7 +3312,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122917069</v>
+        <v>122916997</v>
       </c>
       <c r="B22" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524154</v>
+        <v>524142</v>
       </c>
       <c r="R22" t="n">
         <v>6713729</v>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3466,10 +3466,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122915863</v>
+        <v>122917069</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
+        <v>98370</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3478,43 +3478,57 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>524025</v>
+        <v>524154</v>
       </c>
       <c r="R23" t="n">
-        <v>6713544</v>
+        <v>6713729</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3546,7 +3560,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3556,7 +3570,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3583,10 +3602,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122916997</v>
+        <v>122915863</v>
       </c>
       <c r="B24" t="n">
-        <v>98368</v>
+        <v>8441</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3595,57 +3614,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524142</v>
+        <v>524025</v>
       </c>
       <c r="R24" t="n">
-        <v>6713729</v>
+        <v>6713544</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3677,7 +3682,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3687,12 +3692,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3719,10 +3719,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122958244</v>
+        <v>122958484</v>
       </c>
       <c r="B25" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3778,10 +3778,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524143</v>
+        <v>524142</v>
       </c>
       <c r="R25" t="n">
-        <v>6713721</v>
+        <v>6713723</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3813,7 +3813,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3823,12 +3823,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3855,10 +3850,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122958631</v>
+        <v>122958550</v>
       </c>
       <c r="B26" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3890,7 +3885,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3914,10 +3909,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524136</v>
+        <v>524147</v>
       </c>
       <c r="R26" t="n">
-        <v>6713723</v>
+        <v>6713728</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3949,7 +3944,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3959,12 +3954,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3991,10 +3986,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122961337</v>
+        <v>122958244</v>
       </c>
       <c r="B27" t="n">
-        <v>90955</v>
+        <v>98370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4003,41 +3998,57 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524040</v>
+        <v>524143</v>
       </c>
       <c r="R27" t="n">
-        <v>6713957</v>
+        <v>6713721</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4069,7 +4080,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4079,7 +4090,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4088,7 +4104,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4107,10 +4122,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122957710</v>
+        <v>122959354</v>
       </c>
       <c r="B28" t="n">
-        <v>98368</v>
+        <v>8441</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4119,40 +4134,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4161,10 +4167,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524145</v>
+        <v>524122</v>
       </c>
       <c r="R28" t="n">
-        <v>6713733</v>
+        <v>6713710</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4196,7 +4202,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4206,12 +4212,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Under klena granar.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4355,10 +4356,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122958842</v>
+        <v>122961337</v>
       </c>
       <c r="B30" t="n">
-        <v>57851</v>
+        <v>90957</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4367,50 +4368,44 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524149</v>
+        <v>524040</v>
       </c>
       <c r="R30" t="n">
-        <v>6713704</v>
+        <v>6713957</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4439,7 +4434,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4449,7 +4444,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4458,6 +4453,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4476,10 +4472,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122958484</v>
+        <v>122959503</v>
       </c>
       <c r="B31" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4511,12 +4507,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4524,21 +4520,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524142</v>
+        <v>524145</v>
       </c>
       <c r="R31" t="n">
-        <v>6713723</v>
+        <v>6713672</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4570,7 +4561,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4580,7 +4571,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4607,10 +4598,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122959354</v>
+        <v>122958842</v>
       </c>
       <c r="B32" t="n">
-        <v>8441</v>
+        <v>57851</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4623,42 +4614,46 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524122</v>
+        <v>524149</v>
       </c>
       <c r="R32" t="n">
-        <v>6713710</v>
+        <v>6713704</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4687,7 +4682,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4697,7 +4692,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4724,10 +4719,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122959503</v>
+        <v>122958064</v>
       </c>
       <c r="B33" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4764,7 +4759,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4772,16 +4767,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524145</v>
+        <v>524144</v>
       </c>
       <c r="R33" t="n">
-        <v>6713672</v>
+        <v>6713722</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4823,7 +4823,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4850,10 +4855,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122958064</v>
+        <v>122957710</v>
       </c>
       <c r="B34" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4885,12 +4890,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4898,21 +4903,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524144</v>
+        <v>524145</v>
       </c>
       <c r="R34" t="n">
-        <v>6713722</v>
+        <v>6713733</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4986,10 +4986,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122958550</v>
+        <v>122958631</v>
       </c>
       <c r="B35" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524147</v>
+        <v>524136</v>
       </c>
       <c r="R35" t="n">
-        <v>6713728</v>
+        <v>6713723</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5125,7 +5125,7 @@
         <v>123412367</v>
       </c>
       <c r="B36" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5248,10 +5248,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123413633</v>
+        <v>123413726</v>
       </c>
       <c r="B37" t="n">
-        <v>57497</v>
+        <v>98370</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5260,43 +5260,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524031</v>
+        <v>524030</v>
       </c>
       <c r="R37" t="n">
-        <v>6713503</v>
+        <v>6713469</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5328,7 +5337,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5338,7 +5347,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5365,10 +5374,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123413119</v>
+        <v>123414352</v>
       </c>
       <c r="B38" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5400,12 +5409,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5413,22 +5422,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524101</v>
+        <v>524098</v>
       </c>
       <c r="R38" t="n">
-        <v>6713638</v>
+        <v>6713405</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5460,7 +5463,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5470,12 +5473,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5484,7 +5482,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5503,10 +5500,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123412326</v>
+        <v>123413119</v>
       </c>
       <c r="B39" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5543,7 +5540,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5551,16 +5548,22 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524122</v>
+        <v>524101</v>
       </c>
       <c r="R39" t="n">
-        <v>6713640</v>
+        <v>6713638</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5592,7 +5595,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5602,7 +5605,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5611,6 +5619,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5629,10 +5638,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123413726</v>
+        <v>123412973</v>
       </c>
       <c r="B40" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5664,7 +5673,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5677,16 +5686,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524030</v>
+        <v>524116</v>
       </c>
       <c r="R40" t="n">
-        <v>6713469</v>
+        <v>6713634</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5718,7 +5732,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5728,7 +5742,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5755,10 +5769,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123412439</v>
+        <v>123414270</v>
       </c>
       <c r="B41" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5790,7 +5804,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5803,21 +5817,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524137</v>
+        <v>524085</v>
       </c>
       <c r="R41" t="n">
-        <v>6713646</v>
+        <v>6713390</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5849,7 +5858,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5859,12 +5868,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5891,10 +5895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123414270</v>
+        <v>123412326</v>
       </c>
       <c r="B42" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5926,7 +5930,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5945,10 +5949,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524085</v>
+        <v>524122</v>
       </c>
       <c r="R42" t="n">
-        <v>6713390</v>
+        <v>6713640</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5980,7 +5984,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5990,7 +5994,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6017,10 +6021,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123412973</v>
+        <v>123413856</v>
       </c>
       <c r="B43" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6052,7 +6056,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6065,21 +6069,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524116</v>
+        <v>524041</v>
       </c>
       <c r="R43" t="n">
-        <v>6713634</v>
+        <v>6713443</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6111,7 +6110,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6121,7 +6120,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6148,10 +6147,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123413856</v>
+        <v>123413633</v>
       </c>
       <c r="B44" t="n">
-        <v>98368</v>
+        <v>57497</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6160,52 +6159,43 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524041</v>
+        <v>524031</v>
       </c>
       <c r="R44" t="n">
-        <v>6713443</v>
+        <v>6713503</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6237,7 +6227,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6247,7 +6237,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6274,10 +6264,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123412257</v>
+        <v>123413078</v>
       </c>
       <c r="B45" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6309,7 +6299,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6322,16 +6312,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524123</v>
+        <v>524102</v>
       </c>
       <c r="R45" t="n">
-        <v>6713637</v>
+        <v>6713632</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6363,7 +6358,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6373,7 +6368,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6400,10 +6395,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123413078</v>
+        <v>123412439</v>
       </c>
       <c r="B46" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6435,7 +6430,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6455,14 +6450,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524102</v>
+        <v>524137</v>
       </c>
       <c r="R46" t="n">
-        <v>6713632</v>
+        <v>6713646</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6494,7 +6489,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6504,7 +6499,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6531,10 +6531,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123414352</v>
+        <v>123412257</v>
       </c>
       <c r="B47" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524098</v>
+        <v>524123</v>
       </c>
       <c r="R47" t="n">
-        <v>6713405</v>
+        <v>6713637</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD47" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2525,7 +2525,7 @@
         <v>122821104</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>122821198</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2796,10 +2796,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122821745</v>
+        <v>122817980</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2851,14 +2851,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>524080</v>
+        <v>524038</v>
       </c>
       <c r="R18" t="n">
-        <v>6714074</v>
+        <v>6713288</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2900,7 +2900,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>10-15 bladrosetter under klen senvuxen gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2927,10 +2932,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122821824</v>
+        <v>122821729</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2962,12 +2967,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2986,10 +2991,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>524055</v>
+        <v>524077</v>
       </c>
       <c r="R19" t="n">
-        <v>6714048</v>
+        <v>6714076</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3021,7 +3026,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3031,7 +3036,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3058,10 +3068,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122821729</v>
+        <v>122821824</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3093,12 +3103,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3117,10 +3127,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>524077</v>
+        <v>524055</v>
       </c>
       <c r="R20" t="n">
-        <v>6714076</v>
+        <v>6714048</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3152,7 +3162,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3162,12 +3172,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:35</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3194,10 +3199,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122817980</v>
+        <v>122821745</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3234,7 +3239,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3249,14 +3254,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>524038</v>
+        <v>524080</v>
       </c>
       <c r="R21" t="n">
-        <v>6713288</v>
+        <v>6714074</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3288,7 +3293,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3298,12 +3303,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:58</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>10-15 bladrosetter under klen senvuxen gran.</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3330,10 +3330,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122916997</v>
+        <v>122915863</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>8441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3342,57 +3342,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>524142</v>
+        <v>524025</v>
       </c>
       <c r="R22" t="n">
-        <v>6713729</v>
+        <v>6713544</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3424,7 +3410,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3434,12 +3420,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:33</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3469,7 +3450,7 @@
         <v>122917069</v>
       </c>
       <c r="B23" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3602,10 +3583,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122915863</v>
+        <v>122916997</v>
       </c>
       <c r="B24" t="n">
-        <v>8441</v>
+        <v>98376</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3614,43 +3595,57 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>524025</v>
+        <v>524142</v>
       </c>
       <c r="R24" t="n">
-        <v>6713544</v>
+        <v>6713729</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3682,7 +3677,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3692,7 +3687,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>17:33</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Under klena granar intill två lite grövre gran/tall. Större antal bladrosetter, små och nån större.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3719,10 +3719,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122958484</v>
+        <v>122961337</v>
       </c>
       <c r="B25" t="n">
-        <v>98370</v>
+        <v>90963</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3731,57 +3731,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524142</v>
+        <v>524040</v>
       </c>
       <c r="R25" t="n">
-        <v>6713723</v>
+        <v>6713957</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3813,7 +3797,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3823,7 +3807,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3832,6 +3816,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3850,10 +3835,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122958550</v>
+        <v>122958842</v>
       </c>
       <c r="B26" t="n">
-        <v>98370</v>
+        <v>57851</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3862,25 +3847,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3888,34 +3873,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524147</v>
+        <v>524149</v>
       </c>
       <c r="R26" t="n">
-        <v>6713728</v>
+        <v>6713704</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3944,7 +3919,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3954,12 +3929,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3986,10 +3956,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122958244</v>
+        <v>122959354</v>
       </c>
       <c r="B27" t="n">
-        <v>98370</v>
+        <v>8441</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3998,45 +3968,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4045,10 +4001,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524143</v>
+        <v>524122</v>
       </c>
       <c r="R27" t="n">
-        <v>6713721</v>
+        <v>6713710</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4080,7 +4036,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4090,12 +4046,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4122,10 +4073,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122959354</v>
+        <v>122958244</v>
       </c>
       <c r="B28" t="n">
-        <v>8441</v>
+        <v>98376</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4134,31 +4085,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4167,10 +4132,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524122</v>
+        <v>524143</v>
       </c>
       <c r="R28" t="n">
-        <v>6713710</v>
+        <v>6713721</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4202,7 +4167,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4212,7 +4177,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4239,10 +4209,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122959453</v>
+        <v>122958550</v>
       </c>
       <c r="B29" t="n">
-        <v>8441</v>
+        <v>98376</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4251,31 +4221,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4284,10 +4268,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524128</v>
+        <v>524147</v>
       </c>
       <c r="R29" t="n">
-        <v>6713669</v>
+        <v>6713728</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4319,7 +4303,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4329,7 +4313,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4356,10 +4345,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122961337</v>
+        <v>122957710</v>
       </c>
       <c r="B30" t="n">
-        <v>90957</v>
+        <v>98376</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4368,41 +4357,52 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524040</v>
+        <v>524145</v>
       </c>
       <c r="R30" t="n">
-        <v>6713957</v>
+        <v>6713733</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4444,7 +4444,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4453,7 +4458,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4472,10 +4476,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122959503</v>
+        <v>122959453</v>
       </c>
       <c r="B31" t="n">
-        <v>98370</v>
+        <v>8441</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4484,40 +4488,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4526,10 +4521,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524145</v>
+        <v>524128</v>
       </c>
       <c r="R31" t="n">
-        <v>6713672</v>
+        <v>6713669</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4561,7 +4556,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4571,7 +4566,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4598,10 +4593,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122958842</v>
+        <v>122959503</v>
       </c>
       <c r="B32" t="n">
-        <v>57851</v>
+        <v>98376</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4610,25 +4605,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4636,24 +4631,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524149</v>
+        <v>524145</v>
       </c>
       <c r="R32" t="n">
-        <v>6713704</v>
+        <v>6713672</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4719,10 +4719,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122958064</v>
+        <v>122958484</v>
       </c>
       <c r="B33" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4754,12 +4754,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524144</v>
+        <v>524142</v>
       </c>
       <c r="R33" t="n">
-        <v>6713722</v>
+        <v>6713723</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4823,12 +4823,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4855,10 +4850,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122957710</v>
+        <v>122958631</v>
       </c>
       <c r="B34" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4890,7 +4885,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4903,16 +4898,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524145</v>
+        <v>524136</v>
       </c>
       <c r="R34" t="n">
-        <v>6713733</v>
+        <v>6713723</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Under klena granar.</t>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4986,10 +4986,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122958631</v>
+        <v>122958064</v>
       </c>
       <c r="B35" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5021,12 +5021,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5045,10 +5045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524136</v>
+        <v>524144</v>
       </c>
       <c r="R35" t="n">
-        <v>6713723</v>
+        <v>6713722</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5122,10 +5122,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123412367</v>
+        <v>123413726</v>
       </c>
       <c r="B36" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5172,14 +5172,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524136</v>
+        <v>524030</v>
       </c>
       <c r="R36" t="n">
-        <v>6713648</v>
+        <v>6713469</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5248,10 +5248,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123413726</v>
+        <v>123412973</v>
       </c>
       <c r="B37" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5296,16 +5296,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524030</v>
+        <v>524116</v>
       </c>
       <c r="R37" t="n">
-        <v>6713469</v>
+        <v>6713634</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5337,7 +5342,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5347,7 +5352,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5374,10 +5379,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123414352</v>
+        <v>123413078</v>
       </c>
       <c r="B38" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5409,7 +5414,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5422,16 +5427,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524098</v>
+        <v>524102</v>
       </c>
       <c r="R38" t="n">
-        <v>6713405</v>
+        <v>6713632</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5463,7 +5473,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5473,7 +5483,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5500,10 +5510,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123413119</v>
+        <v>123412326</v>
       </c>
       <c r="B39" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5540,7 +5550,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5548,22 +5558,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524101</v>
+        <v>524122</v>
       </c>
       <c r="R39" t="n">
-        <v>6713638</v>
+        <v>6713640</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5595,7 +5599,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5605,12 +5609,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5619,7 +5618,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5638,10 +5636,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123412973</v>
+        <v>123414270</v>
       </c>
       <c r="B40" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5673,7 +5671,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5686,21 +5684,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524116</v>
+        <v>524085</v>
       </c>
       <c r="R40" t="n">
-        <v>6713634</v>
+        <v>6713390</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5732,7 +5725,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5742,7 +5735,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5769,10 +5762,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123414270</v>
+        <v>123413633</v>
       </c>
       <c r="B41" t="n">
-        <v>98370</v>
+        <v>57497</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5781,52 +5774,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524085</v>
+        <v>524031</v>
       </c>
       <c r="R41" t="n">
-        <v>6713390</v>
+        <v>6713503</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5858,7 +5842,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5868,7 +5852,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5895,10 +5879,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123412326</v>
+        <v>123412257</v>
       </c>
       <c r="B42" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5930,7 +5914,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5949,10 +5933,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524122</v>
+        <v>524123</v>
       </c>
       <c r="R42" t="n">
-        <v>6713640</v>
+        <v>6713637</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5984,7 +5968,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5994,7 +5978,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6021,10 +6005,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123413856</v>
+        <v>123412367</v>
       </c>
       <c r="B43" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6056,7 +6040,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6071,14 +6055,14 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524041</v>
+        <v>524136</v>
       </c>
       <c r="R43" t="n">
-        <v>6713443</v>
+        <v>6713648</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6110,7 +6094,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6120,7 +6104,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6147,10 +6131,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123413633</v>
+        <v>123413119</v>
       </c>
       <c r="B44" t="n">
-        <v>57497</v>
+        <v>98376</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6159,43 +6143,58 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524031</v>
+        <v>524101</v>
       </c>
       <c r="R44" t="n">
-        <v>6713503</v>
+        <v>6713638</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6227,7 +6226,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6237,7 +6236,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6246,6 +6250,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -6264,10 +6269,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123413078</v>
+        <v>123413856</v>
       </c>
       <c r="B45" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6299,7 +6304,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6312,21 +6317,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524102</v>
+        <v>524041</v>
       </c>
       <c r="R45" t="n">
-        <v>6713632</v>
+        <v>6713443</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6395,10 +6395,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123412439</v>
+        <v>123414352</v>
       </c>
       <c r="B46" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6443,21 +6443,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524137</v>
+        <v>524098</v>
       </c>
       <c r="R46" t="n">
-        <v>6713646</v>
+        <v>6713405</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6489,7 +6484,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6499,12 +6494,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6531,10 +6521,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123412257</v>
+        <v>123412439</v>
       </c>
       <c r="B47" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6566,7 +6556,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6579,16 +6569,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524123</v>
+        <v>524137</v>
       </c>
       <c r="R47" t="n">
-        <v>6713637</v>
+        <v>6713646</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6620,7 +6615,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6630,7 +6625,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6654,6 +6654,514 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123528562</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>524033</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6713503</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>123526470</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>524101</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6713880</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>123528345</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>524025</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6713476</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>123527655</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98379</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>524041</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6713460</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-03-27</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>18:05</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -3836,10 +3836,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122958842</v>
+        <v>122958484</v>
       </c>
       <c r="B26" t="n">
-        <v>57851</v>
+        <v>98379</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3848,50 +3848,60 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524149</v>
+        <v>524142</v>
       </c>
       <c r="R26" t="n">
-        <v>6713704</v>
+        <v>6713723</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3920,7 +3930,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3930,7 +3940,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3957,10 +3967,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122958484</v>
+        <v>122958842</v>
       </c>
       <c r="B27" t="n">
-        <v>98379</v>
+        <v>57851</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3969,60 +3979,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524142</v>
+        <v>524149</v>
       </c>
       <c r="R27" t="n">
-        <v>6713723</v>
+        <v>6713704</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4224,10 +4224,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122959354</v>
+        <v>122957710</v>
       </c>
       <c r="B29" t="n">
-        <v>8441</v>
+        <v>98379</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4236,31 +4236,40 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4269,10 +4278,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524122</v>
+        <v>524145</v>
       </c>
       <c r="R29" t="n">
-        <v>6713710</v>
+        <v>6713733</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4304,7 +4313,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4314,7 +4323,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4341,7 +4355,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122957710</v>
+        <v>122958550</v>
       </c>
       <c r="B30" t="n">
         <v>98379</v>
@@ -4376,7 +4390,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4389,16 +4403,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524145</v>
+        <v>524147</v>
       </c>
       <c r="R30" t="n">
-        <v>6713733</v>
+        <v>6713728</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4430,7 +4449,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4440,12 +4459,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Under klena granar.</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4472,10 +4491,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122958550</v>
+        <v>122959354</v>
       </c>
       <c r="B31" t="n">
-        <v>98379</v>
+        <v>8441</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4484,45 +4503,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4531,10 +4536,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524147</v>
+        <v>524122</v>
       </c>
       <c r="R31" t="n">
-        <v>6713728</v>
+        <v>6713710</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4566,7 +4571,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4576,12 +4581,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -8139,10 +8139,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123569808</v>
+        <v>123572491</v>
       </c>
       <c r="B60" t="n">
-        <v>97333</v>
+        <v>90966</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8151,43 +8151,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524077</v>
+        <v>523993</v>
       </c>
       <c r="R60" t="n">
-        <v>6713436</v>
+        <v>6713281</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8219,7 +8214,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8229,7 +8224,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8256,10 +8251,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123572491</v>
+        <v>123569808</v>
       </c>
       <c r="B61" t="n">
-        <v>90966</v>
+        <v>97333</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8268,38 +8263,43 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523993</v>
+        <v>524077</v>
       </c>
       <c r="R61" t="n">
-        <v>6713281</v>
+        <v>6713436</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3333,7 +3333,7 @@
         <v>122916997</v>
       </c>
       <c r="B22" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3469,7 +3469,7 @@
         <v>122915863</v>
       </c>
       <c r="B23" t="n">
-        <v>8441</v>
+        <v>8445</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3586,7 +3586,7 @@
         <v>122917069</v>
       </c>
       <c r="B24" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3719,10 +3719,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122959453</v>
+        <v>122957710</v>
       </c>
       <c r="B25" t="n">
-        <v>8441</v>
+        <v>98396</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3731,31 +3731,40 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3764,10 +3773,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524128</v>
+        <v>524145</v>
       </c>
       <c r="R25" t="n">
-        <v>6713669</v>
+        <v>6713733</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3799,7 +3808,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3809,7 +3818,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3836,10 +3850,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122958484</v>
+        <v>122958842</v>
       </c>
       <c r="B26" t="n">
-        <v>98379</v>
+        <v>57857</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3848,60 +3862,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524142</v>
+        <v>524149</v>
       </c>
       <c r="R26" t="n">
-        <v>6713723</v>
+        <v>6713704</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3930,7 +3934,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3940,7 +3944,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3967,10 +3971,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122958842</v>
+        <v>122961337</v>
       </c>
       <c r="B27" t="n">
-        <v>57851</v>
+        <v>90983</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3979,50 +3983,44 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>524149</v>
+        <v>524040</v>
       </c>
       <c r="R27" t="n">
-        <v>6713704</v>
+        <v>6713957</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -4051,7 +4049,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -4061,7 +4059,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4070,6 +4068,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4088,10 +4087,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122958064</v>
+        <v>122959453</v>
       </c>
       <c r="B28" t="n">
-        <v>98379</v>
+        <v>8445</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4100,45 +4099,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4147,10 +4132,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>524144</v>
+        <v>524128</v>
       </c>
       <c r="R28" t="n">
-        <v>6713722</v>
+        <v>6713669</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4182,7 +4167,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4192,12 +4177,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4224,10 +4204,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122957710</v>
+        <v>122958484</v>
       </c>
       <c r="B29" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4259,7 +4239,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4272,16 +4252,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>524145</v>
+        <v>524142</v>
       </c>
       <c r="R29" t="n">
-        <v>6713733</v>
+        <v>6713723</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4313,7 +4298,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4323,12 +4308,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Under klena granar.</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4355,10 +4335,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122958550</v>
+        <v>122959503</v>
       </c>
       <c r="B30" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4395,7 +4375,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4403,21 +4383,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>524147</v>
+        <v>524145</v>
       </c>
       <c r="R30" t="n">
-        <v>6713728</v>
+        <v>6713672</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4449,7 +4424,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4459,12 +4434,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4491,10 +4461,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122959354</v>
+        <v>122958631</v>
       </c>
       <c r="B31" t="n">
-        <v>8441</v>
+        <v>98396</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4503,31 +4473,45 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4536,10 +4520,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>524122</v>
+        <v>524136</v>
       </c>
       <c r="R31" t="n">
-        <v>6713710</v>
+        <v>6713723</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4571,7 +4555,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4581,7 +4565,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Bladrosetter och en överblommad.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4608,10 +4597,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122958631</v>
+        <v>122958064</v>
       </c>
       <c r="B32" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4643,12 +4632,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4667,10 +4656,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>524136</v>
+        <v>524144</v>
       </c>
       <c r="R32" t="n">
-        <v>6713723</v>
+        <v>6713722</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4702,7 +4691,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4712,12 +4701,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Bladrosetter och en överblommad.</t>
+          <t>Spridda sporadiskt intill klena granar inom ca 1kvm.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4744,10 +4733,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122961337</v>
+        <v>122958550</v>
       </c>
       <c r="B33" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4756,41 +4745,57 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>524040</v>
+        <v>524147</v>
       </c>
       <c r="R33" t="n">
-        <v>6713957</v>
+        <v>6713728</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4822,7 +4827,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4832,7 +4837,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4841,7 +4851,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4860,10 +4869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122959503</v>
+        <v>122958244</v>
       </c>
       <c r="B34" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4895,12 +4904,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4908,16 +4917,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524145</v>
+        <v>524143</v>
       </c>
       <c r="R34" t="n">
-        <v>6713672</v>
+        <v>6713721</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4949,7 +4963,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4959,7 +4973,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4986,10 +5005,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122958244</v>
+        <v>122959354</v>
       </c>
       <c r="B35" t="n">
-        <v>98379</v>
+        <v>8445</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4998,45 +5017,31 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5045,10 +5050,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524143</v>
+        <v>524122</v>
       </c>
       <c r="R35" t="n">
-        <v>6713721</v>
+        <v>6713710</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5080,7 +5085,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5090,12 +5095,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -5122,10 +5122,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123413726</v>
+        <v>123413856</v>
       </c>
       <c r="B36" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524030</v>
+        <v>524041</v>
       </c>
       <c r="R36" t="n">
-        <v>6713469</v>
+        <v>6713443</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5248,10 +5248,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123412439</v>
+        <v>123414270</v>
       </c>
       <c r="B37" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5296,21 +5296,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524137</v>
+        <v>524085</v>
       </c>
       <c r="R37" t="n">
-        <v>6713646</v>
+        <v>6713390</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5342,7 +5337,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5352,12 +5347,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5384,10 +5374,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123414270</v>
+        <v>123413633</v>
       </c>
       <c r="B38" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5396,52 +5386,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524085</v>
+        <v>524031</v>
       </c>
       <c r="R38" t="n">
-        <v>6713390</v>
+        <v>6713503</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5473,7 +5454,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5483,7 +5464,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5510,10 +5491,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123413078</v>
+        <v>123412257</v>
       </c>
       <c r="B39" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5545,7 +5526,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5558,21 +5539,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524102</v>
+        <v>524123</v>
       </c>
       <c r="R39" t="n">
-        <v>6713632</v>
+        <v>6713637</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5604,7 +5580,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5614,7 +5590,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5641,10 +5617,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123412257</v>
+        <v>123412973</v>
       </c>
       <c r="B40" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5676,7 +5652,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5689,16 +5665,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524123</v>
+        <v>524116</v>
       </c>
       <c r="R40" t="n">
-        <v>6713637</v>
+        <v>6713634</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5730,7 +5711,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5740,7 +5721,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5767,10 +5748,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123413119</v>
+        <v>123413726</v>
       </c>
       <c r="B41" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5807,7 +5788,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5815,22 +5796,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524101</v>
+        <v>524030</v>
       </c>
       <c r="R41" t="n">
-        <v>6713638</v>
+        <v>6713469</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5862,7 +5837,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5872,12 +5847,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5886,7 +5856,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5905,10 +5874,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123412367</v>
+        <v>123413078</v>
       </c>
       <c r="B42" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5940,7 +5909,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5953,16 +5922,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524136</v>
+        <v>524102</v>
       </c>
       <c r="R42" t="n">
-        <v>6713648</v>
+        <v>6713632</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5994,7 +5968,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6004,7 +5978,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6031,10 +6005,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123412326</v>
+        <v>123412439</v>
       </c>
       <c r="B43" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6066,7 +6040,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6079,16 +6053,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524122</v>
+        <v>524137</v>
       </c>
       <c r="R43" t="n">
-        <v>6713640</v>
+        <v>6713646</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6120,7 +6099,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6130,7 +6109,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6157,10 +6141,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123412973</v>
+        <v>123412326</v>
       </c>
       <c r="B44" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6192,7 +6176,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6205,21 +6189,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524116</v>
+        <v>524122</v>
       </c>
       <c r="R44" t="n">
-        <v>6713634</v>
+        <v>6713640</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6251,7 +6230,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6261,7 +6240,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6288,10 +6267,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123413633</v>
+        <v>123414352</v>
       </c>
       <c r="B45" t="n">
-        <v>57497</v>
+        <v>98396</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6300,43 +6279,52 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524031</v>
+        <v>524098</v>
       </c>
       <c r="R45" t="n">
-        <v>6713503</v>
+        <v>6713405</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6368,7 +6356,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6378,7 +6366,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6405,10 +6393,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123414352</v>
+        <v>123412367</v>
       </c>
       <c r="B46" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6440,7 +6428,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6455,14 +6443,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524098</v>
+        <v>524136</v>
       </c>
       <c r="R46" t="n">
-        <v>6713405</v>
+        <v>6713648</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6494,7 +6482,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6504,7 +6492,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6531,10 +6519,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123413856</v>
+        <v>123413119</v>
       </c>
       <c r="B47" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6566,12 +6554,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6579,16 +6567,22 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524041</v>
+        <v>524101</v>
       </c>
       <c r="R47" t="n">
-        <v>6713443</v>
+        <v>6713638</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6620,7 +6614,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6630,7 +6624,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6639,6 +6638,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6657,10 +6657,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123528345</v>
+        <v>123528562</v>
       </c>
       <c r="B48" t="n">
-        <v>98379</v>
+        <v>57503</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6669,54 +6669,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524025</v>
+        <v>524033</v>
       </c>
       <c r="R48" t="n">
-        <v>6713476</v>
+        <v>6713503</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6761,18 +6750,12 @@
           <t>18:41</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6791,10 +6774,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123527741</v>
+        <v>123526470</v>
       </c>
       <c r="B49" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6826,12 +6809,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6839,18 +6822,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524029</v>
+        <v>524101</v>
       </c>
       <c r="R49" t="n">
-        <v>6713459</v>
+        <v>6713880</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6882,7 +6868,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6892,12 +6878,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Sporadiskt spridda över ytan.</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6906,7 +6887,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6925,10 +6905,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123528562</v>
+        <v>123527655</v>
       </c>
       <c r="B50" t="n">
-        <v>57497</v>
+        <v>98396</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6937,43 +6917,52 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524033</v>
+        <v>524041</v>
       </c>
       <c r="R50" t="n">
-        <v>6713503</v>
+        <v>6713460</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7005,7 +6994,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7015,7 +7004,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7042,10 +7031,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123526470</v>
+        <v>123528345</v>
       </c>
       <c r="B51" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7077,12 +7066,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -7090,21 +7079,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524101</v>
+        <v>524025</v>
       </c>
       <c r="R51" t="n">
-        <v>6713880</v>
+        <v>6713476</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7136,7 +7122,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7146,7 +7132,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7155,6 +7146,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7173,10 +7165,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123527655</v>
+        <v>123527741</v>
       </c>
       <c r="B52" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7208,12 +7200,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -7221,16 +7213,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524041</v>
+        <v>524029</v>
       </c>
       <c r="R52" t="n">
-        <v>6713460</v>
+        <v>6713459</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7262,7 +7256,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7272,7 +7266,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Sporadiskt spridda över ytan.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7281,6 +7280,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7299,10 +7299,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123562313</v>
+        <v>123566767</v>
       </c>
       <c r="B53" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7311,38 +7311,52 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523993</v>
+        <v>524084</v>
       </c>
       <c r="R53" t="n">
-        <v>6713299</v>
+        <v>6713408</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7374,7 +7388,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7384,7 +7398,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7411,10 +7425,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123568589</v>
+        <v>123563043</v>
       </c>
       <c r="B54" t="n">
-        <v>97333</v>
+        <v>58165</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7427,37 +7441,47 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>103044</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524065</v>
+        <v>524035</v>
       </c>
       <c r="R54" t="n">
-        <v>6713431</v>
+        <v>6713295</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7486,7 +7510,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7496,7 +7520,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7523,10 +7547,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123566656</v>
+        <v>123572491</v>
       </c>
       <c r="B55" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7535,52 +7559,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524082</v>
+        <v>523993</v>
       </c>
       <c r="R55" t="n">
-        <v>6713393</v>
+        <v>6713281</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7612,7 +7622,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7622,7 +7632,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7649,10 +7659,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123564666</v>
+        <v>123568031</v>
       </c>
       <c r="B56" t="n">
-        <v>98379</v>
+        <v>58165</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7661,52 +7671,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524034</v>
+        <v>524094</v>
       </c>
       <c r="R56" t="n">
-        <v>6713303</v>
+        <v>6713439</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7738,7 +7739,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7748,7 +7749,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7775,10 +7776,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123565789</v>
+        <v>123569630</v>
       </c>
       <c r="B57" t="n">
-        <v>90966</v>
+        <v>100662</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7787,38 +7788,54 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524075</v>
+        <v>524047</v>
       </c>
       <c r="R57" t="n">
-        <v>6713354</v>
+        <v>6713427</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7850,7 +7867,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7860,7 +7877,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Spridda över ca 15x10m.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7869,6 +7891,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7887,10 +7910,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123567299</v>
+        <v>123564906</v>
       </c>
       <c r="B58" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7941,10 +7964,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524117</v>
+        <v>524050</v>
       </c>
       <c r="R58" t="n">
-        <v>6713411</v>
+        <v>6713310</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7976,7 +7999,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7986,7 +8009,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8013,10 +8036,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123570699</v>
+        <v>123569808</v>
       </c>
       <c r="B59" t="n">
-        <v>98379</v>
+        <v>97350</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8025,40 +8048,31 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8067,10 +8081,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524145</v>
+        <v>524077</v>
       </c>
       <c r="R59" t="n">
-        <v>6713399</v>
+        <v>6713436</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8102,7 +8116,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8112,7 +8126,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8139,10 +8153,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123572491</v>
+        <v>123564666</v>
       </c>
       <c r="B60" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8151,38 +8165,52 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523993</v>
+        <v>524034</v>
       </c>
       <c r="R60" t="n">
-        <v>6713281</v>
+        <v>6713303</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8214,7 +8242,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8224,7 +8252,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8251,10 +8279,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123569808</v>
+        <v>123565789</v>
       </c>
       <c r="B61" t="n">
-        <v>97333</v>
+        <v>90983</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8263,43 +8291,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524077</v>
+        <v>524075</v>
       </c>
       <c r="R61" t="n">
-        <v>6713436</v>
+        <v>6713354</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8331,7 +8354,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8341,7 +8364,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8371,7 +8394,7 @@
         <v>123567823</v>
       </c>
       <c r="B62" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8494,10 +8517,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123563043</v>
+        <v>123562888</v>
       </c>
       <c r="B63" t="n">
-        <v>58159</v>
+        <v>57857</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8510,16 +8533,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8527,15 +8550,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>adult</t>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8544,13 +8566,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524035</v>
+        <v>524019</v>
       </c>
       <c r="R63" t="n">
-        <v>6713295</v>
+        <v>6713291</v>
       </c>
       <c r="S63" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8579,7 +8601,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8589,7 +8611,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8616,10 +8638,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123566767</v>
+        <v>123571398</v>
       </c>
       <c r="B64" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8628,52 +8650,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524084</v>
+        <v>524112</v>
       </c>
       <c r="R64" t="n">
-        <v>6713408</v>
+        <v>6713375</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8705,7 +8713,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8715,7 +8723,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8742,10 +8750,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123569917</v>
+        <v>123568589</v>
       </c>
       <c r="B65" t="n">
-        <v>57497</v>
+        <v>97350</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8754,43 +8762,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524078</v>
+        <v>524065</v>
       </c>
       <c r="R65" t="n">
-        <v>6713434</v>
+        <v>6713431</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8822,7 +8825,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8832,7 +8835,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8859,10 +8862,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123562888</v>
+        <v>123569917</v>
       </c>
       <c r="B66" t="n">
-        <v>57851</v>
+        <v>57503</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8871,20 +8874,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -8892,14 +8895,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8908,10 +8907,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524019</v>
+        <v>524078</v>
       </c>
       <c r="R66" t="n">
-        <v>6713291</v>
+        <v>6713434</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8943,7 +8942,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8953,7 +8952,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8980,10 +8979,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123568031</v>
+        <v>123566656</v>
       </c>
       <c r="B67" t="n">
-        <v>58159</v>
+        <v>98396</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8992,43 +8991,52 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524094</v>
+        <v>524082</v>
       </c>
       <c r="R67" t="n">
-        <v>6713439</v>
+        <v>6713393</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9060,7 +9068,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9070,7 +9078,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9097,10 +9105,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123564906</v>
+        <v>123562313</v>
       </c>
       <c r="B68" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9109,52 +9117,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524050</v>
+        <v>523993</v>
       </c>
       <c r="R68" t="n">
-        <v>6713310</v>
+        <v>6713299</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9186,7 +9180,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9196,7 +9190,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9223,10 +9217,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123569630</v>
+        <v>123570699</v>
       </c>
       <c r="B69" t="n">
-        <v>100645</v>
+        <v>98396</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9235,42 +9229,40 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -9279,10 +9271,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524047</v>
+        <v>524145</v>
       </c>
       <c r="R69" t="n">
-        <v>6713427</v>
+        <v>6713399</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9314,7 +9306,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9324,12 +9316,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Spridda över ca 15x10m.</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9338,7 +9325,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -9357,10 +9343,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123571398</v>
+        <v>123567299</v>
       </c>
       <c r="B70" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9369,38 +9355,52 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>524112</v>
+        <v>524117</v>
       </c>
       <c r="R70" t="n">
-        <v>6713375</v>
+        <v>6713411</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9466,6 +9466,511 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>123760786</v>
+      </c>
+      <c r="B71" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>523969</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6713750</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>123761045</v>
+      </c>
+      <c r="B72" t="n">
+        <v>8445</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>523984</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6713796</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>123762639</v>
+      </c>
+      <c r="B73" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>524016</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6713966</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På större yta, ca 35x15m, kanske mer.</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>123761091</v>
+      </c>
+      <c r="B74" t="n">
+        <v>98396</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>523962</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6713819</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>19:13</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3719,10 +3719,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122957710</v>
+        <v>122958842</v>
       </c>
       <c r="B25" t="n">
-        <v>98396</v>
+        <v>57857</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3731,55 +3731,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvallen, Smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>524145</v>
+        <v>524149</v>
       </c>
       <c r="R25" t="n">
-        <v>6713733</v>
+        <v>6713704</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3808,7 +3803,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3818,12 +3813,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Under klena granar.</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3850,10 +3840,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122958842</v>
+        <v>122957710</v>
       </c>
       <c r="B26" t="n">
-        <v>57857</v>
+        <v>98396</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3862,50 +3852,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Banvallen, Smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>524149</v>
+        <v>524145</v>
       </c>
       <c r="R26" t="n">
-        <v>6713704</v>
+        <v>6713733</v>
       </c>
       <c r="S26" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3934,7 +3929,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3944,7 +3939,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Under klena granar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -8638,10 +8638,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123571398</v>
+        <v>123569917</v>
       </c>
       <c r="B64" t="n">
-        <v>90983</v>
+        <v>57503</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8654,34 +8654,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524112</v>
+        <v>524078</v>
       </c>
       <c r="R64" t="n">
-        <v>6713375</v>
+        <v>6713434</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8713,7 +8718,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8723,7 +8728,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8750,10 +8755,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123568589</v>
+        <v>123571398</v>
       </c>
       <c r="B65" t="n">
-        <v>97350</v>
+        <v>90983</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8762,25 +8767,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8790,10 +8795,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524065</v>
+        <v>524112</v>
       </c>
       <c r="R65" t="n">
-        <v>6713431</v>
+        <v>6713375</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8825,7 +8830,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8835,7 +8840,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8862,10 +8867,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123569917</v>
+        <v>123568589</v>
       </c>
       <c r="B66" t="n">
-        <v>57503</v>
+        <v>97350</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8874,43 +8879,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524078</v>
+        <v>524065</v>
       </c>
       <c r="R66" t="n">
-        <v>6713434</v>
+        <v>6713431</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -9972,6 +9972,969 @@
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>123769023</v>
+      </c>
+      <c r="B75" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>524017</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6713986</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>123768989</v>
+      </c>
+      <c r="B76" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>524017</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6713958</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>123768976</v>
+      </c>
+      <c r="B77" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>524011</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6713981</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>123769093</v>
+      </c>
+      <c r="B78" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>524033</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6713983</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>08:49</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>123768995</v>
+      </c>
+      <c r="B79" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>524011</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6713982</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>08:46</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>123768932</v>
+      </c>
+      <c r="B80" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>524000</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6713968</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>123769126</v>
+      </c>
+      <c r="B81" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>524017</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6713977</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>123769072</v>
+      </c>
+      <c r="B82" t="n">
+        <v>100662</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>524031</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6713998</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -4869,10 +4869,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122958244</v>
+        <v>122959354</v>
       </c>
       <c r="B34" t="n">
-        <v>98396</v>
+        <v>8445</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4881,45 +4881,31 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4928,10 +4914,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>524143</v>
+        <v>524122</v>
       </c>
       <c r="R34" t="n">
-        <v>6713721</v>
+        <v>6713710</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4963,7 +4949,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4973,12 +4959,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter. Kanske fler.</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5005,10 +4986,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122959354</v>
+        <v>122958244</v>
       </c>
       <c r="B35" t="n">
-        <v>8445</v>
+        <v>98396</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -5017,31 +4998,45 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5050,10 +5045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>524122</v>
+        <v>524143</v>
       </c>
       <c r="R35" t="n">
-        <v>6713710</v>
+        <v>6713721</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5085,7 +5080,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -5095,7 +5090,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter. Kanske fler.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -8036,10 +8036,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123569808</v>
+        <v>123564666</v>
       </c>
       <c r="B59" t="n">
-        <v>97350</v>
+        <v>98396</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8048,31 +8048,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8081,10 +8090,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524077</v>
+        <v>524034</v>
       </c>
       <c r="R59" t="n">
-        <v>6713436</v>
+        <v>6713303</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8116,7 +8125,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8126,7 +8135,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8153,10 +8162,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123564666</v>
+        <v>123569808</v>
       </c>
       <c r="B60" t="n">
-        <v>98396</v>
+        <v>97350</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8165,40 +8174,31 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -8207,10 +8207,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524034</v>
+        <v>524077</v>
       </c>
       <c r="R60" t="n">
-        <v>6713303</v>
+        <v>6713436</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8252,7 +8252,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8638,10 +8638,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123569917</v>
+        <v>123571398</v>
       </c>
       <c r="B64" t="n">
-        <v>57503</v>
+        <v>90983</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8654,39 +8654,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524078</v>
+        <v>524112</v>
       </c>
       <c r="R64" t="n">
-        <v>6713434</v>
+        <v>6713375</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8718,7 +8713,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8728,7 +8723,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8755,10 +8750,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123571398</v>
+        <v>123568589</v>
       </c>
       <c r="B65" t="n">
-        <v>90983</v>
+        <v>97350</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8767,25 +8762,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8795,10 +8790,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524112</v>
+        <v>524065</v>
       </c>
       <c r="R65" t="n">
-        <v>6713375</v>
+        <v>6713431</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8830,7 +8825,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8840,7 +8835,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8867,10 +8862,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123568589</v>
+        <v>123569917</v>
       </c>
       <c r="B66" t="n">
-        <v>97350</v>
+        <v>57503</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8879,38 +8874,43 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524065</v>
+        <v>524078</v>
       </c>
       <c r="R66" t="n">
-        <v>6713431</v>
+        <v>6713434</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -8638,10 +8638,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123571398</v>
+        <v>123569917</v>
       </c>
       <c r="B64" t="n">
-        <v>90983</v>
+        <v>57503</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8654,34 +8654,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524112</v>
+        <v>524078</v>
       </c>
       <c r="R64" t="n">
-        <v>6713375</v>
+        <v>6713434</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8713,7 +8718,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8723,7 +8728,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8750,10 +8755,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123568589</v>
+        <v>123571398</v>
       </c>
       <c r="B65" t="n">
-        <v>97350</v>
+        <v>90983</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8762,25 +8767,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8790,10 +8795,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524065</v>
+        <v>524112</v>
       </c>
       <c r="R65" t="n">
-        <v>6713431</v>
+        <v>6713375</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8825,7 +8830,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8835,7 +8840,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8862,10 +8867,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123569917</v>
+        <v>123568589</v>
       </c>
       <c r="B66" t="n">
-        <v>57503</v>
+        <v>97350</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8874,43 +8879,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524078</v>
+        <v>524065</v>
       </c>
       <c r="R66" t="n">
-        <v>6713434</v>
+        <v>6713431</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -5122,10 +5122,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123413856</v>
+        <v>123413633</v>
       </c>
       <c r="B36" t="n">
-        <v>98396</v>
+        <v>57506</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5134,52 +5134,43 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524041</v>
+        <v>524031</v>
       </c>
       <c r="R36" t="n">
-        <v>6713443</v>
+        <v>6713503</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5211,7 +5202,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5221,7 +5212,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5248,10 +5239,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123414270</v>
+        <v>123413078</v>
       </c>
       <c r="B37" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5283,7 +5274,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5296,16 +5287,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524085</v>
+        <v>524102</v>
       </c>
       <c r="R37" t="n">
-        <v>6713390</v>
+        <v>6713632</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5337,7 +5333,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5347,7 +5343,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5374,10 +5370,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123413633</v>
+        <v>123413856</v>
       </c>
       <c r="B38" t="n">
-        <v>57503</v>
+        <v>98502</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5386,43 +5382,52 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524031</v>
+        <v>524041</v>
       </c>
       <c r="R38" t="n">
-        <v>6713503</v>
+        <v>6713443</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5454,7 +5459,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5464,7 +5469,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5491,10 +5496,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123412257</v>
+        <v>123412367</v>
       </c>
       <c r="B39" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5526,7 +5531,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5541,14 +5546,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524123</v>
+        <v>524136</v>
       </c>
       <c r="R39" t="n">
-        <v>6713637</v>
+        <v>6713648</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5580,7 +5585,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5590,7 +5595,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5617,10 +5622,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123412973</v>
+        <v>123413726</v>
       </c>
       <c r="B40" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5652,7 +5657,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5665,21 +5670,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524116</v>
+        <v>524030</v>
       </c>
       <c r="R40" t="n">
-        <v>6713634</v>
+        <v>6713469</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5711,7 +5711,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5721,7 +5721,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5748,10 +5748,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123413726</v>
+        <v>123412973</v>
       </c>
       <c r="B41" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5796,16 +5796,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524030</v>
+        <v>524116</v>
       </c>
       <c r="R41" t="n">
-        <v>6713469</v>
+        <v>6713634</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5837,7 +5842,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5847,7 +5852,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5874,10 +5879,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123413078</v>
+        <v>123412439</v>
       </c>
       <c r="B42" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5909,7 +5914,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5929,14 +5934,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524102</v>
+        <v>524137</v>
       </c>
       <c r="R42" t="n">
-        <v>6713632</v>
+        <v>6713646</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5968,7 +5973,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5978,7 +5983,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6005,10 +6015,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123412439</v>
+        <v>123412326</v>
       </c>
       <c r="B43" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6040,7 +6050,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6053,21 +6063,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524137</v>
+        <v>524122</v>
       </c>
       <c r="R43" t="n">
-        <v>6713646</v>
+        <v>6713640</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6099,7 +6104,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6109,12 +6114,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6141,10 +6141,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123412326</v>
+        <v>123412257</v>
       </c>
       <c r="B44" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6176,7 +6176,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6195,10 +6195,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524122</v>
+        <v>524123</v>
       </c>
       <c r="R44" t="n">
-        <v>6713640</v>
+        <v>6713637</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6267,10 +6267,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123414352</v>
+        <v>123414270</v>
       </c>
       <c r="B45" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6321,10 +6321,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524098</v>
+        <v>524085</v>
       </c>
       <c r="R45" t="n">
-        <v>6713405</v>
+        <v>6713390</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6356,7 +6356,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6393,10 +6393,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123412367</v>
+        <v>123414352</v>
       </c>
       <c r="B46" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6428,7 +6428,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6443,14 +6443,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524136</v>
+        <v>524098</v>
       </c>
       <c r="R46" t="n">
-        <v>6713648</v>
+        <v>6713405</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6522,7 +6522,7 @@
         <v>123413119</v>
       </c>
       <c r="B47" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6657,10 +6657,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123528562</v>
+        <v>123527741</v>
       </c>
       <c r="B48" t="n">
-        <v>57503</v>
+        <v>98502</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6669,43 +6669,54 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524033</v>
+        <v>524029</v>
       </c>
       <c r="R48" t="n">
-        <v>6713503</v>
+        <v>6713459</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6737,7 +6748,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6747,7 +6758,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Sporadiskt spridda över ytan.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6756,6 +6772,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6774,10 +6791,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123526470</v>
+        <v>123528345</v>
       </c>
       <c r="B49" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6809,12 +6826,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -6822,21 +6839,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524101</v>
+        <v>524025</v>
       </c>
       <c r="R49" t="n">
-        <v>6713880</v>
+        <v>6713476</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6868,7 +6882,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6878,7 +6892,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:41</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6887,6 +6906,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6905,10 +6925,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123527655</v>
+        <v>123526470</v>
       </c>
       <c r="B50" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6940,7 +6960,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6953,16 +6973,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524041</v>
+        <v>524101</v>
       </c>
       <c r="R50" t="n">
-        <v>6713460</v>
+        <v>6713880</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6994,7 +7019,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7004,7 +7029,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7031,10 +7056,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123528345</v>
+        <v>123527655</v>
       </c>
       <c r="B51" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7071,7 +7096,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -7079,18 +7104,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524025</v>
+        <v>524041</v>
       </c>
       <c r="R51" t="n">
-        <v>6713476</v>
+        <v>6713460</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7122,7 +7145,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7132,12 +7155,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7146,7 +7164,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7165,10 +7182,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123527741</v>
+        <v>123528562</v>
       </c>
       <c r="B52" t="n">
-        <v>98396</v>
+        <v>57506</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7177,54 +7194,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524029</v>
+        <v>524033</v>
       </c>
       <c r="R52" t="n">
-        <v>6713459</v>
+        <v>6713503</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7256,7 +7262,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7266,12 +7272,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Sporadiskt spridda över ytan.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7280,7 +7281,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7299,10 +7299,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123566767</v>
+        <v>123564666</v>
       </c>
       <c r="B53" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524084</v>
+        <v>524034</v>
       </c>
       <c r="R53" t="n">
-        <v>6713408</v>
+        <v>6713303</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7388,7 +7388,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7398,7 +7398,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7425,10 +7425,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123563043</v>
+        <v>123569630</v>
       </c>
       <c r="B54" t="n">
-        <v>58165</v>
+        <v>100680</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7441,47 +7441,53 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103044</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524035</v>
+        <v>524047</v>
       </c>
       <c r="R54" t="n">
-        <v>6713295</v>
+        <v>6713427</v>
       </c>
       <c r="S54" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7510,7 +7516,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7520,7 +7526,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Spridda över ca 15x10m.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7529,6 +7540,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7547,10 +7559,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123572491</v>
+        <v>123562888</v>
       </c>
       <c r="B55" t="n">
-        <v>90983</v>
+        <v>57860</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7559,38 +7571,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523993</v>
+        <v>524019</v>
       </c>
       <c r="R55" t="n">
-        <v>6713281</v>
+        <v>6713291</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7622,7 +7643,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7632,7 +7653,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7659,10 +7680,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123568031</v>
+        <v>123567823</v>
       </c>
       <c r="B56" t="n">
-        <v>58165</v>
+        <v>98502</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7671,40 +7692,49 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524094</v>
+        <v>524093</v>
       </c>
       <c r="R56" t="n">
         <v>6713439</v>
@@ -7739,7 +7769,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7749,7 +7779,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7776,10 +7806,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123569630</v>
+        <v>123564906</v>
       </c>
       <c r="B57" t="n">
-        <v>100662</v>
+        <v>98502</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7788,42 +7818,40 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7832,10 +7860,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524047</v>
+        <v>524050</v>
       </c>
       <c r="R57" t="n">
-        <v>6713427</v>
+        <v>6713310</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7867,7 +7895,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7877,12 +7905,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Spridda över ca 15x10m.</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7891,7 +7914,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7910,10 +7932,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123564906</v>
+        <v>123565789</v>
       </c>
       <c r="B58" t="n">
-        <v>98396</v>
+        <v>90988</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7922,52 +7944,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524050</v>
+        <v>524075</v>
       </c>
       <c r="R58" t="n">
-        <v>6713310</v>
+        <v>6713354</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7999,7 +8007,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8009,7 +8017,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8036,10 +8044,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123564666</v>
+        <v>123568031</v>
       </c>
       <c r="B59" t="n">
-        <v>98396</v>
+        <v>58168</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8048,52 +8056,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524034</v>
+        <v>524094</v>
       </c>
       <c r="R59" t="n">
-        <v>6713303</v>
+        <v>6713439</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8125,7 +8124,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8135,7 +8134,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8162,10 +8161,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123569808</v>
+        <v>123570699</v>
       </c>
       <c r="B60" t="n">
-        <v>97350</v>
+        <v>98502</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8174,31 +8173,40 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -8207,10 +8215,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524077</v>
+        <v>524145</v>
       </c>
       <c r="R60" t="n">
-        <v>6713436</v>
+        <v>6713399</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8242,7 +8250,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8252,7 +8260,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8279,10 +8287,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123565789</v>
+        <v>123568589</v>
       </c>
       <c r="B61" t="n">
-        <v>90983</v>
+        <v>97367</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8291,25 +8299,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8319,10 +8327,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524075</v>
+        <v>524065</v>
       </c>
       <c r="R61" t="n">
-        <v>6713354</v>
+        <v>6713431</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8354,7 +8362,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8364,7 +8372,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8391,10 +8399,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123567823</v>
+        <v>123571398</v>
       </c>
       <c r="B62" t="n">
-        <v>98396</v>
+        <v>90988</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8403,52 +8411,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524093</v>
+        <v>524112</v>
       </c>
       <c r="R62" t="n">
-        <v>6713439</v>
+        <v>6713375</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8480,7 +8474,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8490,7 +8484,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8517,10 +8511,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123562888</v>
+        <v>123566656</v>
       </c>
       <c r="B63" t="n">
-        <v>57857</v>
+        <v>98502</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8529,47 +8523,52 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524019</v>
+        <v>524082</v>
       </c>
       <c r="R63" t="n">
-        <v>6713291</v>
+        <v>6713393</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8601,7 +8600,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8611,7 +8610,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8638,10 +8637,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123569917</v>
+        <v>123572491</v>
       </c>
       <c r="B64" t="n">
-        <v>57503</v>
+        <v>90988</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8654,39 +8653,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524078</v>
+        <v>523993</v>
       </c>
       <c r="R64" t="n">
-        <v>6713434</v>
+        <v>6713281</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8718,7 +8712,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8728,7 +8722,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8755,10 +8749,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123571398</v>
+        <v>123569917</v>
       </c>
       <c r="B65" t="n">
-        <v>90983</v>
+        <v>57506</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8771,34 +8765,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524112</v>
+        <v>524078</v>
       </c>
       <c r="R65" t="n">
-        <v>6713375</v>
+        <v>6713434</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8830,7 +8829,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8840,7 +8839,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8867,10 +8866,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123568589</v>
+        <v>123566767</v>
       </c>
       <c r="B66" t="n">
-        <v>97350</v>
+        <v>98502</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8879,38 +8878,52 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524065</v>
+        <v>524084</v>
       </c>
       <c r="R66" t="n">
-        <v>6713431</v>
+        <v>6713408</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8942,7 +8955,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8952,7 +8965,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8979,10 +8992,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123566656</v>
+        <v>123563043</v>
       </c>
       <c r="B67" t="n">
-        <v>98396</v>
+        <v>58168</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8991,55 +9004,51 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524082</v>
+        <v>524035</v>
       </c>
       <c r="R67" t="n">
-        <v>6713393</v>
+        <v>6713295</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9068,7 +9077,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9078,7 +9087,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9108,7 +9117,7 @@
         <v>123562313</v>
       </c>
       <c r="B68" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9217,10 +9226,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123570699</v>
+        <v>123569808</v>
       </c>
       <c r="B69" t="n">
-        <v>98396</v>
+        <v>97367</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9229,40 +9238,31 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524145</v>
+        <v>524077</v>
       </c>
       <c r="R69" t="n">
-        <v>6713399</v>
+        <v>6713436</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9346,7 +9346,7 @@
         <v>123567299</v>
       </c>
       <c r="B70" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>123760786</v>
       </c>
       <c r="B71" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9598,7 +9598,7 @@
         <v>123761045</v>
       </c>
       <c r="B72" t="n">
-        <v>8445</v>
+        <v>8447</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9712,10 +9712,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123762639</v>
+        <v>123761091</v>
       </c>
       <c r="B73" t="n">
-        <v>100662</v>
+        <v>98502</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9724,30 +9724,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9757,24 +9757,19 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524016</v>
+        <v>523962</v>
       </c>
       <c r="R73" t="n">
-        <v>6713966</v>
+        <v>6713819</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9806,7 +9801,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9816,12 +9811,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>20:14</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>På större yta, ca 35x15m, kanske mer.</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9848,10 +9838,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123761091</v>
+        <v>123768932</v>
       </c>
       <c r="B74" t="n">
-        <v>98396</v>
+        <v>100680</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9860,52 +9850,52 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523962</v>
+        <v>524000</v>
       </c>
       <c r="R74" t="n">
-        <v>6713819</v>
+        <v>6713968</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9932,22 +9922,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9974,10 +9964,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123769023</v>
+        <v>123769126</v>
       </c>
       <c r="B75" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10022,7 +10012,7 @@
         <v>524017</v>
       </c>
       <c r="R75" t="n">
-        <v>6713986</v>
+        <v>6713977</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10054,7 +10044,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10064,7 +10054,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10091,10 +10081,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123768989</v>
+        <v>123768995</v>
       </c>
       <c r="B76" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10136,10 +10126,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R76" t="n">
-        <v>6713958</v>
+        <v>6713982</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10171,7 +10161,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10181,7 +10171,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10208,10 +10198,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123768976</v>
+        <v>123769072</v>
       </c>
       <c r="B77" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10241,22 +10231,31 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524011</v>
+        <v>524031</v>
       </c>
       <c r="R77" t="n">
-        <v>6713981</v>
+        <v>6713998</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10288,7 +10287,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10298,7 +10297,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10325,10 +10324,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123769093</v>
+        <v>123769023</v>
       </c>
       <c r="B78" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10358,16 +10357,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10379,10 +10369,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524033</v>
+        <v>524017</v>
       </c>
       <c r="R78" t="n">
-        <v>6713983</v>
+        <v>6713986</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10414,7 +10404,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10424,7 +10414,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10451,10 +10441,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123768995</v>
+        <v>123768989</v>
       </c>
       <c r="B79" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10496,10 +10486,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524011</v>
+        <v>524017</v>
       </c>
       <c r="R79" t="n">
-        <v>6713982</v>
+        <v>6713958</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10531,7 +10521,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10541,7 +10531,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10568,10 +10558,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123768932</v>
+        <v>123769093</v>
       </c>
       <c r="B80" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10622,10 +10612,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524000</v>
+        <v>524033</v>
       </c>
       <c r="R80" t="n">
-        <v>6713968</v>
+        <v>6713983</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10657,7 +10647,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10667,7 +10657,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10694,10 +10684,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123769126</v>
+        <v>123768976</v>
       </c>
       <c r="B81" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10739,10 +10729,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R81" t="n">
-        <v>6713977</v>
+        <v>6713981</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10774,7 +10764,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10784,7 +10774,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10811,10 +10801,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>123769072</v>
+        <v>123762639</v>
       </c>
       <c r="B82" t="n">
-        <v>100662</v>
+        <v>100680</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10846,7 +10836,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10856,19 +10846,25 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524031</v>
+        <v>524016</v>
       </c>
       <c r="R82" t="n">
-        <v>6713998</v>
+        <v>6713966</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10895,22 +10891,27 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>20:14</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På större yta, ca 35x15m, kanske mer. På avverkningsyta där dom dragit basväg rakt över växtplatsen.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10919,6 +10920,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -5122,10 +5122,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123413633</v>
+        <v>123413856</v>
       </c>
       <c r="B36" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5134,43 +5134,52 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524031</v>
+        <v>524041</v>
       </c>
       <c r="R36" t="n">
-        <v>6713503</v>
+        <v>6713443</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5202,7 +5211,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5212,7 +5221,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5239,10 +5248,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123413078</v>
+        <v>123412257</v>
       </c>
       <c r="B37" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5274,7 +5283,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5287,21 +5296,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524102</v>
+        <v>524123</v>
       </c>
       <c r="R37" t="n">
-        <v>6713632</v>
+        <v>6713637</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5333,7 +5337,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5343,7 +5347,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5370,10 +5374,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123413856</v>
+        <v>123412326</v>
       </c>
       <c r="B38" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5405,7 +5409,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5424,10 +5428,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524041</v>
+        <v>524122</v>
       </c>
       <c r="R38" t="n">
-        <v>6713443</v>
+        <v>6713640</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5459,7 +5463,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5469,7 +5473,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5496,10 +5500,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123412367</v>
+        <v>123413078</v>
       </c>
       <c r="B39" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5531,7 +5535,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5544,16 +5548,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524136</v>
+        <v>524102</v>
       </c>
       <c r="R39" t="n">
-        <v>6713648</v>
+        <v>6713632</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5585,7 +5594,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5595,7 +5604,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5622,10 +5631,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123413726</v>
+        <v>123413119</v>
       </c>
       <c r="B40" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5662,7 +5671,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5670,16 +5679,22 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524030</v>
+        <v>524101</v>
       </c>
       <c r="R40" t="n">
-        <v>6713469</v>
+        <v>6713638</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5711,7 +5726,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5721,7 +5736,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5730,6 +5750,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5748,10 +5769,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123412973</v>
+        <v>123412439</v>
       </c>
       <c r="B41" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5783,7 +5804,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5807,10 +5828,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524116</v>
+        <v>524137</v>
       </c>
       <c r="R41" t="n">
-        <v>6713634</v>
+        <v>6713646</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5842,7 +5863,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5852,7 +5873,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5879,10 +5905,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123412439</v>
+        <v>123414270</v>
       </c>
       <c r="B42" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5914,7 +5940,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5927,21 +5953,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524137</v>
+        <v>524085</v>
       </c>
       <c r="R42" t="n">
-        <v>6713646</v>
+        <v>6713390</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5973,7 +5994,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5983,12 +6004,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6015,10 +6031,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123412326</v>
+        <v>123413633</v>
       </c>
       <c r="B43" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6027,52 +6043,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524122</v>
+        <v>524031</v>
       </c>
       <c r="R43" t="n">
-        <v>6713640</v>
+        <v>6713503</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6104,7 +6111,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6114,7 +6121,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6141,10 +6148,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123412257</v>
+        <v>123414352</v>
       </c>
       <c r="B44" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6176,7 +6183,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6195,10 +6202,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524123</v>
+        <v>524098</v>
       </c>
       <c r="R44" t="n">
-        <v>6713637</v>
+        <v>6713405</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6230,7 +6237,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6240,7 +6247,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6267,10 +6274,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123414270</v>
+        <v>123412367</v>
       </c>
       <c r="B45" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6302,7 +6309,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6317,14 +6324,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524085</v>
+        <v>524136</v>
       </c>
       <c r="R45" t="n">
-        <v>6713390</v>
+        <v>6713648</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6356,7 +6363,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6366,7 +6373,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6393,10 +6400,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123414352</v>
+        <v>123413726</v>
       </c>
       <c r="B46" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6428,7 +6435,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6447,10 +6454,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524098</v>
+        <v>524030</v>
       </c>
       <c r="R46" t="n">
-        <v>6713405</v>
+        <v>6713469</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6482,7 +6489,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6492,7 +6499,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6519,10 +6526,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123413119</v>
+        <v>123412973</v>
       </c>
       <c r="B47" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6554,12 +6561,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -6567,7 +6574,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr"/>
       <c r="N47" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6575,14 +6581,14 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524101</v>
+        <v>524116</v>
       </c>
       <c r="R47" t="n">
-        <v>6713638</v>
+        <v>6713634</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6614,7 +6620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6624,12 +6630,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6638,7 +6639,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6657,10 +6657,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123527741</v>
+        <v>123528562</v>
       </c>
       <c r="B48" t="n">
-        <v>98502</v>
+        <v>57507</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6669,54 +6669,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524029</v>
+        <v>524033</v>
       </c>
       <c r="R48" t="n">
-        <v>6713459</v>
+        <v>6713503</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6748,7 +6737,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6758,12 +6747,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Sporadiskt spridda över ytan.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6772,7 +6756,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6791,10 +6774,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123528345</v>
+        <v>123527741</v>
       </c>
       <c r="B49" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6826,7 +6809,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6847,10 +6830,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524025</v>
+        <v>524029</v>
       </c>
       <c r="R49" t="n">
-        <v>6713476</v>
+        <v>6713459</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6882,7 +6865,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6892,12 +6875,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Sporadiskt spridda över ytan.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6928,7 +6911,7 @@
         <v>123526470</v>
       </c>
       <c r="B50" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7059,7 +7042,7 @@
         <v>123527655</v>
       </c>
       <c r="B51" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7182,10 +7165,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123528562</v>
+        <v>123528345</v>
       </c>
       <c r="B52" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7194,43 +7177,54 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524033</v>
+        <v>524025</v>
       </c>
       <c r="R52" t="n">
-        <v>6713503</v>
+        <v>6713476</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7275,12 +7269,18 @@
           <t>18:41</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7302,7 +7302,7 @@
         <v>123564666</v>
       </c>
       <c r="B53" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7425,10 +7425,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123569630</v>
+        <v>123569808</v>
       </c>
       <c r="B54" t="n">
-        <v>100680</v>
+        <v>97369</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7441,35 +7441,24 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="N54" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -7481,10 +7470,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524047</v>
+        <v>524077</v>
       </c>
       <c r="R54" t="n">
-        <v>6713427</v>
+        <v>6713436</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7516,7 +7505,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7526,12 +7515,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Spridda över ca 15x10m.</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7540,7 +7524,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -7559,10 +7542,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123562888</v>
+        <v>123564906</v>
       </c>
       <c r="B55" t="n">
-        <v>57860</v>
+        <v>98504</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7571,47 +7554,52 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524019</v>
+        <v>524050</v>
       </c>
       <c r="R55" t="n">
-        <v>6713291</v>
+        <v>6713310</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7643,7 +7631,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7653,7 +7641,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7680,10 +7668,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123567823</v>
+        <v>123567299</v>
       </c>
       <c r="B56" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7715,7 +7703,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -7734,10 +7722,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524093</v>
+        <v>524117</v>
       </c>
       <c r="R56" t="n">
-        <v>6713439</v>
+        <v>6713411</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7769,7 +7757,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7779,7 +7767,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7806,10 +7794,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123564906</v>
+        <v>123568031</v>
       </c>
       <c r="B57" t="n">
-        <v>98502</v>
+        <v>58169</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7818,52 +7806,43 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524050</v>
+        <v>524094</v>
       </c>
       <c r="R57" t="n">
-        <v>6713310</v>
+        <v>6713439</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7895,7 +7874,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7905,7 +7884,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7932,10 +7911,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123565789</v>
+        <v>123569630</v>
       </c>
       <c r="B58" t="n">
-        <v>90988</v>
+        <v>100682</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7944,38 +7923,54 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524075</v>
+        <v>524047</v>
       </c>
       <c r="R58" t="n">
-        <v>6713354</v>
+        <v>6713427</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8007,7 +8002,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8017,7 +8012,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Spridda över ca 15x10m.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8026,6 +8026,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -8044,10 +8045,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123568031</v>
+        <v>123562888</v>
       </c>
       <c r="B59" t="n">
-        <v>58168</v>
+        <v>57861</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8060,16 +8061,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -8077,10 +8078,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8089,10 +8094,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524094</v>
+        <v>524019</v>
       </c>
       <c r="R59" t="n">
-        <v>6713439</v>
+        <v>6713291</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8124,7 +8129,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8134,7 +8139,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8161,10 +8166,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123570699</v>
+        <v>123566656</v>
       </c>
       <c r="B60" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8196,7 +8201,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8215,10 +8220,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524145</v>
+        <v>524082</v>
       </c>
       <c r="R60" t="n">
-        <v>6713399</v>
+        <v>6713393</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8250,7 +8255,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8260,7 +8265,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8290,7 +8295,7 @@
         <v>123568589</v>
       </c>
       <c r="B61" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8399,10 +8404,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123571398</v>
+        <v>123569917</v>
       </c>
       <c r="B62" t="n">
-        <v>90988</v>
+        <v>57507</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8415,34 +8420,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524112</v>
+        <v>524078</v>
       </c>
       <c r="R62" t="n">
-        <v>6713375</v>
+        <v>6713434</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8474,7 +8484,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8484,7 +8494,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8511,10 +8521,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123566656</v>
+        <v>123572491</v>
       </c>
       <c r="B63" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8523,52 +8533,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524082</v>
+        <v>523993</v>
       </c>
       <c r="R63" t="n">
-        <v>6713393</v>
+        <v>6713281</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8600,7 +8596,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8610,7 +8606,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8637,10 +8633,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123572491</v>
+        <v>123567823</v>
       </c>
       <c r="B64" t="n">
-        <v>90988</v>
+        <v>98504</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8649,38 +8645,52 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523993</v>
+        <v>524093</v>
       </c>
       <c r="R64" t="n">
-        <v>6713281</v>
+        <v>6713439</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8712,7 +8722,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8722,7 +8732,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8749,10 +8759,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123569917</v>
+        <v>123570699</v>
       </c>
       <c r="B65" t="n">
-        <v>57506</v>
+        <v>98504</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8761,43 +8771,52 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524078</v>
+        <v>524145</v>
       </c>
       <c r="R65" t="n">
-        <v>6713434</v>
+        <v>6713399</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8829,7 +8848,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8839,7 +8858,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8866,10 +8885,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123566767</v>
+        <v>123571398</v>
       </c>
       <c r="B66" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8878,52 +8897,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524084</v>
+        <v>524112</v>
       </c>
       <c r="R66" t="n">
-        <v>6713408</v>
+        <v>6713375</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8955,7 +8960,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8965,7 +8970,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8995,7 +9000,7 @@
         <v>123563043</v>
       </c>
       <c r="B67" t="n">
-        <v>58168</v>
+        <v>58169</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9117,7 +9122,7 @@
         <v>123562313</v>
       </c>
       <c r="B68" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9226,10 +9231,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123569808</v>
+        <v>123566767</v>
       </c>
       <c r="B69" t="n">
-        <v>97367</v>
+        <v>98504</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9238,31 +9243,40 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -9271,10 +9285,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524077</v>
+        <v>524084</v>
       </c>
       <c r="R69" t="n">
-        <v>6713436</v>
+        <v>6713408</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9306,7 +9320,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9316,7 +9330,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9343,10 +9357,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123567299</v>
+        <v>123565789</v>
       </c>
       <c r="B70" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9355,52 +9369,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>524117</v>
+        <v>524075</v>
       </c>
       <c r="R70" t="n">
-        <v>6713411</v>
+        <v>6713354</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9469,10 +9469,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123760786</v>
+        <v>123761091</v>
       </c>
       <c r="B71" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9523,10 +9523,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523969</v>
+        <v>523962</v>
       </c>
       <c r="R71" t="n">
-        <v>6713750</v>
+        <v>6713819</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9712,10 +9712,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123761091</v>
+        <v>123760786</v>
       </c>
       <c r="B73" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523962</v>
+        <v>523969</v>
       </c>
       <c r="R73" t="n">
-        <v>6713819</v>
+        <v>6713750</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9838,10 +9838,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123768932</v>
+        <v>123768989</v>
       </c>
       <c r="B74" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9871,16 +9871,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -9892,10 +9883,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524000</v>
+        <v>524017</v>
       </c>
       <c r="R74" t="n">
-        <v>6713968</v>
+        <v>6713958</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9927,7 +9918,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9937,7 +9928,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9964,10 +9955,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123769126</v>
+        <v>123768976</v>
       </c>
       <c r="B75" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10009,10 +10000,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R75" t="n">
-        <v>6713977</v>
+        <v>6713981</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10044,7 +10035,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10054,7 +10045,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10081,10 +10072,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123768995</v>
+        <v>123769023</v>
       </c>
       <c r="B76" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10126,10 +10117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524011</v>
+        <v>524017</v>
       </c>
       <c r="R76" t="n">
-        <v>6713982</v>
+        <v>6713986</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10201,7 +10192,7 @@
         <v>123769072</v>
       </c>
       <c r="B77" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10324,10 +10315,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123769023</v>
+        <v>123769093</v>
       </c>
       <c r="B78" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10357,7 +10348,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10369,10 +10369,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524017</v>
+        <v>524033</v>
       </c>
       <c r="R78" t="n">
-        <v>6713986</v>
+        <v>6713983</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10404,7 +10404,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10441,10 +10441,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123768989</v>
+        <v>123769126</v>
       </c>
       <c r="B79" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>524017</v>
       </c>
       <c r="R79" t="n">
-        <v>6713958</v>
+        <v>6713977</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10521,7 +10521,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10558,10 +10558,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123769093</v>
+        <v>123768995</v>
       </c>
       <c r="B80" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10591,16 +10591,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10612,10 +10603,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524033</v>
+        <v>524011</v>
       </c>
       <c r="R80" t="n">
-        <v>6713983</v>
+        <v>6713982</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10647,7 +10638,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10657,7 +10648,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10684,10 +10675,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123768976</v>
+        <v>123768932</v>
       </c>
       <c r="B81" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10717,7 +10708,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10729,10 +10729,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524011</v>
+        <v>524000</v>
       </c>
       <c r="R81" t="n">
-        <v>6713981</v>
+        <v>6713968</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10804,7 +10804,7 @@
         <v>123762639</v>
       </c>
       <c r="B82" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -8521,10 +8521,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123572491</v>
+        <v>123567823</v>
       </c>
       <c r="B63" t="n">
-        <v>90990</v>
+        <v>98504</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8533,38 +8533,52 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523993</v>
+        <v>524093</v>
       </c>
       <c r="R63" t="n">
-        <v>6713281</v>
+        <v>6713439</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8596,7 +8610,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8606,7 +8620,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8633,7 +8647,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123567823</v>
+        <v>123570699</v>
       </c>
       <c r="B64" t="n">
         <v>98504</v>
@@ -8668,7 +8682,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -8687,10 +8701,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524093</v>
+        <v>524145</v>
       </c>
       <c r="R64" t="n">
-        <v>6713439</v>
+        <v>6713399</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8722,7 +8736,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8732,7 +8746,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8759,10 +8773,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123570699</v>
+        <v>123572491</v>
       </c>
       <c r="B65" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8771,52 +8785,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524145</v>
+        <v>523993</v>
       </c>
       <c r="R65" t="n">
-        <v>6713399</v>
+        <v>6713281</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD65" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -7668,10 +7668,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123567299</v>
+        <v>123568031</v>
       </c>
       <c r="B56" t="n">
-        <v>98504</v>
+        <v>58169</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7680,52 +7680,43 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524117</v>
+        <v>524094</v>
       </c>
       <c r="R56" t="n">
-        <v>6713411</v>
+        <v>6713439</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7757,7 +7748,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7767,7 +7758,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7794,10 +7785,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123568031</v>
+        <v>123567299</v>
       </c>
       <c r="B57" t="n">
-        <v>58169</v>
+        <v>98504</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7806,43 +7797,52 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524094</v>
+        <v>524117</v>
       </c>
       <c r="R57" t="n">
-        <v>6713439</v>
+        <v>6713411</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -5125,7 +5125,7 @@
         <v>123413856</v>
       </c>
       <c r="B36" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -5248,10 +5248,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123412257</v>
+        <v>123412367</v>
       </c>
       <c r="B37" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5298,14 +5298,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524123</v>
+        <v>524136</v>
       </c>
       <c r="R37" t="n">
-        <v>6713637</v>
+        <v>6713648</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5374,10 +5374,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123412326</v>
+        <v>123413633</v>
       </c>
       <c r="B38" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5386,52 +5386,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524122</v>
+        <v>524031</v>
       </c>
       <c r="R38" t="n">
-        <v>6713640</v>
+        <v>6713503</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5463,7 +5454,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5473,7 +5464,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5500,10 +5491,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123413078</v>
+        <v>123414352</v>
       </c>
       <c r="B39" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5535,7 +5526,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5548,21 +5539,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524102</v>
+        <v>524098</v>
       </c>
       <c r="R39" t="n">
-        <v>6713632</v>
+        <v>6713405</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5594,7 +5580,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5604,7 +5590,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5631,10 +5617,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123413119</v>
+        <v>123412973</v>
       </c>
       <c r="B40" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5666,12 +5652,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5679,7 +5665,6 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5687,14 +5672,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524101</v>
+        <v>524116</v>
       </c>
       <c r="R40" t="n">
-        <v>6713638</v>
+        <v>6713634</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5726,7 +5711,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5736,12 +5721,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5750,7 +5730,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5769,10 +5748,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123412439</v>
+        <v>123413119</v>
       </c>
       <c r="B41" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5804,12 +5783,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5817,6 +5796,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5824,14 +5804,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524137</v>
+        <v>524101</v>
       </c>
       <c r="R41" t="n">
-        <v>6713646</v>
+        <v>6713638</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5863,7 +5843,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5873,12 +5853,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5887,6 +5867,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5908,7 +5889,7 @@
         <v>123414270</v>
       </c>
       <c r="B42" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6031,10 +6012,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123413633</v>
+        <v>123412326</v>
       </c>
       <c r="B43" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6043,43 +6024,52 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524031</v>
+        <v>524122</v>
       </c>
       <c r="R43" t="n">
-        <v>6713503</v>
+        <v>6713640</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6111,7 +6101,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6121,7 +6111,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6148,10 +6138,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123414352</v>
+        <v>123413726</v>
       </c>
       <c r="B44" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6183,7 +6173,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6202,10 +6192,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524098</v>
+        <v>524030</v>
       </c>
       <c r="R44" t="n">
-        <v>6713405</v>
+        <v>6713469</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6237,7 +6227,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6247,7 +6237,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6274,10 +6264,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123412367</v>
+        <v>123412439</v>
       </c>
       <c r="B45" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6309,7 +6299,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6322,16 +6312,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524136</v>
+        <v>524137</v>
       </c>
       <c r="R45" t="n">
-        <v>6713648</v>
+        <v>6713646</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6363,7 +6358,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6373,7 +6368,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6400,10 +6400,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123413726</v>
+        <v>123413078</v>
       </c>
       <c r="B46" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6448,16 +6448,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524030</v>
+        <v>524102</v>
       </c>
       <c r="R46" t="n">
-        <v>6713469</v>
+        <v>6713632</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6489,7 +6494,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6499,7 +6504,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6526,10 +6531,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123412973</v>
+        <v>123412257</v>
       </c>
       <c r="B47" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6561,7 +6566,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6574,21 +6579,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524116</v>
+        <v>524123</v>
       </c>
       <c r="R47" t="n">
-        <v>6713634</v>
+        <v>6713637</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6657,10 +6657,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123528562</v>
+        <v>123526470</v>
       </c>
       <c r="B48" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6669,43 +6669,57 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524033</v>
+        <v>524101</v>
       </c>
       <c r="R48" t="n">
-        <v>6713503</v>
+        <v>6713880</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6737,7 +6751,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6747,7 +6761,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6774,10 +6788,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123527741</v>
+        <v>123528345</v>
       </c>
       <c r="B49" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6809,7 +6823,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6830,10 +6844,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524029</v>
+        <v>524025</v>
       </c>
       <c r="R49" t="n">
-        <v>6713459</v>
+        <v>6713476</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6865,7 +6879,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6875,12 +6889,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Sporadiskt spridda över ytan.</t>
+          <t>En överblommad.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6908,10 +6922,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123526470</v>
+        <v>123527741</v>
       </c>
       <c r="B50" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6943,12 +6957,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6956,21 +6970,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524101</v>
+        <v>524029</v>
       </c>
       <c r="R50" t="n">
-        <v>6713880</v>
+        <v>6713459</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7002,7 +7013,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7012,7 +7023,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Sporadiskt spridda över ytan.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7021,6 +7037,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -7042,7 +7059,7 @@
         <v>123527655</v>
       </c>
       <c r="B51" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7165,10 +7182,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123528345</v>
+        <v>123528562</v>
       </c>
       <c r="B52" t="n">
-        <v>98504</v>
+        <v>57507</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7177,54 +7194,43 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524025</v>
+        <v>524033</v>
       </c>
       <c r="R52" t="n">
-        <v>6713476</v>
+        <v>6713503</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7269,18 +7275,12 @@
           <t>18:41</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7299,10 +7299,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123564666</v>
+        <v>123563043</v>
       </c>
       <c r="B53" t="n">
-        <v>98504</v>
+        <v>58169</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7311,55 +7311,51 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524034</v>
+        <v>524035</v>
       </c>
       <c r="R53" t="n">
-        <v>6713303</v>
+        <v>6713295</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7388,7 +7384,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7398,7 +7394,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7428,7 +7424,7 @@
         <v>123569808</v>
       </c>
       <c r="B54" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7545,7 +7541,7 @@
         <v>123564906</v>
       </c>
       <c r="B55" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7668,10 +7664,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123568031</v>
+        <v>123567823</v>
       </c>
       <c r="B56" t="n">
-        <v>58169</v>
+        <v>98079</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7680,40 +7676,49 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524094</v>
+        <v>524093</v>
       </c>
       <c r="R56" t="n">
         <v>6713439</v>
@@ -7748,7 +7753,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7758,7 +7763,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7785,10 +7790,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123567299</v>
+        <v>123570699</v>
       </c>
       <c r="B57" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7820,7 +7825,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7839,10 +7844,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524117</v>
+        <v>524145</v>
       </c>
       <c r="R57" t="n">
-        <v>6713411</v>
+        <v>6713399</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7874,7 +7879,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7884,7 +7889,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7911,10 +7916,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123569630</v>
+        <v>123566767</v>
       </c>
       <c r="B58" t="n">
-        <v>100682</v>
+        <v>98079</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7923,42 +7928,40 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7967,10 +7970,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524047</v>
+        <v>524084</v>
       </c>
       <c r="R58" t="n">
-        <v>6713427</v>
+        <v>6713408</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -8002,7 +8005,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8012,12 +8015,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Spridda över ca 15x10m.</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8026,7 +8024,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -8045,10 +8042,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123562888</v>
+        <v>123566656</v>
       </c>
       <c r="B59" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8057,47 +8054,52 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524019</v>
+        <v>524082</v>
       </c>
       <c r="R59" t="n">
-        <v>6713291</v>
+        <v>6713393</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8129,7 +8131,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8139,7 +8141,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8166,10 +8168,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123566656</v>
+        <v>123564666</v>
       </c>
       <c r="B60" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8220,10 +8222,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524082</v>
+        <v>524034</v>
       </c>
       <c r="R60" t="n">
-        <v>6713393</v>
+        <v>6713303</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8255,7 +8257,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8265,7 +8267,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8292,10 +8294,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123568589</v>
+        <v>123565789</v>
       </c>
       <c r="B61" t="n">
-        <v>97369</v>
+        <v>90990</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8304,25 +8306,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -8332,10 +8334,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524065</v>
+        <v>524075</v>
       </c>
       <c r="R61" t="n">
-        <v>6713431</v>
+        <v>6713354</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8367,7 +8369,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8377,7 +8379,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8404,10 +8406,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123569917</v>
+        <v>123567299</v>
       </c>
       <c r="B62" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8416,43 +8418,52 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524078</v>
+        <v>524117</v>
       </c>
       <c r="R62" t="n">
-        <v>6713434</v>
+        <v>6713411</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8484,7 +8495,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8494,7 +8505,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8521,10 +8532,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123567823</v>
+        <v>123562313</v>
       </c>
       <c r="B63" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8533,52 +8544,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524093</v>
+        <v>523993</v>
       </c>
       <c r="R63" t="n">
-        <v>6713439</v>
+        <v>6713299</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8610,7 +8607,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8620,7 +8617,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8647,10 +8644,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123570699</v>
+        <v>123562888</v>
       </c>
       <c r="B64" t="n">
-        <v>98504</v>
+        <v>57861</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8659,52 +8656,47 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524145</v>
+        <v>524019</v>
       </c>
       <c r="R64" t="n">
-        <v>6713399</v>
+        <v>6713291</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8736,7 +8728,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8746,7 +8738,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8997,10 +8989,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123563043</v>
+        <v>123569630</v>
       </c>
       <c r="B67" t="n">
-        <v>58169</v>
+        <v>100257</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9013,47 +9005,53 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103044</v>
+        <v>222498</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524035</v>
+        <v>524047</v>
       </c>
       <c r="R67" t="n">
-        <v>6713295</v>
+        <v>6713427</v>
       </c>
       <c r="S67" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -9082,7 +9080,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9092,7 +9090,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Spridda över ca 15x10m.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9101,6 +9104,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9119,10 +9123,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123562313</v>
+        <v>123568589</v>
       </c>
       <c r="B68" t="n">
-        <v>90990</v>
+        <v>96957</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9131,25 +9135,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -9159,10 +9163,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523993</v>
+        <v>524065</v>
       </c>
       <c r="R68" t="n">
-        <v>6713299</v>
+        <v>6713431</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9194,7 +9198,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9204,7 +9208,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9231,10 +9235,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123566767</v>
+        <v>123568031</v>
       </c>
       <c r="B69" t="n">
-        <v>98504</v>
+        <v>58169</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9243,52 +9247,43 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524084</v>
+        <v>524094</v>
       </c>
       <c r="R69" t="n">
-        <v>6713408</v>
+        <v>6713439</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9320,7 +9315,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9330,7 +9325,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9357,10 +9352,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123565789</v>
+        <v>123569917</v>
       </c>
       <c r="B70" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9373,34 +9368,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>524075</v>
+        <v>524078</v>
       </c>
       <c r="R70" t="n">
-        <v>6713354</v>
+        <v>6713434</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9469,10 +9469,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123761091</v>
+        <v>123761045</v>
       </c>
       <c r="B71" t="n">
-        <v>98504</v>
+        <v>8447</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9481,40 +9481,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9523,10 +9514,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523962</v>
+        <v>523984</v>
       </c>
       <c r="R71" t="n">
-        <v>6713819</v>
+        <v>6713796</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9558,7 +9549,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9568,7 +9559,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9595,10 +9586,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123761045</v>
+        <v>123761091</v>
       </c>
       <c r="B72" t="n">
-        <v>8447</v>
+        <v>98079</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9607,31 +9598,40 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -9640,10 +9640,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523984</v>
+        <v>523962</v>
       </c>
       <c r="R72" t="n">
-        <v>6713796</v>
+        <v>6713819</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9715,7 +9715,7 @@
         <v>123760786</v>
       </c>
       <c r="B73" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9838,10 +9838,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123768989</v>
+        <v>123769072</v>
       </c>
       <c r="B74" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9871,22 +9871,31 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524017</v>
+        <v>524031</v>
       </c>
       <c r="R74" t="n">
-        <v>6713958</v>
+        <v>6713998</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9918,7 +9927,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9928,7 +9937,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9958,7 +9967,7 @@
         <v>123768976</v>
       </c>
       <c r="B75" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -10072,10 +10081,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123769023</v>
+        <v>123769093</v>
       </c>
       <c r="B76" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -10105,7 +10114,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr"/>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10117,10 +10135,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524017</v>
+        <v>524033</v>
       </c>
       <c r="R76" t="n">
-        <v>6713986</v>
+        <v>6713983</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10152,7 +10170,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10162,7 +10180,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10189,10 +10207,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123769072</v>
+        <v>123769023</v>
       </c>
       <c r="B77" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -10222,31 +10240,22 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524031</v>
+        <v>524017</v>
       </c>
       <c r="R77" t="n">
-        <v>6713998</v>
+        <v>6713986</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10278,7 +10287,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10288,7 +10297,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10315,10 +10324,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123769093</v>
+        <v>123768932</v>
       </c>
       <c r="B78" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -10369,10 +10378,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524033</v>
+        <v>524000</v>
       </c>
       <c r="R78" t="n">
-        <v>6713983</v>
+        <v>6713968</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10404,7 +10413,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10414,7 +10423,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10441,10 +10450,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123769126</v>
+        <v>123768995</v>
       </c>
       <c r="B79" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -10486,10 +10495,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R79" t="n">
-        <v>6713977</v>
+        <v>6713982</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10521,7 +10530,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10531,7 +10540,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10558,10 +10567,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123768995</v>
+        <v>123769126</v>
       </c>
       <c r="B80" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -10603,10 +10612,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524011</v>
+        <v>524017</v>
       </c>
       <c r="R80" t="n">
-        <v>6713982</v>
+        <v>6713977</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10638,7 +10647,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10648,7 +10657,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10675,10 +10684,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123768932</v>
+        <v>123768989</v>
       </c>
       <c r="B81" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10708,16 +10717,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10729,10 +10729,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524000</v>
+        <v>524017</v>
       </c>
       <c r="R81" t="n">
-        <v>6713968</v>
+        <v>6713958</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10804,7 +10804,7 @@
         <v>123762639</v>
       </c>
       <c r="B82" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -5122,7 +5122,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123413856</v>
+        <v>123412367</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5172,14 +5172,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524041</v>
+        <v>524136</v>
       </c>
       <c r="R36" t="n">
-        <v>6713443</v>
+        <v>6713648</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5248,7 +5248,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123412367</v>
+        <v>123413856</v>
       </c>
       <c r="B37" t="n">
         <v>98079</v>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5298,14 +5298,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524136</v>
+        <v>524041</v>
       </c>
       <c r="R37" t="n">
-        <v>6713648</v>
+        <v>6713443</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5374,10 +5374,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123413633</v>
+        <v>123412257</v>
       </c>
       <c r="B38" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5386,43 +5386,52 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524031</v>
+        <v>524123</v>
       </c>
       <c r="R38" t="n">
-        <v>6713503</v>
+        <v>6713637</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5454,7 +5463,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5464,7 +5473,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5491,7 +5500,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123414352</v>
+        <v>123412973</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -5539,16 +5548,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524098</v>
+        <v>524116</v>
       </c>
       <c r="R39" t="n">
-        <v>6713405</v>
+        <v>6713634</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5580,7 +5594,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5590,7 +5604,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5617,7 +5631,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123412973</v>
+        <v>123412439</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -5652,7 +5666,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5676,10 +5690,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524116</v>
+        <v>524137</v>
       </c>
       <c r="R40" t="n">
-        <v>6713634</v>
+        <v>6713646</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5711,7 +5725,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5721,7 +5735,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5748,7 +5767,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123413119</v>
+        <v>123414352</v>
       </c>
       <c r="B41" t="n">
         <v>98079</v>
@@ -5783,12 +5802,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5796,22 +5815,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524101</v>
+        <v>524098</v>
       </c>
       <c r="R41" t="n">
-        <v>6713638</v>
+        <v>6713405</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5843,7 +5856,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5853,12 +5866,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5867,7 +5875,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5886,7 +5893,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123414270</v>
+        <v>123412326</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5921,7 +5928,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5940,10 +5947,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524085</v>
+        <v>524122</v>
       </c>
       <c r="R42" t="n">
-        <v>6713390</v>
+        <v>6713640</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5975,7 +5982,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5985,7 +5992,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6012,7 +6019,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123412326</v>
+        <v>123413078</v>
       </c>
       <c r="B43" t="n">
         <v>98079</v>
@@ -6047,7 +6054,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6060,16 +6067,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524122</v>
+        <v>524102</v>
       </c>
       <c r="R43" t="n">
-        <v>6713640</v>
+        <v>6713632</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6101,7 +6113,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6111,7 +6123,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6264,7 +6276,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123412439</v>
+        <v>123414270</v>
       </c>
       <c r="B45" t="n">
         <v>98079</v>
@@ -6299,7 +6311,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6312,21 +6324,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524137</v>
+        <v>524085</v>
       </c>
       <c r="R45" t="n">
-        <v>6713646</v>
+        <v>6713390</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6358,7 +6365,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6368,12 +6375,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6400,7 +6402,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123413078</v>
+        <v>123413119</v>
       </c>
       <c r="B46" t="n">
         <v>98079</v>
@@ -6435,12 +6437,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -6448,6 +6450,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -6459,10 +6462,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524102</v>
+        <v>524101</v>
       </c>
       <c r="R46" t="n">
-        <v>6713632</v>
+        <v>6713638</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6494,7 +6497,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6504,7 +6507,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6513,6 +6521,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6531,10 +6540,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123412257</v>
+        <v>123413633</v>
       </c>
       <c r="B47" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6543,52 +6552,43 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524123</v>
+        <v>524031</v>
       </c>
       <c r="R47" t="n">
-        <v>6713637</v>
+        <v>6713503</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6657,7 +6657,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123526470</v>
+        <v>123527655</v>
       </c>
       <c r="B48" t="n">
         <v>98079</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -6705,21 +6705,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524101</v>
+        <v>524041</v>
       </c>
       <c r="R48" t="n">
-        <v>6713880</v>
+        <v>6713460</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6751,7 +6746,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6761,7 +6756,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6788,7 +6783,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123528345</v>
+        <v>123527741</v>
       </c>
       <c r="B49" t="n">
         <v>98079</v>
@@ -6823,7 +6818,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -6844,10 +6839,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524025</v>
+        <v>524029</v>
       </c>
       <c r="R49" t="n">
-        <v>6713476</v>
+        <v>6713459</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6879,7 +6874,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6889,12 +6884,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>En överblommad.</t>
+          <t>Sporadiskt spridda över ytan.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6922,7 +6917,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123527741</v>
+        <v>123526470</v>
       </c>
       <c r="B50" t="n">
         <v>98079</v>
@@ -6957,12 +6952,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6970,18 +6965,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524029</v>
+        <v>524101</v>
       </c>
       <c r="R50" t="n">
-        <v>6713459</v>
+        <v>6713880</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7013,7 +7011,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7023,12 +7021,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Sporadiskt spridda över ytan.</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7037,7 +7030,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -7056,10 +7048,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123527655</v>
+        <v>123528562</v>
       </c>
       <c r="B51" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7068,52 +7060,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524041</v>
+        <v>524033</v>
       </c>
       <c r="R51" t="n">
-        <v>6713460</v>
+        <v>6713503</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7145,7 +7128,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -7155,7 +7138,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -7182,10 +7165,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123528562</v>
+        <v>123528345</v>
       </c>
       <c r="B52" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7194,43 +7177,54 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524033</v>
+        <v>524025</v>
       </c>
       <c r="R52" t="n">
-        <v>6713503</v>
+        <v>6713476</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7275,12 +7269,18 @@
           <t>18:41</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7299,10 +7299,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123563043</v>
+        <v>123569630</v>
       </c>
       <c r="B53" t="n">
-        <v>58169</v>
+        <v>100257</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7315,47 +7315,53 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103044</v>
+        <v>222498</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524035</v>
+        <v>524047</v>
       </c>
       <c r="R53" t="n">
-        <v>6713295</v>
+        <v>6713427</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7384,7 +7390,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7394,7 +7400,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Spridda över ca 15x10m.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7403,6 +7414,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7538,7 +7550,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123564906</v>
+        <v>123567823</v>
       </c>
       <c r="B55" t="n">
         <v>98079</v>
@@ -7573,7 +7585,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7592,10 +7604,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524050</v>
+        <v>524093</v>
       </c>
       <c r="R55" t="n">
-        <v>6713310</v>
+        <v>6713439</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7627,7 +7639,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7637,7 +7649,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7664,10 +7676,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123567823</v>
+        <v>123568589</v>
       </c>
       <c r="B56" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7676,52 +7688,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524093</v>
+        <v>524065</v>
       </c>
       <c r="R56" t="n">
-        <v>6713439</v>
+        <v>6713431</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7753,7 +7751,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7763,7 +7761,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7790,7 +7788,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123570699</v>
+        <v>123566767</v>
       </c>
       <c r="B57" t="n">
         <v>98079</v>
@@ -7825,7 +7823,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7844,10 +7842,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524145</v>
+        <v>524084</v>
       </c>
       <c r="R57" t="n">
-        <v>6713399</v>
+        <v>6713408</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7879,7 +7877,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7889,7 +7887,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7916,10 +7914,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123566767</v>
+        <v>123563043</v>
       </c>
       <c r="B58" t="n">
-        <v>98079</v>
+        <v>58169</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7928,55 +7926,51 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524084</v>
+        <v>524035</v>
       </c>
       <c r="R58" t="n">
-        <v>6713408</v>
+        <v>6713295</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -8005,7 +7999,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8015,7 +8009,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8042,10 +8036,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123566656</v>
+        <v>123569917</v>
       </c>
       <c r="B59" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8054,52 +8048,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524082</v>
+        <v>524078</v>
       </c>
       <c r="R59" t="n">
-        <v>6713393</v>
+        <v>6713434</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8131,7 +8116,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8141,7 +8126,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8168,7 +8153,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123564666</v>
+        <v>123570699</v>
       </c>
       <c r="B60" t="n">
         <v>98079</v>
@@ -8203,7 +8188,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8222,10 +8207,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524034</v>
+        <v>524145</v>
       </c>
       <c r="R60" t="n">
-        <v>6713303</v>
+        <v>6713399</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8257,7 +8242,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8267,7 +8252,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8294,10 +8279,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123565789</v>
+        <v>123564906</v>
       </c>
       <c r="B61" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8306,38 +8291,52 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524075</v>
+        <v>524050</v>
       </c>
       <c r="R61" t="n">
-        <v>6713354</v>
+        <v>6713310</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8369,7 +8368,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8379,7 +8378,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8406,10 +8405,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123567299</v>
+        <v>123565789</v>
       </c>
       <c r="B62" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8418,52 +8417,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524117</v>
+        <v>524075</v>
       </c>
       <c r="R62" t="n">
-        <v>6713411</v>
+        <v>6713354</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8495,7 +8480,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8505,7 +8490,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8532,10 +8517,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123562313</v>
+        <v>123562888</v>
       </c>
       <c r="B63" t="n">
-        <v>90990</v>
+        <v>57861</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8544,38 +8529,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523993</v>
+        <v>524019</v>
       </c>
       <c r="R63" t="n">
-        <v>6713299</v>
+        <v>6713291</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8607,7 +8601,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8617,7 +8611,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8644,10 +8638,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123562888</v>
+        <v>123571398</v>
       </c>
       <c r="B64" t="n">
-        <v>57861</v>
+        <v>90990</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8656,47 +8650,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524019</v>
+        <v>524112</v>
       </c>
       <c r="R64" t="n">
-        <v>6713291</v>
+        <v>6713375</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8728,7 +8713,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8738,7 +8723,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8765,10 +8750,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123572491</v>
+        <v>123567299</v>
       </c>
       <c r="B65" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8777,38 +8762,52 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523993</v>
+        <v>524117</v>
       </c>
       <c r="R65" t="n">
-        <v>6713281</v>
+        <v>6713411</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8840,7 +8839,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8850,7 +8849,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8877,7 +8876,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123571398</v>
+        <v>123572491</v>
       </c>
       <c r="B66" t="n">
         <v>90990</v>
@@ -8917,10 +8916,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524112</v>
+        <v>523993</v>
       </c>
       <c r="R66" t="n">
-        <v>6713375</v>
+        <v>6713281</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8952,7 +8951,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8962,7 +8961,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8989,10 +8988,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123569630</v>
+        <v>123562313</v>
       </c>
       <c r="B67" t="n">
-        <v>100257</v>
+        <v>90990</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9001,54 +9000,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524047</v>
+        <v>523993</v>
       </c>
       <c r="R67" t="n">
-        <v>6713427</v>
+        <v>6713299</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9080,7 +9063,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9090,12 +9073,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Spridda över ca 15x10m.</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9104,7 +9082,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9123,10 +9100,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123568589</v>
+        <v>123568031</v>
       </c>
       <c r="B68" t="n">
-        <v>96957</v>
+        <v>58169</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9139,34 +9116,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>103044</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524065</v>
+        <v>524094</v>
       </c>
       <c r="R68" t="n">
-        <v>6713431</v>
+        <v>6713439</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9198,7 +9180,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9208,7 +9190,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9235,10 +9217,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123568031</v>
+        <v>123564666</v>
       </c>
       <c r="B69" t="n">
-        <v>58169</v>
+        <v>98079</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9247,43 +9229,52 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524094</v>
+        <v>524034</v>
       </c>
       <c r="R69" t="n">
-        <v>6713439</v>
+        <v>6713303</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9315,7 +9306,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9325,7 +9316,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9352,10 +9343,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123569917</v>
+        <v>123566656</v>
       </c>
       <c r="B70" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9364,43 +9355,52 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>524078</v>
+        <v>524082</v>
       </c>
       <c r="R70" t="n">
-        <v>6713434</v>
+        <v>6713393</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9469,10 +9469,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123761045</v>
+        <v>123760786</v>
       </c>
       <c r="B71" t="n">
-        <v>8447</v>
+        <v>98079</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9481,31 +9481,40 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9514,10 +9523,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523984</v>
+        <v>523969</v>
       </c>
       <c r="R71" t="n">
-        <v>6713796</v>
+        <v>6713750</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9549,7 +9558,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9559,7 +9568,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9586,10 +9595,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123761091</v>
+        <v>123761045</v>
       </c>
       <c r="B72" t="n">
-        <v>98079</v>
+        <v>8447</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9598,40 +9607,31 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -9640,10 +9640,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523962</v>
+        <v>523984</v>
       </c>
       <c r="R72" t="n">
-        <v>6713819</v>
+        <v>6713796</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9675,7 +9675,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9712,7 +9712,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123760786</v>
+        <v>123761091</v>
       </c>
       <c r="B73" t="n">
         <v>98079</v>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523969</v>
+        <v>523962</v>
       </c>
       <c r="R73" t="n">
-        <v>6713750</v>
+        <v>6713819</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9838,7 +9838,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123769072</v>
+        <v>123768989</v>
       </c>
       <c r="B74" t="n">
         <v>100257</v>
@@ -9871,31 +9871,22 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524031</v>
+        <v>524017</v>
       </c>
       <c r="R74" t="n">
-        <v>6713998</v>
+        <v>6713958</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9927,7 +9918,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9937,7 +9928,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9964,7 +9955,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123768976</v>
+        <v>123768932</v>
       </c>
       <c r="B75" t="n">
         <v>100257</v>
@@ -9997,7 +9988,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10009,10 +10009,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524011</v>
+        <v>524000</v>
       </c>
       <c r="R75" t="n">
-        <v>6713981</v>
+        <v>6713968</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10081,7 +10081,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123769093</v>
+        <v>123768995</v>
       </c>
       <c r="B76" t="n">
         <v>100257</v>
@@ -10114,16 +10114,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10135,10 +10126,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524033</v>
+        <v>524011</v>
       </c>
       <c r="R76" t="n">
-        <v>6713983</v>
+        <v>6713982</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10170,7 +10161,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10180,7 +10171,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10207,7 +10198,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123769023</v>
+        <v>123769072</v>
       </c>
       <c r="B77" t="n">
         <v>100257</v>
@@ -10240,22 +10231,31 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524017</v>
+        <v>524031</v>
       </c>
       <c r="R77" t="n">
-        <v>6713986</v>
+        <v>6713998</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10287,7 +10287,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10297,7 +10297,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10324,7 +10324,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123768932</v>
+        <v>123768976</v>
       </c>
       <c r="B78" t="n">
         <v>100257</v>
@@ -10357,16 +10357,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10378,10 +10369,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524000</v>
+        <v>524011</v>
       </c>
       <c r="R78" t="n">
-        <v>6713968</v>
+        <v>6713981</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10413,7 +10404,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10423,7 +10414,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10450,7 +10441,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123768995</v>
+        <v>123769126</v>
       </c>
       <c r="B79" t="n">
         <v>100257</v>
@@ -10495,10 +10486,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524011</v>
+        <v>524017</v>
       </c>
       <c r="R79" t="n">
-        <v>6713982</v>
+        <v>6713977</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10530,7 +10521,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10540,7 +10531,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10567,7 +10558,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123769126</v>
+        <v>123769023</v>
       </c>
       <c r="B80" t="n">
         <v>100257</v>
@@ -10615,7 +10606,7 @@
         <v>524017</v>
       </c>
       <c r="R80" t="n">
-        <v>6713977</v>
+        <v>6713986</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10647,7 +10638,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10657,7 +10648,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10684,7 +10675,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123768989</v>
+        <v>123769093</v>
       </c>
       <c r="B81" t="n">
         <v>100257</v>
@@ -10717,7 +10708,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr"/>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K81" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10729,10 +10729,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524017</v>
+        <v>524033</v>
       </c>
       <c r="R81" t="n">
-        <v>6713958</v>
+        <v>6713983</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -5122,7 +5122,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123412367</v>
+        <v>123412257</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -5172,14 +5172,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524136</v>
+        <v>524123</v>
       </c>
       <c r="R36" t="n">
-        <v>6713648</v>
+        <v>6713637</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5248,7 +5248,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123413856</v>
+        <v>123414270</v>
       </c>
       <c r="B37" t="n">
         <v>98079</v>
@@ -5283,7 +5283,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5302,10 +5302,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524041</v>
+        <v>524085</v>
       </c>
       <c r="R37" t="n">
-        <v>6713443</v>
+        <v>6713390</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5337,7 +5337,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5374,7 +5374,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123412257</v>
+        <v>123412326</v>
       </c>
       <c r="B38" t="n">
         <v>98079</v>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5428,10 +5428,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524123</v>
+        <v>524122</v>
       </c>
       <c r="R38" t="n">
-        <v>6713637</v>
+        <v>6713640</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5463,7 +5463,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5500,7 +5500,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123412973</v>
+        <v>123413119</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -5535,12 +5535,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5548,6 +5548,7 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5555,14 +5556,14 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524116</v>
+        <v>524101</v>
       </c>
       <c r="R39" t="n">
-        <v>6713634</v>
+        <v>6713638</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5594,7 +5595,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5604,7 +5605,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5613,6 +5619,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5631,7 +5638,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123412439</v>
+        <v>123412367</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -5666,7 +5673,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5679,21 +5686,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524137</v>
+        <v>524136</v>
       </c>
       <c r="R40" t="n">
-        <v>6713646</v>
+        <v>6713648</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5725,7 +5727,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5735,12 +5737,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5767,7 +5764,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123414352</v>
+        <v>123412439</v>
       </c>
       <c r="B41" t="n">
         <v>98079</v>
@@ -5802,7 +5799,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5815,16 +5812,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524098</v>
+        <v>524137</v>
       </c>
       <c r="R41" t="n">
-        <v>6713405</v>
+        <v>6713646</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5856,7 +5858,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5866,7 +5868,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5893,7 +5900,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123412326</v>
+        <v>123412973</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5928,7 +5935,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5941,16 +5948,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524122</v>
+        <v>524116</v>
       </c>
       <c r="R42" t="n">
-        <v>6713640</v>
+        <v>6713634</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5982,7 +5994,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5992,7 +6004,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6276,7 +6288,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123414270</v>
+        <v>123413856</v>
       </c>
       <c r="B45" t="n">
         <v>98079</v>
@@ -6311,7 +6323,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -6330,10 +6342,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524085</v>
+        <v>524041</v>
       </c>
       <c r="R45" t="n">
-        <v>6713390</v>
+        <v>6713443</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6365,7 +6377,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6375,7 +6387,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6402,10 +6414,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123413119</v>
+        <v>123413633</v>
       </c>
       <c r="B46" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6414,58 +6426,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524101</v>
+        <v>524031</v>
       </c>
       <c r="R46" t="n">
-        <v>6713638</v>
+        <v>6713503</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6497,7 +6494,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6507,12 +6504,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6521,7 +6513,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6540,10 +6531,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123413633</v>
+        <v>123414352</v>
       </c>
       <c r="B47" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6552,43 +6543,52 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524031</v>
+        <v>524098</v>
       </c>
       <c r="R47" t="n">
-        <v>6713503</v>
+        <v>6713405</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6657,7 +6657,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123527655</v>
+        <v>123527741</v>
       </c>
       <c r="B48" t="n">
         <v>98079</v>
@@ -6692,12 +6692,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6705,16 +6705,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524041</v>
+        <v>524029</v>
       </c>
       <c r="R48" t="n">
-        <v>6713460</v>
+        <v>6713459</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6746,7 +6748,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6756,7 +6758,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Sporadiskt spridda över ytan.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6765,6 +6772,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6783,10 +6791,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123527741</v>
+        <v>123528562</v>
       </c>
       <c r="B49" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6795,54 +6803,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524029</v>
+        <v>524033</v>
       </c>
       <c r="R49" t="n">
-        <v>6713459</v>
+        <v>6713503</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6874,7 +6871,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6884,12 +6881,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Sporadiskt spridda över ytan.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6898,7 +6890,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6917,7 +6908,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123526470</v>
+        <v>123527655</v>
       </c>
       <c r="B50" t="n">
         <v>98079</v>
@@ -6952,7 +6943,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -6965,21 +6956,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524101</v>
+        <v>524041</v>
       </c>
       <c r="R50" t="n">
-        <v>6713880</v>
+        <v>6713460</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -7011,7 +6997,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7021,7 +7007,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7048,10 +7034,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123528562</v>
+        <v>123528345</v>
       </c>
       <c r="B51" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7060,43 +7046,54 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>524033</v>
+        <v>524025</v>
       </c>
       <c r="R51" t="n">
-        <v>6713503</v>
+        <v>6713476</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7141,12 +7138,18 @@
           <t>18:41</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>En överblommad.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -7165,7 +7168,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123528345</v>
+        <v>123526470</v>
       </c>
       <c r="B52" t="n">
         <v>98079</v>
@@ -7200,12 +7203,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -7213,18 +7216,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524025</v>
+        <v>524101</v>
       </c>
       <c r="R52" t="n">
-        <v>6713476</v>
+        <v>6713880</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7256,7 +7262,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7266,12 +7272,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:41</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>En överblommad.</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7280,7 +7281,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7433,10 +7433,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123569808</v>
+        <v>123566656</v>
       </c>
       <c r="B54" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7445,31 +7445,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7478,10 +7487,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524077</v>
+        <v>524082</v>
       </c>
       <c r="R54" t="n">
-        <v>6713436</v>
+        <v>6713393</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7513,7 +7522,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7523,7 +7532,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7676,10 +7685,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123568589</v>
+        <v>123562313</v>
       </c>
       <c r="B56" t="n">
-        <v>96957</v>
+        <v>90990</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7688,25 +7697,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7716,10 +7725,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>524065</v>
+        <v>523993</v>
       </c>
       <c r="R56" t="n">
-        <v>6713431</v>
+        <v>6713299</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7751,7 +7760,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7761,7 +7770,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7788,7 +7797,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123566767</v>
+        <v>123567299</v>
       </c>
       <c r="B57" t="n">
         <v>98079</v>
@@ -7823,7 +7832,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -7842,10 +7851,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524084</v>
+        <v>524117</v>
       </c>
       <c r="R57" t="n">
-        <v>6713408</v>
+        <v>6713411</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7877,7 +7886,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7887,7 +7896,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7914,10 +7923,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123563043</v>
+        <v>123568589</v>
       </c>
       <c r="B58" t="n">
-        <v>58169</v>
+        <v>96957</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7930,47 +7939,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103044</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524035</v>
+        <v>524065</v>
       </c>
       <c r="R58" t="n">
-        <v>6713295</v>
+        <v>6713431</v>
       </c>
       <c r="S58" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7999,7 +7998,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8009,7 +8008,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8036,10 +8035,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123569917</v>
+        <v>123572491</v>
       </c>
       <c r="B59" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8052,39 +8051,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524078</v>
+        <v>523993</v>
       </c>
       <c r="R59" t="n">
-        <v>6713434</v>
+        <v>6713281</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8116,7 +8110,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8126,7 +8120,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8153,7 +8147,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123570699</v>
+        <v>123564666</v>
       </c>
       <c r="B60" t="n">
         <v>98079</v>
@@ -8188,7 +8182,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -8207,10 +8201,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524145</v>
+        <v>524034</v>
       </c>
       <c r="R60" t="n">
-        <v>6713399</v>
+        <v>6713303</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8242,7 +8236,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8252,7 +8246,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8279,10 +8273,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123564906</v>
+        <v>123571398</v>
       </c>
       <c r="B61" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8291,52 +8285,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524050</v>
+        <v>524112</v>
       </c>
       <c r="R61" t="n">
-        <v>6713310</v>
+        <v>6713375</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8368,7 +8348,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8378,7 +8358,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8405,10 +8385,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123565789</v>
+        <v>123563043</v>
       </c>
       <c r="B62" t="n">
-        <v>90990</v>
+        <v>58169</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8417,41 +8397,51 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>103044</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524075</v>
+        <v>524035</v>
       </c>
       <c r="R62" t="n">
-        <v>6713354</v>
+        <v>6713295</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8480,7 +8470,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8490,7 +8480,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8517,10 +8507,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123562888</v>
+        <v>123568031</v>
       </c>
       <c r="B63" t="n">
-        <v>57861</v>
+        <v>58169</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8533,16 +8523,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103015</v>
+        <v>103044</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -8550,14 +8540,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="M63" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -8566,10 +8552,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524019</v>
+        <v>524094</v>
       </c>
       <c r="R63" t="n">
-        <v>6713291</v>
+        <v>6713439</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8601,7 +8587,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8611,7 +8597,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8638,10 +8624,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123571398</v>
+        <v>123569808</v>
       </c>
       <c r="B64" t="n">
-        <v>90990</v>
+        <v>96957</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8650,38 +8636,43 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524112</v>
+        <v>524077</v>
       </c>
       <c r="R64" t="n">
-        <v>6713375</v>
+        <v>6713436</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8713,7 +8704,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8723,7 +8714,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8750,10 +8741,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123567299</v>
+        <v>123565789</v>
       </c>
       <c r="B65" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8762,52 +8753,38 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524117</v>
+        <v>524075</v>
       </c>
       <c r="R65" t="n">
-        <v>6713411</v>
+        <v>6713354</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8839,7 +8816,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8849,7 +8826,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8876,10 +8853,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123572491</v>
+        <v>123564906</v>
       </c>
       <c r="B66" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8888,38 +8865,52 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523993</v>
+        <v>524050</v>
       </c>
       <c r="R66" t="n">
-        <v>6713281</v>
+        <v>6713310</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8951,7 +8942,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8961,7 +8952,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8988,10 +8979,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123562313</v>
+        <v>123569917</v>
       </c>
       <c r="B67" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9004,34 +8995,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523993</v>
+        <v>524078</v>
       </c>
       <c r="R67" t="n">
-        <v>6713299</v>
+        <v>6713434</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9063,7 +9059,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9073,7 +9069,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9100,10 +9096,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123568031</v>
+        <v>123562888</v>
       </c>
       <c r="B68" t="n">
-        <v>58169</v>
+        <v>57861</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9116,16 +9112,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103044</v>
+        <v>103015</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -9133,10 +9129,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -9145,10 +9145,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524094</v>
+        <v>524019</v>
       </c>
       <c r="R68" t="n">
-        <v>6713439</v>
+        <v>6713291</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9180,7 +9180,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9217,7 +9217,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123564666</v>
+        <v>123566767</v>
       </c>
       <c r="B69" t="n">
         <v>98079</v>
@@ -9252,7 +9252,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9271,10 +9271,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524034</v>
+        <v>524084</v>
       </c>
       <c r="R69" t="n">
-        <v>6713303</v>
+        <v>6713408</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9316,7 +9316,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9343,7 +9343,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123566656</v>
+        <v>123570699</v>
       </c>
       <c r="B70" t="n">
         <v>98079</v>
@@ -9378,7 +9378,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -9397,10 +9397,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>524082</v>
+        <v>524145</v>
       </c>
       <c r="R70" t="n">
-        <v>6713393</v>
+        <v>6713399</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9838,7 +9838,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123768989</v>
+        <v>123768932</v>
       </c>
       <c r="B74" t="n">
         <v>100257</v>
@@ -9871,7 +9871,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -9883,10 +9892,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524017</v>
+        <v>524000</v>
       </c>
       <c r="R74" t="n">
-        <v>6713958</v>
+        <v>6713968</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9918,7 +9927,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9928,7 +9937,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9955,7 +9964,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123768932</v>
+        <v>123769023</v>
       </c>
       <c r="B75" t="n">
         <v>100257</v>
@@ -9988,16 +9997,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10009,10 +10009,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524000</v>
+        <v>524017</v>
       </c>
       <c r="R75" t="n">
-        <v>6713968</v>
+        <v>6713986</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10198,7 +10198,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123769072</v>
+        <v>123768989</v>
       </c>
       <c r="B77" t="n">
         <v>100257</v>
@@ -10231,31 +10231,22 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524031</v>
+        <v>524017</v>
       </c>
       <c r="R77" t="n">
-        <v>6713998</v>
+        <v>6713958</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10287,7 +10278,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10297,7 +10288,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10441,7 +10432,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123769126</v>
+        <v>123769093</v>
       </c>
       <c r="B79" t="n">
         <v>100257</v>
@@ -10474,7 +10465,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10486,10 +10486,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524017</v>
+        <v>524033</v>
       </c>
       <c r="R79" t="n">
-        <v>6713977</v>
+        <v>6713983</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10521,7 +10521,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10558,7 +10558,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123769023</v>
+        <v>123769126</v>
       </c>
       <c r="B80" t="n">
         <v>100257</v>
@@ -10606,7 +10606,7 @@
         <v>524017</v>
       </c>
       <c r="R80" t="n">
-        <v>6713986</v>
+        <v>6713977</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10638,7 +10638,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10648,7 +10648,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10675,7 +10675,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123769093</v>
+        <v>123769072</v>
       </c>
       <c r="B81" t="n">
         <v>100257</v>
@@ -10710,29 +10710,29 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524033</v>
+        <v>524031</v>
       </c>
       <c r="R81" t="n">
-        <v>6713983</v>
+        <v>6713998</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -5122,7 +5122,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123412257</v>
+        <v>123413119</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -5170,16 +5170,22 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>524123</v>
+        <v>524101</v>
       </c>
       <c r="R36" t="n">
-        <v>6713637</v>
+        <v>6713638</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5211,7 +5217,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5221,7 +5227,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spridda sporadiskt över ytan.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5230,6 +5241,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -5248,7 +5260,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123414270</v>
+        <v>123412326</v>
       </c>
       <c r="B37" t="n">
         <v>98079</v>
@@ -5283,7 +5295,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5302,10 +5314,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>524085</v>
+        <v>524122</v>
       </c>
       <c r="R37" t="n">
-        <v>6713390</v>
+        <v>6713640</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5337,7 +5349,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5347,7 +5359,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5374,7 +5386,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123412326</v>
+        <v>123413078</v>
       </c>
       <c r="B38" t="n">
         <v>98079</v>
@@ -5409,7 +5421,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5422,16 +5434,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>524122</v>
+        <v>524102</v>
       </c>
       <c r="R38" t="n">
-        <v>6713640</v>
+        <v>6713632</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5463,7 +5480,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5473,7 +5490,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5500,7 +5517,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123413119</v>
+        <v>123414270</v>
       </c>
       <c r="B39" t="n">
         <v>98079</v>
@@ -5535,12 +5552,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5548,22 +5565,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>524101</v>
+        <v>524085</v>
       </c>
       <c r="R39" t="n">
-        <v>6713638</v>
+        <v>6713390</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5595,7 +5606,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5605,12 +5616,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Spridda sporadiskt över ytan.</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5619,7 +5625,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5638,7 +5643,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123412367</v>
+        <v>123412973</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -5673,7 +5678,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5686,16 +5691,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>524136</v>
+        <v>524116</v>
       </c>
       <c r="R40" t="n">
-        <v>6713648</v>
+        <v>6713634</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5727,7 +5737,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5737,7 +5747,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5764,7 +5774,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123412439</v>
+        <v>123412367</v>
       </c>
       <c r="B41" t="n">
         <v>98079</v>
@@ -5799,7 +5809,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5812,21 +5822,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>524137</v>
+        <v>524136</v>
       </c>
       <c r="R41" t="n">
-        <v>6713646</v>
+        <v>6713648</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5858,7 +5863,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5868,12 +5873,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:39</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Inom ca 5 kv/dm.</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5900,7 +5900,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123412973</v>
+        <v>123413856</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5935,7 +5935,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -5948,21 +5948,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>524116</v>
+        <v>524041</v>
       </c>
       <c r="R42" t="n">
-        <v>6713634</v>
+        <v>6713443</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5994,7 +5989,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -6004,7 +5999,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6031,7 +6026,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123413078</v>
+        <v>123413726</v>
       </c>
       <c r="B43" t="n">
         <v>98079</v>
@@ -6066,7 +6061,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -6079,21 +6074,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>524102</v>
+        <v>524030</v>
       </c>
       <c r="R43" t="n">
-        <v>6713632</v>
+        <v>6713469</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -6125,7 +6115,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -6135,7 +6125,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6162,7 +6152,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123413726</v>
+        <v>123412439</v>
       </c>
       <c r="B44" t="n">
         <v>98079</v>
@@ -6197,7 +6187,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6210,16 +6200,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>524030</v>
+        <v>524137</v>
       </c>
       <c r="R44" t="n">
-        <v>6713469</v>
+        <v>6713646</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6251,7 +6246,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:39</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6261,7 +6256,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>17:39</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Inom ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6288,10 +6288,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123413856</v>
+        <v>123413633</v>
       </c>
       <c r="B45" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6300,52 +6300,43 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>524041</v>
+        <v>524031</v>
       </c>
       <c r="R45" t="n">
-        <v>6713443</v>
+        <v>6713503</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6377,7 +6368,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6387,7 +6378,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:24</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6414,10 +6405,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123413633</v>
+        <v>123414352</v>
       </c>
       <c r="B46" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6426,43 +6417,52 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>524031</v>
+        <v>524098</v>
       </c>
       <c r="R46" t="n">
-        <v>6713503</v>
+        <v>6713405</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6531,7 +6531,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123414352</v>
+        <v>123412257</v>
       </c>
       <c r="B47" t="n">
         <v>98079</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>524098</v>
+        <v>524123</v>
       </c>
       <c r="R47" t="n">
-        <v>6713405</v>
+        <v>6713637</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6657,10 +6657,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123527741</v>
+        <v>123528562</v>
       </c>
       <c r="B48" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6669,54 +6669,43 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>524029</v>
+        <v>524033</v>
       </c>
       <c r="R48" t="n">
-        <v>6713459</v>
+        <v>6713503</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6748,7 +6737,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6758,12 +6747,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Sporadiskt spridda över ytan.</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6772,7 +6756,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6791,10 +6774,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123528562</v>
+        <v>123526470</v>
       </c>
       <c r="B49" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6803,43 +6786,57 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>524033</v>
+        <v>524101</v>
       </c>
       <c r="R49" t="n">
-        <v>6713503</v>
+        <v>6713880</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6871,7 +6868,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6881,7 +6878,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6908,7 +6905,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123527655</v>
+        <v>123527741</v>
       </c>
       <c r="B50" t="n">
         <v>98079</v>
@@ -6943,12 +6940,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -6956,16 +6953,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>524041</v>
+        <v>524029</v>
       </c>
       <c r="R50" t="n">
-        <v>6713460</v>
+        <v>6713459</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6997,7 +6996,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -7007,7 +7006,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Sporadiskt spridda över ytan.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -7016,6 +7020,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -7168,7 +7173,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123526470</v>
+        <v>123527655</v>
       </c>
       <c r="B52" t="n">
         <v>98079</v>
@@ -7203,7 +7208,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7216,21 +7221,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>524101</v>
+        <v>524041</v>
       </c>
       <c r="R52" t="n">
-        <v>6713880</v>
+        <v>6713460</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7262,7 +7262,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -7272,7 +7272,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7299,10 +7299,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123569630</v>
+        <v>123572491</v>
       </c>
       <c r="B53" t="n">
-        <v>100257</v>
+        <v>90990</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7311,54 +7311,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>524047</v>
+        <v>523993</v>
       </c>
       <c r="R53" t="n">
-        <v>6713427</v>
+        <v>6713281</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7390,7 +7374,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7400,12 +7384,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:01</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Spridda över ca 15x10m.</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7414,7 +7393,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -7433,7 +7411,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123566656</v>
+        <v>123564666</v>
       </c>
       <c r="B54" t="n">
         <v>98079</v>
@@ -7487,10 +7465,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524082</v>
+        <v>524034</v>
       </c>
       <c r="R54" t="n">
-        <v>6713393</v>
+        <v>6713303</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7522,7 +7500,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7532,7 +7510,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7559,10 +7537,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123567823</v>
+        <v>123569808</v>
       </c>
       <c r="B55" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7571,40 +7549,31 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7613,10 +7582,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>524093</v>
+        <v>524077</v>
       </c>
       <c r="R55" t="n">
-        <v>6713439</v>
+        <v>6713436</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7648,7 +7617,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7658,7 +7627,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7685,10 +7654,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123562313</v>
+        <v>123568589</v>
       </c>
       <c r="B56" t="n">
-        <v>90990</v>
+        <v>96957</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7697,25 +7666,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7725,10 +7694,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523993</v>
+        <v>524065</v>
       </c>
       <c r="R56" t="n">
-        <v>6713299</v>
+        <v>6713431</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7760,7 +7729,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7770,7 +7739,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7797,10 +7766,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123567299</v>
+        <v>123563043</v>
       </c>
       <c r="B57" t="n">
-        <v>98079</v>
+        <v>58169</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7809,55 +7778,51 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>103044</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>524117</v>
+        <v>524035</v>
       </c>
       <c r="R57" t="n">
-        <v>6713411</v>
+        <v>6713295</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7886,7 +7851,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7896,7 +7861,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7923,10 +7888,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123568589</v>
+        <v>123567299</v>
       </c>
       <c r="B58" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7935,38 +7900,52 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>524065</v>
+        <v>524117</v>
       </c>
       <c r="R58" t="n">
-        <v>6713431</v>
+        <v>6713411</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7998,7 +7977,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -8008,7 +7987,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>11:43</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -8035,10 +8014,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123572491</v>
+        <v>123568031</v>
       </c>
       <c r="B59" t="n">
-        <v>90990</v>
+        <v>58169</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8047,38 +8026,43 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>103044</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523993</v>
+        <v>524094</v>
       </c>
       <c r="R59" t="n">
-        <v>6713281</v>
+        <v>6713439</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8110,7 +8094,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8120,7 +8104,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8147,10 +8131,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123564666</v>
+        <v>123562313</v>
       </c>
       <c r="B60" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8159,52 +8143,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>524034</v>
+        <v>523993</v>
       </c>
       <c r="R60" t="n">
-        <v>6713303</v>
+        <v>6713299</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8236,7 +8206,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8246,7 +8216,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8273,10 +8243,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123571398</v>
+        <v>123566656</v>
       </c>
       <c r="B61" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -8285,38 +8255,52 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>524112</v>
+        <v>524082</v>
       </c>
       <c r="R61" t="n">
-        <v>6713375</v>
+        <v>6713393</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -8348,7 +8332,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -8358,7 +8342,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8385,10 +8369,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123563043</v>
+        <v>123564906</v>
       </c>
       <c r="B62" t="n">
-        <v>58169</v>
+        <v>98079</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -8397,51 +8381,55 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>524035</v>
+        <v>524050</v>
       </c>
       <c r="R62" t="n">
-        <v>6713295</v>
+        <v>6713310</v>
       </c>
       <c r="S62" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -8470,7 +8458,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -8480,7 +8468,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8507,10 +8495,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123568031</v>
+        <v>123571398</v>
       </c>
       <c r="B63" t="n">
-        <v>58169</v>
+        <v>90990</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8519,43 +8507,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103044</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524094</v>
+        <v>524112</v>
       </c>
       <c r="R63" t="n">
-        <v>6713439</v>
+        <v>6713375</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8587,7 +8570,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8597,7 +8580,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8624,10 +8607,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123569808</v>
+        <v>123562888</v>
       </c>
       <c r="B64" t="n">
-        <v>96957</v>
+        <v>57861</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8640,39 +8623,43 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524077</v>
+        <v>524019</v>
       </c>
       <c r="R64" t="n">
-        <v>6713436</v>
+        <v>6713291</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8704,7 +8691,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8714,7 +8701,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8741,10 +8728,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123565789</v>
+        <v>123570699</v>
       </c>
       <c r="B65" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8753,38 +8740,52 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524075</v>
+        <v>524145</v>
       </c>
       <c r="R65" t="n">
-        <v>6713354</v>
+        <v>6713399</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8816,7 +8817,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8826,7 +8827,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8853,7 +8854,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123564906</v>
+        <v>123567823</v>
       </c>
       <c r="B66" t="n">
         <v>98079</v>
@@ -8888,7 +8889,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8907,10 +8908,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524050</v>
+        <v>524093</v>
       </c>
       <c r="R66" t="n">
-        <v>6713310</v>
+        <v>6713439</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8942,7 +8943,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8952,7 +8953,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8979,10 +8980,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123569917</v>
+        <v>123566767</v>
       </c>
       <c r="B67" t="n">
-        <v>57507</v>
+        <v>98079</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8991,43 +8992,52 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524078</v>
+        <v>524084</v>
       </c>
       <c r="R67" t="n">
-        <v>6713434</v>
+        <v>6713408</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9059,7 +9069,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9069,7 +9079,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -9096,10 +9106,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123562888</v>
+        <v>123569917</v>
       </c>
       <c r="B68" t="n">
-        <v>57861</v>
+        <v>57507</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9108,20 +9118,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -9129,14 +9139,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -9145,10 +9151,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>524019</v>
+        <v>524078</v>
       </c>
       <c r="R68" t="n">
-        <v>6713291</v>
+        <v>6713434</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9180,7 +9186,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -9190,7 +9196,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -9217,10 +9223,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123566767</v>
+        <v>123565789</v>
       </c>
       <c r="B69" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -9229,52 +9235,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>524084</v>
+        <v>524075</v>
       </c>
       <c r="R69" t="n">
-        <v>6713408</v>
+        <v>6713354</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -9306,7 +9298,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9316,7 +9308,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9343,10 +9335,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123570699</v>
+        <v>123569630</v>
       </c>
       <c r="B70" t="n">
-        <v>98079</v>
+        <v>100257</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9355,40 +9347,42 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -9397,10 +9391,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>524145</v>
+        <v>524047</v>
       </c>
       <c r="R70" t="n">
-        <v>6713399</v>
+        <v>6713427</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9432,7 +9426,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9442,7 +9436,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Spridda över ca 15x10m.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9451,6 +9450,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -9469,7 +9469,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123760786</v>
+        <v>123761091</v>
       </c>
       <c r="B71" t="n">
         <v>98079</v>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -9523,10 +9523,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523969</v>
+        <v>523962</v>
       </c>
       <c r="R71" t="n">
-        <v>6713750</v>
+        <v>6713819</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9595,10 +9595,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123761045</v>
+        <v>123760786</v>
       </c>
       <c r="B72" t="n">
-        <v>8447</v>
+        <v>98079</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9607,31 +9607,40 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -9640,10 +9649,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523984</v>
+        <v>523969</v>
       </c>
       <c r="R72" t="n">
-        <v>6713796</v>
+        <v>6713750</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9675,7 +9684,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9685,7 +9694,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9712,10 +9721,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123761091</v>
+        <v>123761045</v>
       </c>
       <c r="B73" t="n">
-        <v>98079</v>
+        <v>8447</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9724,40 +9733,31 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -9766,10 +9766,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523962</v>
+        <v>523984</v>
       </c>
       <c r="R73" t="n">
-        <v>6713819</v>
+        <v>6713796</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9801,7 +9801,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9838,7 +9838,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123768932</v>
+        <v>123768995</v>
       </c>
       <c r="B74" t="n">
         <v>100257</v>
@@ -9871,16 +9871,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -9892,10 +9883,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524000</v>
+        <v>524011</v>
       </c>
       <c r="R74" t="n">
-        <v>6713968</v>
+        <v>6713982</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9927,7 +9918,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9937,7 +9928,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9964,7 +9955,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123769023</v>
+        <v>123768976</v>
       </c>
       <c r="B75" t="n">
         <v>100257</v>
@@ -10009,10 +10000,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R75" t="n">
-        <v>6713986</v>
+        <v>6713981</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10044,7 +10035,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10054,7 +10045,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10081,7 +10072,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123768995</v>
+        <v>123768989</v>
       </c>
       <c r="B76" t="n">
         <v>100257</v>
@@ -10126,10 +10117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524011</v>
+        <v>524017</v>
       </c>
       <c r="R76" t="n">
-        <v>6713982</v>
+        <v>6713958</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10161,7 +10152,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10171,7 +10162,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10198,7 +10189,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123768989</v>
+        <v>123768932</v>
       </c>
       <c r="B77" t="n">
         <v>100257</v>
@@ -10231,7 +10222,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10243,10 +10243,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524017</v>
+        <v>524000</v>
       </c>
       <c r="R77" t="n">
-        <v>6713958</v>
+        <v>6713968</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10278,7 +10278,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10315,7 +10315,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123768976</v>
+        <v>123769093</v>
       </c>
       <c r="B78" t="n">
         <v>100257</v>
@@ -10348,7 +10348,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10360,10 +10369,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524011</v>
+        <v>524033</v>
       </c>
       <c r="R78" t="n">
-        <v>6713981</v>
+        <v>6713983</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10395,7 +10404,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10405,7 +10414,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10432,7 +10441,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123769093</v>
+        <v>123769072</v>
       </c>
       <c r="B79" t="n">
         <v>100257</v>
@@ -10467,29 +10476,29 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524033</v>
+        <v>524031</v>
       </c>
       <c r="R79" t="n">
-        <v>6713983</v>
+        <v>6713998</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10521,7 +10530,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10531,7 +10540,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10558,7 +10567,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123769126</v>
+        <v>123769023</v>
       </c>
       <c r="B80" t="n">
         <v>100257</v>
@@ -10606,7 +10615,7 @@
         <v>524017</v>
       </c>
       <c r="R80" t="n">
-        <v>6713977</v>
+        <v>6713986</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10638,7 +10647,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10648,7 +10657,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10675,7 +10684,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>123769072</v>
+        <v>123769126</v>
       </c>
       <c r="B81" t="n">
         <v>100257</v>
@@ -10708,31 +10717,22 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>524031</v>
+        <v>524017</v>
       </c>
       <c r="R81" t="n">
-        <v>6713998</v>
+        <v>6713977</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD81" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -7299,10 +7299,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123572491</v>
+        <v>123564666</v>
       </c>
       <c r="B53" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7311,38 +7311,52 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523993</v>
+        <v>524034</v>
       </c>
       <c r="R53" t="n">
-        <v>6713281</v>
+        <v>6713303</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -7374,7 +7388,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -7384,7 +7398,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7411,10 +7425,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123564666</v>
+        <v>123572491</v>
       </c>
       <c r="B54" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7423,52 +7437,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>524034</v>
+        <v>523993</v>
       </c>
       <c r="R54" t="n">
-        <v>6713303</v>
+        <v>6713281</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -8014,10 +8014,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123568031</v>
+        <v>123562313</v>
       </c>
       <c r="B59" t="n">
-        <v>58169</v>
+        <v>90990</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -8026,43 +8026,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103044</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>524094</v>
+        <v>523993</v>
       </c>
       <c r="R59" t="n">
-        <v>6713439</v>
+        <v>6713299</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -8094,7 +8089,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -8104,7 +8099,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -8131,10 +8126,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123562313</v>
+        <v>123568031</v>
       </c>
       <c r="B60" t="n">
-        <v>90990</v>
+        <v>58169</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -8143,38 +8138,43 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1202</v>
+        <v>103044</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523993</v>
+        <v>524094</v>
       </c>
       <c r="R60" t="n">
-        <v>6713299</v>
+        <v>6713439</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8495,10 +8495,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123571398</v>
+        <v>123562888</v>
       </c>
       <c r="B63" t="n">
-        <v>90990</v>
+        <v>57861</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -8507,38 +8507,47 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>103015</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>524112</v>
+        <v>524019</v>
       </c>
       <c r="R63" t="n">
-        <v>6713375</v>
+        <v>6713291</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8570,7 +8579,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8580,7 +8589,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8607,10 +8616,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123562888</v>
+        <v>123570699</v>
       </c>
       <c r="B64" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8619,47 +8628,52 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>524019</v>
+        <v>524145</v>
       </c>
       <c r="R64" t="n">
-        <v>6713291</v>
+        <v>6713399</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8691,7 +8705,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -8701,7 +8715,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8728,7 +8742,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>123570699</v>
+        <v>123567823</v>
       </c>
       <c r="B65" t="n">
         <v>98079</v>
@@ -8763,7 +8777,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -8782,10 +8796,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>524145</v>
+        <v>524093</v>
       </c>
       <c r="R65" t="n">
-        <v>6713399</v>
+        <v>6713439</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8817,7 +8831,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8827,7 +8841,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8854,7 +8868,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>123567823</v>
+        <v>123566767</v>
       </c>
       <c r="B66" t="n">
         <v>98079</v>
@@ -8889,7 +8903,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -8908,10 +8922,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>524093</v>
+        <v>524084</v>
       </c>
       <c r="R66" t="n">
-        <v>6713439</v>
+        <v>6713408</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8943,7 +8957,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8953,7 +8967,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8980,10 +8994,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123566767</v>
+        <v>123571398</v>
       </c>
       <c r="B67" t="n">
-        <v>98079</v>
+        <v>90990</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8992,52 +9006,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>524084</v>
+        <v>524112</v>
       </c>
       <c r="R67" t="n">
-        <v>6713408</v>
+        <v>6713375</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9357,10 +9357,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123761045</v>
+        <v>123761091</v>
       </c>
       <c r="B70" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -9369,31 +9369,40 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -9402,10 +9411,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523984</v>
+        <v>523962</v>
       </c>
       <c r="R70" t="n">
-        <v>6713796</v>
+        <v>6713819</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -9437,7 +9446,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9447,7 +9456,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9474,10 +9483,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123760786</v>
+        <v>123761045</v>
       </c>
       <c r="B71" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -9486,40 +9495,31 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -9528,10 +9528,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523969</v>
+        <v>523984</v>
       </c>
       <c r="R71" t="n">
-        <v>6713750</v>
+        <v>6713796</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9600,7 +9600,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>123761091</v>
+        <v>123760786</v>
       </c>
       <c r="B72" t="n">
         <v>98101</v>
@@ -9635,7 +9635,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -9654,10 +9654,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523962</v>
+        <v>523969</v>
       </c>
       <c r="R72" t="n">
-        <v>6713819</v>
+        <v>6713750</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9689,7 +9689,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9726,7 +9726,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>123768976</v>
+        <v>123769093</v>
       </c>
       <c r="B73" t="n">
         <v>100279</v>
@@ -9759,7 +9759,16 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -9771,10 +9780,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>524011</v>
+        <v>524033</v>
       </c>
       <c r="R73" t="n">
-        <v>6713981</v>
+        <v>6713983</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9806,7 +9815,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9816,7 +9825,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:49</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9843,7 +9852,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>123768932</v>
+        <v>123769023</v>
       </c>
       <c r="B74" t="n">
         <v>100279</v>
@@ -9876,16 +9885,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="K74" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -9897,10 +9897,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>524000</v>
+        <v>524017</v>
       </c>
       <c r="R74" t="n">
-        <v>6713968</v>
+        <v>6713986</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9932,7 +9932,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9942,7 +9942,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9969,7 +9969,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>123769093</v>
+        <v>123768989</v>
       </c>
       <c r="B75" t="n">
         <v>100279</v>
@@ -10002,16 +10002,7 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -10023,10 +10014,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>524033</v>
+        <v>524017</v>
       </c>
       <c r="R75" t="n">
-        <v>6713983</v>
+        <v>6713958</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -10058,7 +10049,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -10068,7 +10059,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>08:49</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -10095,7 +10086,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>123768989</v>
+        <v>123768976</v>
       </c>
       <c r="B76" t="n">
         <v>100279</v>
@@ -10140,10 +10131,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R76" t="n">
-        <v>6713958</v>
+        <v>6713981</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -10175,7 +10166,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -10185,7 +10176,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -10212,7 +10203,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>123768995</v>
+        <v>123769126</v>
       </c>
       <c r="B77" t="n">
         <v>100279</v>
@@ -10257,10 +10248,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>524011</v>
+        <v>524017</v>
       </c>
       <c r="R77" t="n">
-        <v>6713982</v>
+        <v>6713977</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -10292,7 +10283,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10302,7 +10293,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10329,7 +10320,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>123769126</v>
+        <v>123769072</v>
       </c>
       <c r="B78" t="n">
         <v>100279</v>
@@ -10362,22 +10353,31 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>524017</v>
+        <v>524031</v>
       </c>
       <c r="R78" t="n">
-        <v>6713977</v>
+        <v>6713998</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -10409,7 +10409,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10446,7 +10446,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>123769072</v>
+        <v>123768932</v>
       </c>
       <c r="B79" t="n">
         <v>100279</v>
@@ -10481,29 +10481,29 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>524031</v>
+        <v>524000</v>
       </c>
       <c r="R79" t="n">
-        <v>6713998</v>
+        <v>6713968</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10535,7 +10535,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10545,7 +10545,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10572,7 +10572,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>123769023</v>
+        <v>123768995</v>
       </c>
       <c r="B80" t="n">
         <v>100279</v>
@@ -10617,10 +10617,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>524017</v>
+        <v>524011</v>
       </c>
       <c r="R80" t="n">
-        <v>6713986</v>
+        <v>6713982</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10827,7 +10827,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124433963</v>
+        <v>124431841</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524033</v>
+        <v>524168</v>
       </c>
       <c r="R82" t="n">
-        <v>6713451</v>
+        <v>6713526</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10953,7 +10953,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124432135</v>
+        <v>124434100</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -11001,16 +11001,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524180</v>
+        <v>524042</v>
       </c>
       <c r="R83" t="n">
-        <v>6713485</v>
+        <v>6713423</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11042,7 +11047,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11052,7 +11057,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11079,10 +11089,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124431841</v>
+        <v>124434324</v>
       </c>
       <c r="B84" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11091,40 +11101,31 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -11133,10 +11134,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524168</v>
+        <v>524045</v>
       </c>
       <c r="R84" t="n">
-        <v>6713526</v>
+        <v>6713403</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11168,7 +11169,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11178,7 +11179,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11205,7 +11206,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124434100</v>
+        <v>124432412</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11253,21 +11254,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524042</v>
+        <v>524183</v>
       </c>
       <c r="R85" t="n">
-        <v>6713423</v>
+        <v>6713449</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11299,7 +11295,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11309,12 +11305,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11341,7 +11332,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124431501</v>
+        <v>124433963</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11376,7 +11367,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11395,10 +11386,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524175</v>
+        <v>524033</v>
       </c>
       <c r="R86" t="n">
-        <v>6713573</v>
+        <v>6713451</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11430,7 +11421,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11440,12 +11431,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11608,10 +11594,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124434324</v>
+        <v>124432135</v>
       </c>
       <c r="B88" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11620,31 +11606,40 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11653,10 +11648,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524045</v>
+        <v>524180</v>
       </c>
       <c r="R88" t="n">
-        <v>6713403</v>
+        <v>6713485</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11688,7 +11683,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11698,7 +11693,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11725,7 +11720,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124432412</v>
+        <v>124431501</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -11760,7 +11755,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11779,10 +11774,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524183</v>
+        <v>524175</v>
       </c>
       <c r="R89" t="n">
-        <v>6713449</v>
+        <v>6713573</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11814,7 +11809,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11824,7 +11819,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11848,6 +11848,132 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>124711417</v>
+      </c>
+      <c r="B90" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>524045</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6713421</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-05-03</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -10953,10 +10953,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124434100</v>
+        <v>124434324</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10965,45 +10965,31 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -11012,10 +10998,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524042</v>
+        <v>524045</v>
       </c>
       <c r="R83" t="n">
-        <v>6713423</v>
+        <v>6713403</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11047,7 +11033,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11057,12 +11043,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11089,10 +11070,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124434324</v>
+        <v>124431501</v>
       </c>
       <c r="B84" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11101,31 +11082,40 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -11134,10 +11124,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524045</v>
+        <v>524175</v>
       </c>
       <c r="R84" t="n">
-        <v>6713403</v>
+        <v>6713573</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11169,7 +11159,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11179,7 +11169,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11720,7 +11715,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124431501</v>
+        <v>124434100</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -11755,7 +11750,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11768,16 +11763,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524175</v>
+        <v>524042</v>
       </c>
       <c r="R89" t="n">
-        <v>6713573</v>
+        <v>6713423</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -10827,7 +10827,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124431841</v>
+        <v>124433963</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524168</v>
+        <v>524033</v>
       </c>
       <c r="R82" t="n">
-        <v>6713526</v>
+        <v>6713451</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11070,7 +11070,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124431501</v>
+        <v>124432135</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11105,7 +11105,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11124,10 +11124,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524175</v>
+        <v>524180</v>
       </c>
       <c r="R84" t="n">
-        <v>6713573</v>
+        <v>6713485</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11169,12 +11169,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11201,7 +11196,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124432412</v>
+        <v>124435133</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11236,7 +11231,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11249,16 +11244,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524183</v>
+        <v>523934</v>
       </c>
       <c r="R85" t="n">
-        <v>6713449</v>
+        <v>6713790</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11290,7 +11290,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11300,7 +11300,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11327,7 +11332,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124433963</v>
+        <v>124431841</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11362,7 +11367,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11381,10 +11386,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524033</v>
+        <v>524168</v>
       </c>
       <c r="R86" t="n">
-        <v>6713451</v>
+        <v>6713526</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11416,7 +11421,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11426,7 +11431,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11453,7 +11458,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124435133</v>
+        <v>124432412</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -11488,7 +11493,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11501,21 +11506,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523934</v>
+        <v>524183</v>
       </c>
       <c r="R87" t="n">
-        <v>6713790</v>
+        <v>6713449</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11547,7 +11547,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11557,12 +11557,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>20:13</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>En vinterståndare.</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11589,7 +11584,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124432135</v>
+        <v>124434100</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -11624,7 +11619,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11637,16 +11632,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524180</v>
+        <v>524042</v>
       </c>
       <c r="R88" t="n">
-        <v>6713485</v>
+        <v>6713423</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11678,7 +11678,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11688,7 +11688,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11715,7 +11720,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124434100</v>
+        <v>124431501</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -11750,7 +11755,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11763,21 +11768,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524042</v>
+        <v>524175</v>
       </c>
       <c r="R89" t="n">
-        <v>6713423</v>
+        <v>6713573</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -10953,10 +10953,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124434324</v>
+        <v>124434100</v>
       </c>
       <c r="B83" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10965,31 +10965,45 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10998,10 +11012,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524045</v>
+        <v>524042</v>
       </c>
       <c r="R83" t="n">
-        <v>6713403</v>
+        <v>6713423</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11033,7 +11047,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11043,7 +11057,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11070,7 +11089,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124432135</v>
+        <v>124431501</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11105,7 +11124,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11124,10 +11143,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524180</v>
+        <v>524175</v>
       </c>
       <c r="R84" t="n">
-        <v>6713485</v>
+        <v>6713573</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11159,7 +11178,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11169,7 +11188,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11332,7 +11356,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124431841</v>
+        <v>124432412</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11367,7 +11391,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11386,10 +11410,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524168</v>
+        <v>524183</v>
       </c>
       <c r="R86" t="n">
-        <v>6713526</v>
+        <v>6713449</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11421,7 +11445,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11431,7 +11455,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11458,7 +11482,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124432412</v>
+        <v>124431841</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -11493,7 +11517,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11512,10 +11536,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524183</v>
+        <v>524168</v>
       </c>
       <c r="R87" t="n">
-        <v>6713449</v>
+        <v>6713526</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11547,7 +11571,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11557,7 +11581,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11584,10 +11608,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124434100</v>
+        <v>124434324</v>
       </c>
       <c r="B88" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11596,45 +11620,31 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11643,10 +11653,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524042</v>
+        <v>524045</v>
       </c>
       <c r="R88" t="n">
-        <v>6713423</v>
+        <v>6713403</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11678,7 +11688,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11688,12 +11698,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11720,7 +11725,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124431501</v>
+        <v>124432135</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -11755,7 +11760,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11774,10 +11779,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524175</v>
+        <v>524180</v>
       </c>
       <c r="R89" t="n">
-        <v>6713573</v>
+        <v>6713485</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11809,7 +11814,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11819,12 +11824,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -10953,7 +10953,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124434100</v>
+        <v>124435133</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -11008,14 +11008,14 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524042</v>
+        <v>523934</v>
       </c>
       <c r="R83" t="n">
-        <v>6713423</v>
+        <v>6713790</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11047,7 +11047,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11089,7 +11089,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124431501</v>
+        <v>124434100</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11137,16 +11137,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524175</v>
+        <v>524042</v>
       </c>
       <c r="R84" t="n">
-        <v>6713573</v>
+        <v>6713423</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11178,7 +11183,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11188,12 +11193,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11220,10 +11225,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124435133</v>
+        <v>124434324</v>
       </c>
       <c r="B85" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11232,57 +11237,43 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523934</v>
+        <v>524045</v>
       </c>
       <c r="R85" t="n">
-        <v>6713790</v>
+        <v>6713403</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11314,7 +11305,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11324,12 +11315,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>20:13</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>En vinterståndare.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11356,7 +11342,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124432412</v>
+        <v>124431841</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11391,7 +11377,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11410,10 +11396,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524183</v>
+        <v>524168</v>
       </c>
       <c r="R86" t="n">
-        <v>6713449</v>
+        <v>6713526</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11445,7 +11431,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11455,7 +11441,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11482,7 +11468,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124431841</v>
+        <v>124432412</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -11517,7 +11503,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11536,10 +11522,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524168</v>
+        <v>524183</v>
       </c>
       <c r="R87" t="n">
-        <v>6713526</v>
+        <v>6713449</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11571,7 +11557,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11581,7 +11567,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11608,10 +11594,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124434324</v>
+        <v>124431501</v>
       </c>
       <c r="B88" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11620,31 +11606,40 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11653,10 +11648,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524045</v>
+        <v>524175</v>
       </c>
       <c r="R88" t="n">
-        <v>6713403</v>
+        <v>6713573</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11688,7 +11683,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11698,7 +11693,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -10827,7 +10827,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124433963</v>
+        <v>124431841</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524033</v>
+        <v>524168</v>
       </c>
       <c r="R82" t="n">
-        <v>6713451</v>
+        <v>6713526</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10953,7 +10953,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124435133</v>
+        <v>124432135</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -11001,21 +11001,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523934</v>
+        <v>524180</v>
       </c>
       <c r="R83" t="n">
-        <v>6713790</v>
+        <v>6713485</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11047,7 +11042,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11057,12 +11052,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>20:13</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>En vinterståndare.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11089,7 +11079,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124434100</v>
+        <v>124435133</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11124,7 +11114,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11144,14 +11134,14 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524042</v>
+        <v>523934</v>
       </c>
       <c r="R84" t="n">
-        <v>6713423</v>
+        <v>6713790</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11183,7 +11173,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11193,12 +11183,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11225,10 +11215,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124434324</v>
+        <v>124433963</v>
       </c>
       <c r="B85" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -11237,31 +11227,40 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -11270,10 +11269,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524045</v>
+        <v>524033</v>
       </c>
       <c r="R85" t="n">
-        <v>6713403</v>
+        <v>6713451</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11305,7 +11304,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11315,7 +11314,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11342,7 +11341,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124431841</v>
+        <v>124434100</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11377,7 +11376,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11390,16 +11389,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524168</v>
+        <v>524042</v>
       </c>
       <c r="R86" t="n">
-        <v>6713526</v>
+        <v>6713423</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11431,7 +11435,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11441,7 +11445,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11594,10 +11603,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124431501</v>
+        <v>124434324</v>
       </c>
       <c r="B88" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11606,40 +11615,31 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11648,10 +11648,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524175</v>
+        <v>524045</v>
       </c>
       <c r="R88" t="n">
-        <v>6713573</v>
+        <v>6713403</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11683,7 +11683,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11693,12 +11693,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11725,7 +11720,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124432135</v>
+        <v>124431501</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -11760,7 +11755,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11779,10 +11774,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524180</v>
+        <v>524175</v>
       </c>
       <c r="R89" t="n">
-        <v>6713485</v>
+        <v>6713573</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11814,7 +11809,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11824,7 +11819,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -10827,7 +10827,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124431841</v>
+        <v>124432135</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524168</v>
+        <v>524180</v>
       </c>
       <c r="R82" t="n">
-        <v>6713526</v>
+        <v>6713485</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10953,7 +10953,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124432135</v>
+        <v>124432412</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -11007,10 +11007,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524180</v>
+        <v>524183</v>
       </c>
       <c r="R83" t="n">
-        <v>6713485</v>
+        <v>6713449</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11079,10 +11079,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124435133</v>
+        <v>124434324</v>
       </c>
       <c r="B84" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11091,57 +11091,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523934</v>
+        <v>524045</v>
       </c>
       <c r="R84" t="n">
-        <v>6713790</v>
+        <v>6713403</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11173,7 +11159,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11183,12 +11169,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>20:13</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>En vinterståndare.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11215,7 +11196,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124433963</v>
+        <v>124431841</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11250,7 +11231,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11269,10 +11250,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524033</v>
+        <v>524168</v>
       </c>
       <c r="R85" t="n">
-        <v>6713451</v>
+        <v>6713526</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11304,7 +11285,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11314,7 +11295,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11341,7 +11322,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124434100</v>
+        <v>124435133</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11376,7 +11357,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11396,14 +11377,14 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524042</v>
+        <v>523934</v>
       </c>
       <c r="R86" t="n">
-        <v>6713423</v>
+        <v>6713790</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11435,7 +11416,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11445,12 +11426,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11477,7 +11458,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124432412</v>
+        <v>124431501</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -11512,7 +11493,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11531,10 +11512,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524183</v>
+        <v>524175</v>
       </c>
       <c r="R87" t="n">
-        <v>6713449</v>
+        <v>6713573</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11566,7 +11547,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11576,7 +11557,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11603,10 +11589,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124434324</v>
+        <v>124433963</v>
       </c>
       <c r="B88" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11615,31 +11601,40 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11648,10 +11643,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524045</v>
+        <v>524033</v>
       </c>
       <c r="R88" t="n">
-        <v>6713403</v>
+        <v>6713451</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11683,7 +11678,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11693,7 +11688,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11720,7 +11715,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124431501</v>
+        <v>124434100</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -11755,7 +11750,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11768,16 +11763,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524175</v>
+        <v>524042</v>
       </c>
       <c r="R89" t="n">
-        <v>6713573</v>
+        <v>6713423</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -10827,7 +10827,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124432135</v>
+        <v>124432412</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524180</v>
+        <v>524183</v>
       </c>
       <c r="R82" t="n">
-        <v>6713485</v>
+        <v>6713449</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10953,10 +10953,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124432412</v>
+        <v>124434324</v>
       </c>
       <c r="B83" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10965,40 +10965,31 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -11007,10 +10998,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524183</v>
+        <v>524045</v>
       </c>
       <c r="R83" t="n">
-        <v>6713449</v>
+        <v>6713403</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11042,7 +11033,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11052,7 +11043,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11079,10 +11070,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124434324</v>
+        <v>124433963</v>
       </c>
       <c r="B84" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11091,31 +11082,40 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -11124,10 +11124,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524045</v>
+        <v>524033</v>
       </c>
       <c r="R84" t="n">
-        <v>6713403</v>
+        <v>6713451</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11159,7 +11159,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11196,7 +11196,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124431841</v>
+        <v>124432135</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11250,10 +11250,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524168</v>
+        <v>524180</v>
       </c>
       <c r="R85" t="n">
-        <v>6713526</v>
+        <v>6713485</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11285,7 +11285,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11322,7 +11322,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124435133</v>
+        <v>124434100</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11357,7 +11357,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11377,14 +11377,14 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523934</v>
+        <v>524042</v>
       </c>
       <c r="R86" t="n">
-        <v>6713790</v>
+        <v>6713423</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11426,12 +11426,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>En vinterståndare.</t>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11458,7 +11458,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124431501</v>
+        <v>124435133</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -11493,7 +11493,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11506,16 +11506,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524175</v>
+        <v>523934</v>
       </c>
       <c r="R87" t="n">
-        <v>6713573</v>
+        <v>6713790</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11547,7 +11552,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11557,12 +11562,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11589,7 +11594,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124433963</v>
+        <v>124431841</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -11624,7 +11629,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11643,10 +11648,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524033</v>
+        <v>524168</v>
       </c>
       <c r="R88" t="n">
-        <v>6713451</v>
+        <v>6713526</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11678,7 +11683,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11688,7 +11693,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11715,7 +11720,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124434100</v>
+        <v>124431501</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -11750,7 +11755,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11763,21 +11768,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524042</v>
+        <v>524175</v>
       </c>
       <c r="R89" t="n">
-        <v>6713423</v>
+        <v>6713573</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11809,7 +11809,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -10827,7 +10827,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124432412</v>
+        <v>124435133</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10875,16 +10875,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524183</v>
+        <v>523934</v>
       </c>
       <c r="R82" t="n">
-        <v>6713449</v>
+        <v>6713790</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10916,7 +10921,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10926,7 +10931,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10953,10 +10963,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124434324</v>
+        <v>124431841</v>
       </c>
       <c r="B83" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10965,31 +10975,40 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -10998,10 +11017,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524045</v>
+        <v>524168</v>
       </c>
       <c r="R83" t="n">
-        <v>6713403</v>
+        <v>6713526</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11033,7 +11052,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11043,7 +11062,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11070,7 +11089,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124433963</v>
+        <v>124432412</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11105,7 +11124,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11124,10 +11143,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524033</v>
+        <v>524183</v>
       </c>
       <c r="R84" t="n">
-        <v>6713451</v>
+        <v>6713449</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11159,7 +11178,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11169,7 +11188,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11196,7 +11215,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124432135</v>
+        <v>124433963</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11250,10 +11269,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524180</v>
+        <v>524033</v>
       </c>
       <c r="R85" t="n">
-        <v>6713485</v>
+        <v>6713451</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11285,7 +11304,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11295,7 +11314,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11322,7 +11341,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124434100</v>
+        <v>124431501</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11357,7 +11376,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11370,21 +11389,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524042</v>
+        <v>524175</v>
       </c>
       <c r="R86" t="n">
-        <v>6713423</v>
+        <v>6713573</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11416,7 +11430,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11426,12 +11440,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11458,7 +11472,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124435133</v>
+        <v>124434100</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -11493,7 +11507,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11513,14 +11527,14 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523934</v>
+        <v>524042</v>
       </c>
       <c r="R87" t="n">
-        <v>6713790</v>
+        <v>6713423</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11552,7 +11566,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11562,12 +11576,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>En vinterståndare.</t>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11594,10 +11608,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124431841</v>
+        <v>124434324</v>
       </c>
       <c r="B88" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11606,40 +11620,31 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11648,10 +11653,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524168</v>
+        <v>524045</v>
       </c>
       <c r="R88" t="n">
-        <v>6713526</v>
+        <v>6713403</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11683,7 +11688,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11693,7 +11698,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11720,7 +11725,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124431501</v>
+        <v>124432135</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -11755,7 +11760,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11774,10 +11779,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524175</v>
+        <v>524180</v>
       </c>
       <c r="R89" t="n">
-        <v>6713573</v>
+        <v>6713485</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11809,7 +11814,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11819,12 +11824,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -10827,10 +10827,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124435133</v>
+        <v>124434324</v>
       </c>
       <c r="B82" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10839,57 +10839,43 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523934</v>
+        <v>524045</v>
       </c>
       <c r="R82" t="n">
-        <v>6713790</v>
+        <v>6713403</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10921,7 +10907,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10931,12 +10917,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>20:13</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>En vinterståndare.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10963,7 +10944,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124431841</v>
+        <v>124432135</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -10998,7 +10979,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -11017,10 +10998,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524168</v>
+        <v>524180</v>
       </c>
       <c r="R83" t="n">
-        <v>6713526</v>
+        <v>6713485</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11052,7 +11033,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11062,7 +11043,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11089,7 +11070,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124432412</v>
+        <v>124435133</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11124,7 +11105,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11137,16 +11118,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524183</v>
+        <v>523934</v>
       </c>
       <c r="R84" t="n">
-        <v>6713449</v>
+        <v>6713790</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11178,7 +11164,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11188,7 +11174,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11215,7 +11206,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124433963</v>
+        <v>124431841</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11250,7 +11241,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11269,10 +11260,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524033</v>
+        <v>524168</v>
       </c>
       <c r="R85" t="n">
-        <v>6713451</v>
+        <v>6713526</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11304,7 +11295,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11314,7 +11305,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11608,10 +11599,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124434324</v>
+        <v>124433963</v>
       </c>
       <c r="B88" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11620,31 +11611,40 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11653,10 +11653,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524045</v>
+        <v>524033</v>
       </c>
       <c r="R88" t="n">
-        <v>6713403</v>
+        <v>6713451</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11725,7 +11725,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124432135</v>
+        <v>124432412</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11779,10 +11779,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524180</v>
+        <v>524183</v>
       </c>
       <c r="R89" t="n">
-        <v>6713485</v>
+        <v>6713449</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11814,7 +11814,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -10827,10 +10827,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124434324</v>
+        <v>124431841</v>
       </c>
       <c r="B82" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10839,31 +10839,40 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10872,10 +10881,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524045</v>
+        <v>524168</v>
       </c>
       <c r="R82" t="n">
-        <v>6713403</v>
+        <v>6713526</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10907,7 +10916,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10917,7 +10926,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10944,7 +10953,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124432135</v>
+        <v>124431501</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -10979,7 +10988,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -10998,10 +11007,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524180</v>
+        <v>524175</v>
       </c>
       <c r="R83" t="n">
-        <v>6713485</v>
+        <v>6713573</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11033,7 +11042,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11043,7 +11052,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11070,7 +11084,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124435133</v>
+        <v>124434100</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11105,7 +11119,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -11125,14 +11139,14 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523934</v>
+        <v>524042</v>
       </c>
       <c r="R84" t="n">
-        <v>6713790</v>
+        <v>6713423</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11164,7 +11178,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11174,12 +11188,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>En vinterståndare.</t>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11206,7 +11220,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124431841</v>
+        <v>124435133</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11241,7 +11255,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11254,16 +11268,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524168</v>
+        <v>523934</v>
       </c>
       <c r="R85" t="n">
-        <v>6713526</v>
+        <v>6713790</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11295,7 +11314,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11305,7 +11324,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11332,10 +11356,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124431501</v>
+        <v>124434324</v>
       </c>
       <c r="B86" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11344,40 +11368,31 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -11386,10 +11401,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524175</v>
+        <v>524045</v>
       </c>
       <c r="R86" t="n">
-        <v>6713573</v>
+        <v>6713403</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11421,7 +11436,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11431,12 +11446,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11463,7 +11473,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124434100</v>
+        <v>124432135</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -11498,7 +11508,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11511,21 +11521,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524042</v>
+        <v>524180</v>
       </c>
       <c r="R87" t="n">
-        <v>6713423</v>
+        <v>6713485</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11557,7 +11562,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11567,12 +11572,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD87" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -10953,7 +10953,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>124431501</v>
+        <v>124433963</v>
       </c>
       <c r="B83" t="n">
         <v>98101</v>
@@ -10988,7 +10988,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -11007,10 +11007,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>524175</v>
+        <v>524033</v>
       </c>
       <c r="R83" t="n">
-        <v>6713573</v>
+        <v>6713451</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -11052,12 +11052,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -11084,7 +11079,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124434100</v>
+        <v>124432412</v>
       </c>
       <c r="B84" t="n">
         <v>98101</v>
@@ -11132,21 +11127,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524042</v>
+        <v>524183</v>
       </c>
       <c r="R84" t="n">
-        <v>6713423</v>
+        <v>6713449</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11178,7 +11168,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11188,12 +11178,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11220,7 +11205,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124435133</v>
+        <v>124432135</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11255,7 +11240,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11268,21 +11253,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523934</v>
+        <v>524180</v>
       </c>
       <c r="R85" t="n">
-        <v>6713790</v>
+        <v>6713485</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11314,7 +11294,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11324,12 +11304,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>20:13</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>En vinterståndare.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11356,10 +11331,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124434324</v>
+        <v>124435133</v>
       </c>
       <c r="B86" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -11368,43 +11343,57 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524045</v>
+        <v>523934</v>
       </c>
       <c r="R86" t="n">
-        <v>6713403</v>
+        <v>6713790</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11436,7 +11425,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11446,7 +11435,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11473,7 +11467,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124432135</v>
+        <v>124431501</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -11508,7 +11502,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11527,10 +11521,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524180</v>
+        <v>524175</v>
       </c>
       <c r="R87" t="n">
-        <v>6713485</v>
+        <v>6713573</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11562,7 +11556,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11572,7 +11566,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11599,7 +11598,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124433963</v>
+        <v>124434100</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -11634,7 +11633,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11647,16 +11646,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524033</v>
+        <v>524042</v>
       </c>
       <c r="R88" t="n">
-        <v>6713451</v>
+        <v>6713423</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11688,7 +11692,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11698,7 +11702,12 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11725,10 +11734,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124432412</v>
+        <v>124434324</v>
       </c>
       <c r="B89" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11737,40 +11746,31 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11779,10 +11779,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524183</v>
+        <v>524045</v>
       </c>
       <c r="R89" t="n">
-        <v>6713449</v>
+        <v>6713403</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11814,7 +11814,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -10827,7 +10827,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124431841</v>
+        <v>124432412</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -10881,10 +10881,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524168</v>
+        <v>524183</v>
       </c>
       <c r="R82" t="n">
-        <v>6713526</v>
+        <v>6713449</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11079,10 +11079,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124432412</v>
+        <v>124434324</v>
       </c>
       <c r="B84" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11091,40 +11091,31 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -11133,10 +11124,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524183</v>
+        <v>524045</v>
       </c>
       <c r="R84" t="n">
-        <v>6713449</v>
+        <v>6713403</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11168,7 +11159,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11178,7 +11169,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11205,7 +11196,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124432135</v>
+        <v>124431501</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11240,7 +11231,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11259,10 +11250,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524180</v>
+        <v>524175</v>
       </c>
       <c r="R85" t="n">
-        <v>6713485</v>
+        <v>6713573</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11294,7 +11285,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11304,7 +11295,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11331,7 +11327,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124435133</v>
+        <v>124434100</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11366,7 +11362,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11386,14 +11382,14 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523934</v>
+        <v>524042</v>
       </c>
       <c r="R86" t="n">
-        <v>6713790</v>
+        <v>6713423</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11425,7 +11421,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11435,12 +11431,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>En vinterståndare.</t>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11467,7 +11463,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124431501</v>
+        <v>124435133</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -11502,7 +11498,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11515,16 +11511,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>524175</v>
+        <v>523934</v>
       </c>
       <c r="R87" t="n">
-        <v>6713573</v>
+        <v>6713790</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11556,7 +11557,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11566,12 +11567,12 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11598,7 +11599,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124434100</v>
+        <v>124431841</v>
       </c>
       <c r="B88" t="n">
         <v>98101</v>
@@ -11633,7 +11634,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11646,21 +11647,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524042</v>
+        <v>524168</v>
       </c>
       <c r="R88" t="n">
-        <v>6713423</v>
+        <v>6713526</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11692,7 +11688,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11702,12 +11698,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:44</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11734,10 +11725,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124434324</v>
+        <v>124432135</v>
       </c>
       <c r="B89" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -11746,31 +11737,40 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -11779,10 +11779,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524045</v>
+        <v>524180</v>
       </c>
       <c r="R89" t="n">
-        <v>6713403</v>
+        <v>6713485</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11814,7 +11814,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -10827,7 +10827,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>124432412</v>
+        <v>124434100</v>
       </c>
       <c r="B82" t="n">
         <v>98101</v>
@@ -10875,16 +10875,21 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>524183</v>
+        <v>524042</v>
       </c>
       <c r="R82" t="n">
-        <v>6713449</v>
+        <v>6713423</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10916,7 +10921,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:44</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10926,7 +10931,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>19:44</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Över ca 5 kv/dm.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -11079,10 +11089,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>124434324</v>
+        <v>124435133</v>
       </c>
       <c r="B84" t="n">
-        <v>8447</v>
+        <v>98101</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -11091,43 +11101,57 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sumpskogen, Sumpskogen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>524045</v>
+        <v>523934</v>
       </c>
       <c r="R84" t="n">
-        <v>6713403</v>
+        <v>6713790</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11159,7 +11183,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -11169,7 +11193,12 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:13</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>En vinterståndare.</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11196,7 +11225,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124431501</v>
+        <v>124432135</v>
       </c>
       <c r="B85" t="n">
         <v>98101</v>
@@ -11231,7 +11260,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -11250,10 +11279,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>524175</v>
+        <v>524180</v>
       </c>
       <c r="R85" t="n">
-        <v>6713573</v>
+        <v>6713485</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11285,7 +11314,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -11295,12 +11324,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Under senvuxen klen gran.</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -11327,7 +11351,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124434100</v>
+        <v>124431501</v>
       </c>
       <c r="B86" t="n">
         <v>98101</v>
@@ -11362,7 +11386,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -11375,21 +11399,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>524042</v>
+        <v>524175</v>
       </c>
       <c r="R86" t="n">
-        <v>6713423</v>
+        <v>6713573</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11421,7 +11440,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11431,12 +11450,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>19:44</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Över ca 5 kv/dm.</t>
+          <t>Under senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11463,7 +11482,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124435133</v>
+        <v>124431841</v>
       </c>
       <c r="B87" t="n">
         <v>98101</v>
@@ -11498,7 +11517,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11511,21 +11530,16 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523934</v>
+        <v>524168</v>
       </c>
       <c r="R87" t="n">
-        <v>6713790</v>
+        <v>6713526</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11557,7 +11571,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11567,12 +11581,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>20:13</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>En vinterståndare.</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11599,10 +11608,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124431841</v>
+        <v>124434324</v>
       </c>
       <c r="B88" t="n">
-        <v>98101</v>
+        <v>8447</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -11611,40 +11620,31 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -11653,10 +11653,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>524168</v>
+        <v>524045</v>
       </c>
       <c r="R88" t="n">
-        <v>6713526</v>
+        <v>6713403</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11725,7 +11725,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124432135</v>
+        <v>124432412</v>
       </c>
       <c r="B89" t="n">
         <v>98101</v>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11779,10 +11779,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>524180</v>
+        <v>524183</v>
       </c>
       <c r="R89" t="n">
-        <v>6713485</v>
+        <v>6713449</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11814,7 +11814,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -11854,7 +11854,7 @@
         <v>124711417</v>
       </c>
       <c r="B90" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AY92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11975,6 +11975,242 @@
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>125899247</v>
+      </c>
+      <c r="B91" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>524042</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6713304</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>125899180</v>
+      </c>
+      <c r="B92" t="n">
+        <v>58125</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100058</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mindre flugsnappare</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Ficedula parva</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1794)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>524025</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6713299</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -11980,7 +11980,7 @@
         <v>125899247</v>
       </c>
       <c r="B91" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -11980,7 +11980,7 @@
         <v>125899247</v>
       </c>
       <c r="B91" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>125899180</v>
       </c>
       <c r="B92" t="n">
-        <v>58125</v>
+        <v>58126</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -11980,7 +11980,7 @@
         <v>125899247</v>
       </c>
       <c r="B91" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -11980,7 +11980,7 @@
         <v>125899247</v>
       </c>
       <c r="B91" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -11980,7 +11980,7 @@
         <v>125899247</v>
       </c>
       <c r="B91" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -11980,7 +11980,7 @@
         <v>125899247</v>
       </c>
       <c r="B91" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>125899180</v>
       </c>
       <c r="B92" t="n">
-        <v>58126</v>
+        <v>58127</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AY93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12211,6 +12211,113 @@
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>126231015</v>
+      </c>
+      <c r="B93" t="n">
+        <v>91236</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>524063</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6713991</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -11980,7 +11980,7 @@
         <v>125899247</v>
       </c>
       <c r="B91" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -11980,7 +11980,7 @@
         <v>125899247</v>
       </c>
       <c r="B91" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>126231015</v>
       </c>
       <c r="B93" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -11980,7 +11980,7 @@
         <v>125899247</v>
       </c>
       <c r="B91" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>125899180</v>
       </c>
       <c r="B92" t="n">
-        <v>58127</v>
+        <v>58131</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>126231015</v>
       </c>
       <c r="B93" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -11980,7 +11980,7 @@
         <v>125899247</v>
       </c>
       <c r="B91" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -11980,7 +11980,7 @@
         <v>125899247</v>
       </c>
       <c r="B91" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
         <v>125899180</v>
       </c>
       <c r="B92" t="n">
-        <v>58131</v>
+        <v>58134</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12216,7 +12216,7 @@
         <v>126231015</v>
       </c>
       <c r="B93" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -12323,7 +12323,7 @@
         <v>126936299</v>
       </c>
       <c r="B94" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>126934586</v>
       </c>
       <c r="B95" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>126934603</v>
       </c>
       <c r="B96" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>126934577</v>
       </c>
       <c r="B97" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>126934164</v>
       </c>
       <c r="B98" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>126933611</v>
       </c>
       <c r="B99" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>126933275</v>
       </c>
       <c r="B100" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>126936539</v>
       </c>
       <c r="B101" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>126932846</v>
       </c>
       <c r="B102" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>126933692</v>
       </c>
       <c r="B103" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>126932450</v>
       </c>
       <c r="B104" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>126933326</v>
       </c>
       <c r="B105" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>126962844</v>
       </c>
       <c r="B106" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>126963368</v>
       </c>
       <c r="B107" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>126961591</v>
       </c>
       <c r="B108" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>126963263</v>
       </c>
       <c r="B109" t="n">
-        <v>91541</v>
+        <v>91615</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>126962269</v>
       </c>
       <c r="B110" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>126963427</v>
       </c>
       <c r="B111" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>126962421</v>
       </c>
       <c r="B112" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>126963583</v>
       </c>
       <c r="B113" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -12323,7 +12323,7 @@
         <v>126936299</v>
       </c>
       <c r="B94" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>126934586</v>
       </c>
       <c r="B95" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>126934603</v>
       </c>
       <c r="B96" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>126934577</v>
       </c>
       <c r="B97" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>126934164</v>
       </c>
       <c r="B98" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>126933611</v>
       </c>
       <c r="B99" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>126933275</v>
       </c>
       <c r="B100" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>126936539</v>
       </c>
       <c r="B101" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>126932846</v>
       </c>
       <c r="B102" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>126933692</v>
       </c>
       <c r="B103" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>126932450</v>
       </c>
       <c r="B104" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>126933326</v>
       </c>
       <c r="B105" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>126962844</v>
       </c>
       <c r="B106" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>126963368</v>
       </c>
       <c r="B107" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>126961591</v>
       </c>
       <c r="B108" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>126963263</v>
       </c>
       <c r="B109" t="n">
-        <v>91615</v>
+        <v>91621</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>126962269</v>
       </c>
       <c r="B110" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>126963427</v>
       </c>
       <c r="B111" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>126962421</v>
       </c>
       <c r="B112" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>126963583</v>
       </c>
       <c r="B113" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -12323,7 +12323,7 @@
         <v>126936299</v>
       </c>
       <c r="B94" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>126934586</v>
       </c>
       <c r="B95" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>126934603</v>
       </c>
       <c r="B96" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>126934577</v>
       </c>
       <c r="B97" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>126934164</v>
       </c>
       <c r="B98" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>126933611</v>
       </c>
       <c r="B99" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>126933275</v>
       </c>
       <c r="B100" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>126936539</v>
       </c>
       <c r="B101" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>126932846</v>
       </c>
       <c r="B102" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>126933692</v>
       </c>
       <c r="B103" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>126932450</v>
       </c>
       <c r="B104" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>126933326</v>
       </c>
       <c r="B105" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>126962844</v>
       </c>
       <c r="B106" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>126963368</v>
       </c>
       <c r="B107" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>126961591</v>
       </c>
       <c r="B108" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>126963263</v>
       </c>
       <c r="B109" t="n">
-        <v>91621</v>
+        <v>91622</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>126962269</v>
       </c>
       <c r="B110" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>126963427</v>
       </c>
       <c r="B111" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>126962421</v>
       </c>
       <c r="B112" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>126963583</v>
       </c>
       <c r="B113" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -12323,7 +12323,7 @@
         <v>126936299</v>
       </c>
       <c r="B94" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>126934586</v>
       </c>
       <c r="B95" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>126934603</v>
       </c>
       <c r="B96" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>126934577</v>
       </c>
       <c r="B97" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>126934164</v>
       </c>
       <c r="B98" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>126933611</v>
       </c>
       <c r="B99" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>126933275</v>
       </c>
       <c r="B100" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>126936539</v>
       </c>
       <c r="B101" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>126932846</v>
       </c>
       <c r="B102" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>126933692</v>
       </c>
       <c r="B103" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>126932450</v>
       </c>
       <c r="B104" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>126933326</v>
       </c>
       <c r="B105" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>126962844</v>
       </c>
       <c r="B106" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>126963368</v>
       </c>
       <c r="B107" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>126961591</v>
       </c>
       <c r="B108" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>126963263</v>
       </c>
       <c r="B109" t="n">
-        <v>91622</v>
+        <v>91626</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>126962269</v>
       </c>
       <c r="B110" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>126963427</v>
       </c>
       <c r="B111" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>126962421</v>
       </c>
       <c r="B112" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>126963583</v>
       </c>
       <c r="B113" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -12323,7 +12323,7 @@
         <v>126936299</v>
       </c>
       <c r="B94" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>126934586</v>
       </c>
       <c r="B95" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>126934603</v>
       </c>
       <c r="B96" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>126934577</v>
       </c>
       <c r="B97" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>126934164</v>
       </c>
       <c r="B98" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>126933611</v>
       </c>
       <c r="B99" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>126933275</v>
       </c>
       <c r="B100" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>126936539</v>
       </c>
       <c r="B101" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>126932846</v>
       </c>
       <c r="B102" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>126933692</v>
       </c>
       <c r="B103" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>126932450</v>
       </c>
       <c r="B104" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>126933326</v>
       </c>
       <c r="B105" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>126962844</v>
       </c>
       <c r="B106" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>126963368</v>
       </c>
       <c r="B107" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>126961591</v>
       </c>
       <c r="B108" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>126962269</v>
       </c>
       <c r="B110" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>126963427</v>
       </c>
       <c r="B111" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>126962421</v>
       </c>
       <c r="B112" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>126963583</v>
       </c>
       <c r="B113" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY113"/>
+  <dimension ref="A1:AY115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14756,6 +14756,238 @@
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>127727170</v>
+      </c>
+      <c r="B114" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>524154</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6713653</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>127727173</v>
+      </c>
+      <c r="B115" t="n">
+        <v>98448</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Banvallen, Banvallen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>524154</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6713656</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -12323,7 +12323,7 @@
         <v>126936299</v>
       </c>
       <c r="B94" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>126934586</v>
       </c>
       <c r="B95" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12568,7 +12568,7 @@
         <v>126934603</v>
       </c>
       <c r="B96" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>126934577</v>
       </c>
       <c r="B97" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12810,7 +12810,7 @@
         <v>126934164</v>
       </c>
       <c r="B98" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>126933611</v>
       </c>
       <c r="B99" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>126933275</v>
       </c>
       <c r="B100" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>126936539</v>
       </c>
       <c r="B101" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>126932846</v>
       </c>
       <c r="B102" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>126933692</v>
       </c>
       <c r="B103" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>126932450</v>
       </c>
       <c r="B104" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>126933326</v>
       </c>
       <c r="B105" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>126962844</v>
       </c>
       <c r="B106" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>126963368</v>
       </c>
       <c r="B107" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>126961591</v>
       </c>
       <c r="B108" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>126963263</v>
       </c>
       <c r="B109" t="n">
-        <v>91626</v>
+        <v>91628</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>126962269</v>
       </c>
       <c r="B110" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>126963427</v>
       </c>
       <c r="B111" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>126962421</v>
       </c>
       <c r="B112" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>126963583</v>
       </c>
       <c r="B113" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>127727170</v>
       </c>
       <c r="B114" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>127727173</v>
       </c>
       <c r="B115" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -12565,7 +12565,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126934603</v>
+        <v>126934577</v>
       </c>
       <c r="B96" t="n">
         <v>98450</v>
@@ -12614,10 +12614,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524034</v>
+        <v>524036</v>
       </c>
       <c r="R96" t="n">
-        <v>6713296</v>
+        <v>6713293</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12686,7 +12686,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126934577</v>
+        <v>126934603</v>
       </c>
       <c r="B97" t="n">
         <v>98450</v>
@@ -12735,10 +12735,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>524036</v>
+        <v>524034</v>
       </c>
       <c r="R97" t="n">
-        <v>6713293</v>
+        <v>6713296</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -14761,7 +14761,7 @@
         <v>127727170</v>
       </c>
       <c r="B114" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>127727173</v>
       </c>
       <c r="B115" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -14761,7 +14761,7 @@
         <v>127727170</v>
       </c>
       <c r="B114" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>127727173</v>
       </c>
       <c r="B115" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -14761,7 +14761,7 @@
         <v>127727170</v>
       </c>
       <c r="B114" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>127727173</v>
       </c>
       <c r="B115" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -14761,7 +14761,7 @@
         <v>127727170</v>
       </c>
       <c r="B114" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>127727173</v>
       </c>
       <c r="B115" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY115"/>
+  <dimension ref="A1:AY118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14988,6 +14988,341 @@
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>128217774</v>
+      </c>
+      <c r="B116" t="n">
+        <v>92652</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>524149</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6713406</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>128217698</v>
+      </c>
+      <c r="B117" t="n">
+        <v>92674</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>524146</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6713402</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Större antal runt gran.</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>128217134</v>
+      </c>
+      <c r="B118" t="n">
+        <v>57832</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Banvallen, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>524130</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6713667</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -14761,7 +14761,7 @@
         <v>127727170</v>
       </c>
       <c r="B114" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>127727173</v>
       </c>
       <c r="B115" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>128217774</v>
       </c>
       <c r="B116" t="n">
-        <v>92652</v>
+        <v>92653</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>128217698</v>
       </c>
       <c r="B117" t="n">
-        <v>92674</v>
+        <v>92675</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -14761,7 +14761,7 @@
         <v>127727170</v>
       </c>
       <c r="B114" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>127727173</v>
       </c>
       <c r="B115" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>128217774</v>
       </c>
       <c r="B116" t="n">
-        <v>92653</v>
+        <v>92654</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>128217698</v>
       </c>
       <c r="B117" t="n">
-        <v>92675</v>
+        <v>92676</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -14761,7 +14761,7 @@
         <v>127727170</v>
       </c>
       <c r="B114" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>127727173</v>
       </c>
       <c r="B115" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>128217774</v>
       </c>
       <c r="B116" t="n">
-        <v>92654</v>
+        <v>92662</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>128217698</v>
       </c>
       <c r="B117" t="n">
-        <v>92676</v>
+        <v>92684</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>128217134</v>
       </c>
       <c r="B118" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -14761,7 +14761,7 @@
         <v>127727170</v>
       </c>
       <c r="B114" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>127727173</v>
       </c>
       <c r="B115" t="n">
-        <v>98478</v>
+        <v>98490</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>128217774</v>
       </c>
       <c r="B116" t="n">
-        <v>92662</v>
+        <v>92754</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>128217698</v>
       </c>
       <c r="B117" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>128217134</v>
       </c>
       <c r="B118" t="n">
-        <v>57833</v>
+        <v>57845</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -14993,7 +14993,7 @@
         <v>128217774</v>
       </c>
       <c r="B116" t="n">
-        <v>92754</v>
+        <v>92766</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>128217698</v>
       </c>
       <c r="B117" t="n">
-        <v>92776</v>
+        <v>92788</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>128217134</v>
       </c>
       <c r="B118" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -14993,7 +14993,7 @@
         <v>128217774</v>
       </c>
       <c r="B116" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>128217698</v>
       </c>
       <c r="B117" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -14993,7 +14993,7 @@
         <v>128217774</v>
       </c>
       <c r="B116" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>128217698</v>
       </c>
       <c r="B117" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -14993,7 +14993,7 @@
         <v>128217774</v>
       </c>
       <c r="B116" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>128217698</v>
       </c>
       <c r="B117" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>128217134</v>
       </c>
       <c r="B118" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15441,10 +15441,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B120" t="n">
-        <v>92456</v>
+        <v>91293</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15452,43 +15452,43 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R120" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15557,45 +15557,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B121" t="n">
-        <v>91520</v>
+        <v>92456</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R121" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15627,7 +15636,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15637,12 +15646,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15669,54 +15673,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B122" t="n">
-        <v>91293</v>
+        <v>91520</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R122" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15748,7 +15743,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15758,7 +15753,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD122" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15328,7 +15328,7 @@
         <v>129066471</v>
       </c>
       <c r="B119" t="n">
-        <v>92847</v>
+        <v>92852</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15441,54 +15441,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B120" t="n">
-        <v>91293</v>
+        <v>91523</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R120" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15520,7 +15511,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15530,7 +15521,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15557,10 +15553,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B121" t="n">
-        <v>92456</v>
+        <v>91296</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15568,43 +15564,43 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R121" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15636,7 +15632,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15646,7 +15642,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15673,45 +15669,54 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B122" t="n">
-        <v>91520</v>
+        <v>92461</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R122" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15743,7 +15748,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15753,12 +15758,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15788,7 +15788,7 @@
         <v>129116978</v>
       </c>
       <c r="B123" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>129114973</v>
       </c>
       <c r="B124" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>129116918</v>
       </c>
       <c r="B125" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>129115572</v>
       </c>
       <c r="B126" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15328,7 +15328,7 @@
         <v>129066471</v>
       </c>
       <c r="B119" t="n">
-        <v>92852</v>
+        <v>92855</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15441,45 +15441,54 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065420</v>
+        <v>129065356</v>
       </c>
       <c r="B120" t="n">
-        <v>91523</v>
+        <v>91299</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524074</v>
+        <v>524081</v>
       </c>
       <c r="R120" t="n">
-        <v>6713878</v>
+        <v>6713859</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15511,7 +15520,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15521,12 +15530,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15553,54 +15557,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B121" t="n">
-        <v>91296</v>
+        <v>91526</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R121" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15632,7 +15627,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15642,7 +15637,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15672,7 +15672,7 @@
         <v>129064961</v>
       </c>
       <c r="B122" t="n">
-        <v>92461</v>
+        <v>92464</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>129116978</v>
       </c>
       <c r="B123" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>129114973</v>
       </c>
       <c r="B124" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>129116918</v>
       </c>
       <c r="B125" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>129115572</v>
       </c>
       <c r="B126" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15441,54 +15441,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B120" t="n">
-        <v>91299</v>
+        <v>91526</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R120" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15520,7 +15511,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15530,7 +15521,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15557,45 +15553,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B121" t="n">
-        <v>91526</v>
+        <v>92464</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R121" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15627,7 +15632,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15637,12 +15642,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15669,10 +15669,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B122" t="n">
-        <v>92464</v>
+        <v>91299</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15680,43 +15680,43 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R122" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15748,7 +15748,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD122" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15441,45 +15441,54 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B120" t="n">
-        <v>91526</v>
+        <v>92464</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R120" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15511,7 +15520,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15521,12 +15530,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15553,54 +15557,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129064961</v>
+        <v>129065420</v>
       </c>
       <c r="B121" t="n">
-        <v>92464</v>
+        <v>91526</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524024</v>
+        <v>524074</v>
       </c>
       <c r="R121" t="n">
-        <v>6713938</v>
+        <v>6713878</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15632,7 +15627,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15642,7 +15637,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15441,54 +15441,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129064961</v>
+        <v>129065420</v>
       </c>
       <c r="B120" t="n">
-        <v>92464</v>
+        <v>91526</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524024</v>
+        <v>524074</v>
       </c>
       <c r="R120" t="n">
-        <v>6713938</v>
+        <v>6713878</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15520,7 +15511,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15530,7 +15521,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15557,45 +15553,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129065420</v>
+        <v>129065356</v>
       </c>
       <c r="B121" t="n">
-        <v>91526</v>
+        <v>91299</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524074</v>
+        <v>524081</v>
       </c>
       <c r="R121" t="n">
-        <v>6713878</v>
+        <v>6713859</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15627,7 +15632,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15637,12 +15642,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15669,10 +15669,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129065356</v>
+        <v>129064961</v>
       </c>
       <c r="B122" t="n">
-        <v>91299</v>
+        <v>92464</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15680,43 +15680,43 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524081</v>
+        <v>524024</v>
       </c>
       <c r="R122" t="n">
-        <v>6713859</v>
+        <v>6713938</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15748,7 +15748,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD122" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15328,7 +15328,7 @@
         <v>129066471</v>
       </c>
       <c r="B119" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>129065420</v>
       </c>
       <c r="B120" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15553,10 +15553,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129065356</v>
+        <v>129064961</v>
       </c>
       <c r="B121" t="n">
-        <v>91299</v>
+        <v>92471</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15564,43 +15564,43 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524081</v>
+        <v>524024</v>
       </c>
       <c r="R121" t="n">
-        <v>6713859</v>
+        <v>6713938</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15669,10 +15669,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B122" t="n">
-        <v>92464</v>
+        <v>91305</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15680,43 +15680,43 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R122" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15748,7 +15748,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15788,7 +15788,7 @@
         <v>129116978</v>
       </c>
       <c r="B123" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>129114973</v>
       </c>
       <c r="B124" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>129116918</v>
       </c>
       <c r="B125" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>129115572</v>
       </c>
       <c r="B126" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15328,7 +15328,7 @@
         <v>129066471</v>
       </c>
       <c r="B119" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>129065420</v>
       </c>
       <c r="B120" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15553,10 +15553,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B121" t="n">
-        <v>92471</v>
+        <v>91312</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15564,43 +15564,43 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R121" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15669,10 +15669,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129065356</v>
+        <v>129064961</v>
       </c>
       <c r="B122" t="n">
-        <v>91305</v>
+        <v>92478</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15680,43 +15680,43 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524081</v>
+        <v>524024</v>
       </c>
       <c r="R122" t="n">
-        <v>6713859</v>
+        <v>6713938</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15748,7 +15748,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15788,7 +15788,7 @@
         <v>129116978</v>
       </c>
       <c r="B123" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>129114973</v>
       </c>
       <c r="B124" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>129116918</v>
       </c>
       <c r="B125" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>129115572</v>
       </c>
       <c r="B126" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15328,7 +15328,7 @@
         <v>129066471</v>
       </c>
       <c r="B119" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15441,45 +15441,54 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B120" t="n">
-        <v>91540</v>
+        <v>92480</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R120" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15511,7 +15520,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15521,12 +15530,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15553,54 +15557,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B121" t="n">
-        <v>91312</v>
+        <v>91542</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R121" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15632,7 +15627,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15642,7 +15637,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15669,10 +15669,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B122" t="n">
-        <v>92478</v>
+        <v>91314</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15680,43 +15680,43 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R122" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15748,7 +15748,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15788,7 +15788,7 @@
         <v>129116978</v>
       </c>
       <c r="B123" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>129114973</v>
       </c>
       <c r="B124" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>129116918</v>
       </c>
       <c r="B125" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>129115572</v>
       </c>
       <c r="B126" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15441,10 +15441,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B120" t="n">
-        <v>92480</v>
+        <v>91314</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15452,43 +15452,43 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R120" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15669,10 +15669,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129065356</v>
+        <v>129064961</v>
       </c>
       <c r="B122" t="n">
-        <v>91314</v>
+        <v>92480</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15680,43 +15680,43 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524081</v>
+        <v>524024</v>
       </c>
       <c r="R122" t="n">
-        <v>6713859</v>
+        <v>6713938</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15748,7 +15748,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD122" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15328,7 +15328,7 @@
         <v>129066471</v>
       </c>
       <c r="B119" t="n">
-        <v>92871</v>
+        <v>92857</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15441,54 +15441,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B120" t="n">
-        <v>91314</v>
+        <v>91540</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R120" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15520,7 +15511,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15530,7 +15521,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15557,45 +15553,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129065420</v>
+        <v>129065356</v>
       </c>
       <c r="B121" t="n">
-        <v>91542</v>
+        <v>91313</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524074</v>
+        <v>524081</v>
       </c>
       <c r="R121" t="n">
-        <v>6713878</v>
+        <v>6713859</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15627,7 +15632,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15637,12 +15642,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15672,7 +15672,7 @@
         <v>129064961</v>
       </c>
       <c r="B122" t="n">
-        <v>92480</v>
+        <v>92494</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>129116978</v>
       </c>
       <c r="B123" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>129114973</v>
       </c>
       <c r="B124" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>129116918</v>
       </c>
       <c r="B125" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>129115572</v>
       </c>
       <c r="B126" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15328,7 +15328,7 @@
         <v>129066471</v>
       </c>
       <c r="B119" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15441,45 +15441,54 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B120" t="n">
-        <v>91540</v>
+        <v>92495</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R120" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15511,7 +15520,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15521,12 +15530,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15553,54 +15557,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B121" t="n">
-        <v>91313</v>
+        <v>91540</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R121" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15632,7 +15627,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15642,7 +15637,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15669,10 +15669,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B122" t="n">
-        <v>92494</v>
+        <v>91313</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15680,43 +15680,43 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R122" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15748,7 +15748,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15788,7 +15788,7 @@
         <v>129116978</v>
       </c>
       <c r="B123" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>129114973</v>
       </c>
       <c r="B124" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>129116918</v>
       </c>
       <c r="B125" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>129115572</v>
       </c>
       <c r="B126" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15441,54 +15441,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129064961</v>
+        <v>129065420</v>
       </c>
       <c r="B120" t="n">
-        <v>92495</v>
+        <v>91540</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524024</v>
+        <v>524074</v>
       </c>
       <c r="R120" t="n">
-        <v>6713938</v>
+        <v>6713878</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15520,7 +15511,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15530,7 +15521,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15557,45 +15553,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B121" t="n">
-        <v>91540</v>
+        <v>92495</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R121" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15627,7 +15632,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15637,12 +15642,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15909,7 +15909,7 @@
         <v>129114973</v>
       </c>
       <c r="B124" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>129115572</v>
       </c>
       <c r="B126" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15328,7 +15328,7 @@
         <v>129066471</v>
       </c>
       <c r="B119" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15441,45 +15441,54 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B120" t="n">
-        <v>91540</v>
+        <v>92498</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R120" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15511,7 +15520,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15521,12 +15530,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15553,54 +15557,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129064961</v>
+        <v>129065420</v>
       </c>
       <c r="B121" t="n">
-        <v>92495</v>
+        <v>91543</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524024</v>
+        <v>524074</v>
       </c>
       <c r="R121" t="n">
-        <v>6713938</v>
+        <v>6713878</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15632,7 +15627,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15642,7 +15637,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15672,7 +15672,7 @@
         <v>129065356</v>
       </c>
       <c r="B122" t="n">
-        <v>91313</v>
+        <v>91316</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>129116978</v>
       </c>
       <c r="B123" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>129114973</v>
       </c>
       <c r="B124" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>129116918</v>
       </c>
       <c r="B125" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>129115572</v>
       </c>
       <c r="B126" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15328,7 +15328,7 @@
         <v>129066471</v>
       </c>
       <c r="B119" t="n">
-        <v>92861</v>
+        <v>92863</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>129064961</v>
       </c>
       <c r="B120" t="n">
-        <v>92498</v>
+        <v>92500</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15557,45 +15557,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129065420</v>
+        <v>129065356</v>
       </c>
       <c r="B121" t="n">
-        <v>91543</v>
+        <v>91318</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524074</v>
+        <v>524081</v>
       </c>
       <c r="R121" t="n">
-        <v>6713878</v>
+        <v>6713859</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15627,7 +15636,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15637,12 +15646,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15669,54 +15673,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B122" t="n">
-        <v>91316</v>
+        <v>91545</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R122" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15748,7 +15743,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15758,7 +15753,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15788,7 +15788,7 @@
         <v>129116978</v>
       </c>
       <c r="B123" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>129114973</v>
       </c>
       <c r="B124" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>129116918</v>
       </c>
       <c r="B125" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>129115572</v>
       </c>
       <c r="B126" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15328,7 +15328,7 @@
         <v>129066471</v>
       </c>
       <c r="B119" t="n">
-        <v>92863</v>
+        <v>92867</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15441,54 +15441,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129064961</v>
+        <v>129065420</v>
       </c>
       <c r="B120" t="n">
-        <v>92500</v>
+        <v>91549</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524024</v>
+        <v>524074</v>
       </c>
       <c r="R120" t="n">
-        <v>6713938</v>
+        <v>6713878</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15520,7 +15511,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15530,7 +15521,12 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15560,7 +15556,7 @@
         <v>129065356</v>
       </c>
       <c r="B121" t="n">
-        <v>91318</v>
+        <v>91322</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15673,45 +15669,54 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129065420</v>
+        <v>129064961</v>
       </c>
       <c r="B122" t="n">
-        <v>91545</v>
+        <v>92504</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524074</v>
+        <v>524024</v>
       </c>
       <c r="R122" t="n">
-        <v>6713878</v>
+        <v>6713938</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15743,7 +15748,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15753,12 +15758,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15788,7 +15788,7 @@
         <v>129116978</v>
       </c>
       <c r="B123" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>129114973</v>
       </c>
       <c r="B124" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>129116918</v>
       </c>
       <c r="B125" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>129115572</v>
       </c>
       <c r="B126" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15328,7 +15328,7 @@
         <v>129066471</v>
       </c>
       <c r="B119" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>129065420</v>
       </c>
       <c r="B120" t="n">
-        <v>91549</v>
+        <v>91550</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>129065356</v>
       </c>
       <c r="B121" t="n">
-        <v>91322</v>
+        <v>91323</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>129064961</v>
       </c>
       <c r="B122" t="n">
-        <v>92504</v>
+        <v>92505</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>129116978</v>
       </c>
       <c r="B123" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>129114973</v>
       </c>
       <c r="B124" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>129116918</v>
       </c>
       <c r="B125" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>129115572</v>
       </c>
       <c r="B126" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -12101,7 +12101,7 @@
         <v>125899180</v>
       </c>
       <c r="B92" t="n">
-        <v>58134</v>
+        <v>58204</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15328,7 +15328,7 @@
         <v>129066471</v>
       </c>
       <c r="B119" t="n">
-        <v>92868</v>
+        <v>92871</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15444,7 +15444,7 @@
         <v>129065420</v>
       </c>
       <c r="B120" t="n">
-        <v>91550</v>
+        <v>91553</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>129065356</v>
       </c>
       <c r="B121" t="n">
-        <v>91323</v>
+        <v>91326</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15672,7 +15672,7 @@
         <v>129064961</v>
       </c>
       <c r="B122" t="n">
-        <v>92505</v>
+        <v>92508</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>129116978</v>
       </c>
       <c r="B123" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>129114973</v>
       </c>
       <c r="B124" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>129116918</v>
       </c>
       <c r="B125" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>129115572</v>
       </c>
       <c r="B126" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15441,45 +15441,54 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065420</v>
+        <v>129065356</v>
       </c>
       <c r="B120" t="n">
-        <v>91553</v>
+        <v>91326</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524074</v>
+        <v>524081</v>
       </c>
       <c r="R120" t="n">
-        <v>6713878</v>
+        <v>6713859</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15511,7 +15520,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15521,12 +15530,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15553,54 +15557,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129065356</v>
+        <v>129065420</v>
       </c>
       <c r="B121" t="n">
-        <v>91326</v>
+        <v>91553</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524081</v>
+        <v>524074</v>
       </c>
       <c r="R121" t="n">
-        <v>6713859</v>
+        <v>6713878</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15632,7 +15627,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15642,7 +15637,12 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15441,10 +15441,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129065356</v>
+        <v>129064961</v>
       </c>
       <c r="B120" t="n">
-        <v>91326</v>
+        <v>92508</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15452,43 +15452,43 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524081</v>
+        <v>524024</v>
       </c>
       <c r="R120" t="n">
-        <v>6713859</v>
+        <v>6713938</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15557,45 +15557,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129065420</v>
+        <v>129065356</v>
       </c>
       <c r="B121" t="n">
-        <v>91553</v>
+        <v>91326</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>3215</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524074</v>
+        <v>524081</v>
       </c>
       <c r="R121" t="n">
-        <v>6713878</v>
+        <v>6713859</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15627,7 +15636,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15637,12 +15646,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Längs hela stammen.</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -15669,54 +15673,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129064961</v>
+        <v>129065420</v>
       </c>
       <c r="B122" t="n">
-        <v>92508</v>
+        <v>91553</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvall smedsbo, Banvall smedsbo, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>524024</v>
+        <v>524074</v>
       </c>
       <c r="R122" t="n">
-        <v>6713938</v>
+        <v>6713878</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15748,7 +15743,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -15758,7 +15753,12 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Längs hela stammen.</t>
         </is>
       </c>
       <c r="AD122" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -15441,10 +15441,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129064961</v>
+        <v>129065356</v>
       </c>
       <c r="B120" t="n">
-        <v>92508</v>
+        <v>91326</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -15452,43 +15452,43 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>3215</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
+          <t>Banvallen, Banvallen, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>524024</v>
+        <v>524081</v>
       </c>
       <c r="R120" t="n">
-        <v>6713938</v>
+        <v>6713859</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -15520,7 +15520,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -15530,7 +15530,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -15557,10 +15557,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129065356</v>
+        <v>129064961</v>
       </c>
       <c r="B121" t="n">
-        <v>91326</v>
+        <v>92508</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -15568,43 +15568,43 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>3215</v>
+        <v>4769</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Banvallen, Banvallen, Dlr</t>
+          <t>Snevtjärnen, Snevtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>524081</v>
+        <v>524024</v>
       </c>
       <c r="R121" t="n">
-        <v>6713859</v>
+        <v>6713938</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -15636,7 +15636,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -15646,7 +15646,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="AD121" t="b">

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -12101,7 +12101,7 @@
         <v>125899180</v>
       </c>
       <c r="B92" t="n">
-        <v>58204</v>
+        <v>58207</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -12101,7 +12101,7 @@
         <v>125899180</v>
       </c>
       <c r="B92" t="n">
-        <v>58207</v>
+        <v>58212</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -12101,7 +12101,7 @@
         <v>125899180</v>
       </c>
       <c r="B92" t="n">
-        <v>58212</v>
+        <v>58213</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -12101,7 +12101,7 @@
         <v>125899180</v>
       </c>
       <c r="B92" t="n">
-        <v>58213</v>
+        <v>58215</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -12323,7 +12323,7 @@
         <v>126936299</v>
       </c>
       <c r="B94" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>126934586</v>
       </c>
       <c r="B95" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12565,10 +12565,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126934577</v>
+        <v>126934603</v>
       </c>
       <c r="B96" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12614,10 +12614,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524036</v>
+        <v>524034</v>
       </c>
       <c r="R96" t="n">
-        <v>6713293</v>
+        <v>6713296</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12686,10 +12686,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126934603</v>
+        <v>126934577</v>
       </c>
       <c r="B97" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12735,10 +12735,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>524034</v>
+        <v>524036</v>
       </c>
       <c r="R97" t="n">
-        <v>6713296</v>
+        <v>6713293</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12810,7 +12810,7 @@
         <v>126934164</v>
       </c>
       <c r="B98" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>126933611</v>
       </c>
       <c r="B99" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>126933275</v>
       </c>
       <c r="B100" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>126936539</v>
       </c>
       <c r="B101" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>126932846</v>
       </c>
       <c r="B102" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>126933692</v>
       </c>
       <c r="B103" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>126932450</v>
       </c>
       <c r="B104" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>126933326</v>
       </c>
       <c r="B105" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>126962844</v>
       </c>
       <c r="B106" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>126963368</v>
       </c>
       <c r="B107" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>126961591</v>
       </c>
       <c r="B108" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>126963263</v>
       </c>
       <c r="B109" t="n">
-        <v>91628</v>
+        <v>91615</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>126962269</v>
       </c>
       <c r="B110" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>126963427</v>
       </c>
       <c r="B111" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>126962421</v>
       </c>
       <c r="B112" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>126963583</v>
       </c>
       <c r="B113" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY126"/>
+  <dimension ref="A1:AY127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16267,6 +16267,127 @@
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>130321255</v>
+      </c>
+      <c r="B127" t="n">
+        <v>101109</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Sumpskogen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>524148</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6713407</v>
+      </c>
+      <c r="S127" t="n">
+        <v>5</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -12323,7 +12323,7 @@
         <v>126936299</v>
       </c>
       <c r="B94" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12444,7 +12444,7 @@
         <v>126934586</v>
       </c>
       <c r="B95" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12565,10 +12565,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126934603</v>
+        <v>126934577</v>
       </c>
       <c r="B96" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12614,10 +12614,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>524034</v>
+        <v>524036</v>
       </c>
       <c r="R96" t="n">
-        <v>6713296</v>
+        <v>6713293</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12649,7 +12649,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -12659,7 +12659,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -12686,10 +12686,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>126934577</v>
+        <v>126934603</v>
       </c>
       <c r="B97" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12735,10 +12735,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>524036</v>
+        <v>524034</v>
       </c>
       <c r="R97" t="n">
-        <v>6713293</v>
+        <v>6713296</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12810,7 +12810,7 @@
         <v>126934164</v>
       </c>
       <c r="B98" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>126933611</v>
       </c>
       <c r="B99" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13052,7 +13052,7 @@
         <v>126933275</v>
       </c>
       <c r="B100" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13173,7 +13173,7 @@
         <v>126936539</v>
       </c>
       <c r="B101" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>126932846</v>
       </c>
       <c r="B102" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>126933692</v>
       </c>
       <c r="B103" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13536,7 +13536,7 @@
         <v>126932450</v>
       </c>
       <c r="B104" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13657,7 +13657,7 @@
         <v>126933326</v>
       </c>
       <c r="B105" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>126962844</v>
       </c>
       <c r="B106" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13899,7 +13899,7 @@
         <v>126963368</v>
       </c>
       <c r="B107" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -14020,7 +14020,7 @@
         <v>126961591</v>
       </c>
       <c r="B108" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>126963263</v>
       </c>
       <c r="B109" t="n">
-        <v>91615</v>
+        <v>91628</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>126962269</v>
       </c>
       <c r="B110" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>126963427</v>
       </c>
       <c r="B111" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>126962421</v>
       </c>
       <c r="B112" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>126963583</v>
       </c>
       <c r="B113" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -16272,7 +16272,7 @@
         <v>130321255</v>
       </c>
       <c r="B127" t="n">
-        <v>101109</v>
+        <v>101112</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -16272,7 +16272,7 @@
         <v>130321255</v>
       </c>
       <c r="B127" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -16272,7 +16272,7 @@
         <v>130321255</v>
       </c>
       <c r="B127" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -16272,7 +16272,7 @@
         <v>130321255</v>
       </c>
       <c r="B127" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -16272,7 +16272,7 @@
         <v>130321255</v>
       </c>
       <c r="B127" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -16272,7 +16272,7 @@
         <v>130321255</v>
       </c>
       <c r="B127" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -16272,7 +16272,7 @@
         <v>130321255</v>
       </c>
       <c r="B127" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -16272,7 +16272,7 @@
         <v>130321255</v>
       </c>
       <c r="B127" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -16272,7 +16272,7 @@
         <v>130321255</v>
       </c>
       <c r="B127" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY127"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16388,6 +16388,230 @@
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>131843813</v>
+      </c>
+      <c r="B128" t="n">
+        <v>58061</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Banvallen, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>524150</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6713670</v>
+      </c>
+      <c r="S128" t="n">
+        <v>5</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>131843634</v>
+      </c>
+      <c r="B129" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Banvallen, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>524145</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6713721</v>
+      </c>
+      <c r="S129" t="n">
+        <v>5</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -16393,7 +16393,7 @@
         <v>131843813</v>
       </c>
       <c r="B128" t="n">
-        <v>58061</v>
+        <v>58063</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -16505,7 +16505,7 @@
         <v>131843634</v>
       </c>
       <c r="B129" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -16393,7 +16393,7 @@
         <v>131843813</v>
       </c>
       <c r="B128" t="n">
-        <v>58107</v>
+        <v>58109</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY129"/>
+  <dimension ref="A1:AY131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16612,6 +16612,240 @@
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>133544380</v>
+      </c>
+      <c r="B130" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Banvallen, Smedsbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>523932</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6713818</v>
+      </c>
+      <c r="S130" t="n">
+        <v>5</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>133546012</v>
+      </c>
+      <c r="B131" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>Sumpskogen, Bomsarvet, Borlänge, Dlr</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>523990</v>
+      </c>
+      <c r="R131" t="n">
+        <v>6713262</v>
+      </c>
+      <c r="S131" t="n">
+        <v>5</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Asp.</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -16617,7 +16617,7 @@
         <v>133544380</v>
       </c>
       <c r="B130" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>133546012</v>
       </c>
       <c r="B131" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -16617,7 +16617,7 @@
         <v>133544380</v>
       </c>
       <c r="B130" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>133546012</v>
       </c>
       <c r="B131" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>

--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY142"/>
+  <dimension ref="A1:AZ142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126963263</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122961337</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123562313</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123562349</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123565789</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1332,6 +1362,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123571398</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123572491</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,6 +1586,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126231015</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1658,6 +1703,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129065420</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1774,6 +1824,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129065356</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1881,6 +1936,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128217774</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1997,6 +2057,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064961</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2113,6 +2178,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128217698</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2229,6 +2299,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129066471</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2350,6 +2425,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116918</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2471,6 +2551,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129116978</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2613,6 +2698,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115538741</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2733,6 +2823,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114920743</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2845,6 +2940,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115551643</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2957,6 +3057,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123413633</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3069,6 +3174,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123526941</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3181,6 +3291,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123526961</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3293,6 +3408,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123528562</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3405,6 +3525,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123569917</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3517,6 +3642,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131843634</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3629,6 +3759,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133544380</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3751,6 +3886,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133546012</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3868,6 +4008,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944542</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3980,6 +4125,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134944606</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4095,6 +4245,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125899180</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4223,6 +4378,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113739774</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4339,6 +4499,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958842</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4455,6 +4620,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123562888</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4583,6 +4753,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113739771</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4695,6 +4870,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128217134</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4807,6 +4987,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131843813</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4924,6 +5109,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123563043</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5036,6 +5226,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123568031</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5148,6 +5343,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122915863</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5260,6 +5460,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122959354</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5372,6 +5577,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122959453</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5484,6 +5694,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123761045</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5596,6 +5811,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124434324</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5729,6 +5949,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118592128</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5855,6 +6080,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680065</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5986,6 +6216,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680241</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6117,6 +6352,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680271</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6248,6 +6488,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680340</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6374,6 +6619,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680431</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6500,6 +6750,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680590</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6631,6 +6886,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118680966</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6762,6 +7022,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122817980</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6893,6 +7158,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122821104</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7026,6 +7296,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122821198</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7157,6 +7432,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122821729</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7283,6 +7563,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122821745</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7409,6 +7694,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122821824</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7540,6 +7830,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122916997</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7671,6 +7966,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122917069</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7797,6 +8097,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122957710</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7928,6 +8233,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958064</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8059,6 +8369,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958244</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8185,6 +8500,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958484</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8316,6 +8636,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958550</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8447,6 +8772,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122958631</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8568,6 +8898,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122959503</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8689,6 +9024,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123412257</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8810,6 +9150,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123412326</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8931,6 +9276,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123412367</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9062,6 +9412,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123412439</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9188,6 +9543,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123412973</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9314,6 +9674,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123413078</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9447,6 +9812,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123413119</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9568,6 +9938,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123413726</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9689,6 +10064,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123413856</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9810,6 +10190,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123414270</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9931,6 +10316,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123414352</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -10062,6 +10452,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123525488</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -10193,6 +10588,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123526406</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -10319,6 +10719,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123526470</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10440,6 +10845,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123527655</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10569,6 +10979,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123527741</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10698,6 +11113,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123528345</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10819,6 +11239,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123564666</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10940,6 +11365,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123564906</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -11061,6 +11491,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123566656</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -11182,6 +11617,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123566767</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -11303,6 +11743,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123567299</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11424,6 +11869,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123567823</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11545,6 +11995,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123570699</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11666,6 +12121,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123760786</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11787,6 +12247,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123761091</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11913,6 +12378,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124431501</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -12034,6 +12504,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124431841</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -12155,6 +12630,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432135</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -12276,6 +12756,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124432412</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12397,6 +12882,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124433963</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12528,6 +13018,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124434100</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12659,6 +13154,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124435133</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12780,6 +13280,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124711417</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12901,6 +13406,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125899247</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -13022,6 +13532,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932450</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -13143,6 +13658,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126932846</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -13264,6 +13784,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126933275</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -13385,6 +13910,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126933326</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13506,6 +14036,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126933611</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13627,6 +14162,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126933692</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13748,6 +14288,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126934164</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13869,6 +14414,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126934577</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13993,6 +14543,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126934586</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -14114,6 +14669,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126934603</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -14235,6 +14795,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126935325</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -14356,6 +14921,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936299</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -14477,6 +15047,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126936539</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14603,6 +15178,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126961591</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -14724,6 +15304,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126962144</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -14845,6 +15430,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126962269</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14966,6 +15556,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126962421</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -15087,6 +15682,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126962844</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -15208,6 +15808,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126963368</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -15329,6 +15934,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126963427</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -15460,6 +16070,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126963583</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -15576,6 +16191,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127727170</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -15692,6 +16312,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127727173</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -15813,6 +16438,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064197</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -15925,6 +16555,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129064260</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -16046,6 +16681,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129114973</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -16167,6 +16807,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129115572</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -16279,6 +16924,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123569808</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -16408,6 +17058,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123569630</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -16541,6 +17196,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123762639</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -16662,6 +17322,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123768932</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -16774,6 +17439,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123768976</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -16886,6 +17556,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123768989</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -16998,6 +17673,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123768995</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -17110,6 +17790,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123769023</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -17231,6 +17916,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123769072</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -17352,6 +18042,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123769093</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -17464,6 +18159,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123769126</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -17585,6 +18285,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321255</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -17706,8 +18411,156 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132755530</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 37099-2024 artfynd.xlsx
+++ b/artfynd/A 37099-2024 artfynd.xlsx
@@ -3897,7 +3897,7 @@
         <v>134944542</v>
       </c>
       <c r="B29" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>134944606</v>
       </c>
       <c r="B30" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
